--- a/out/Logo Library - Research Index.xlsx
+++ b/out/Logo Library - Research Index.xlsx
@@ -1450,12 +1450,12 @@
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>Bank uses a lockup with wave symbol + wordmark; wordmark is the recognised public mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J2" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K2" s="8" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N2" s="6" t="inlineStr">
         <is>
-          <t>State-owned (KBMI 4). Asset not sourced - egress blocked this session; verify against OJK/BI registry and pull official asset.</t>
+          <t>State-owned (KBMI 4).</t>
         </is>
       </c>
     </row>
@@ -1510,12 +1510,12 @@
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
-          <t>Traditional bank with no separate compact symbol in common use</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J3" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K3" s="8" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="N3" s="6" t="inlineStr">
         <is>
-          <t>State-owned (KBMI 4). Asset not sourced - egress blocked this session; verify against OJK/BI registry.</t>
+          <t>State-owned (KBMI 4). Verify: OJK/BI register.</t>
         </is>
       </c>
     </row>
@@ -1570,12 +1570,12 @@
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>BNI "46" mark is widely used standalone in compact checkout UI</t>
+          <t>Standalone symbol, reads well compact</t>
         </is>
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square-ish icon)</t>
+          <t>TBD (square-ish)</t>
         </is>
       </c>
       <c r="K4" s="8" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>State-owned (KBMI 4). Asset not sourced - egress blocked this session; verify against OJK/BI registry.</t>
+          <t>State-owned (KBMI 4). Verify: OJK/BI register.</t>
         </is>
       </c>
     </row>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>BCA has a distinct symbol used standalone on Indonesian checkout screens</t>
+          <t>Standalone symbol, reads well compact</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square-ish icon)</t>
+          <t>TBD (square-ish)</t>
         </is>
       </c>
       <c r="K5" s="8" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>Largest private bank. Asset not sourced - egress blocked this session; verify against OJK/BI registry.</t>
+          <t>Largest private bank. Verify: OJK/BI register.</t>
         </is>
       </c>
     </row>
@@ -1690,12 +1690,12 @@
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>No separate compact symbol commonly used</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>State-owned. Asset not sourced - egress blocked this session; verify against OJK/BI registry.</t>
+          <t>State-owned. Verify: OJK/BI register.</t>
         </is>
       </c>
     </row>
@@ -1750,12 +1750,12 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>Post-2021 merger identity; wordmark+symbol lockup is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J7" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K7" s="8" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>Formed 2021 from BRIsyariah/BNI Syariah/Mandiri Syariah merger. Asset not sourced - egress blocked.</t>
+          <t>Formed 2021 from BRIsyariah/BNI Syariah/Mandiri Syariah merger.</t>
         </is>
       </c>
     </row>
@@ -1810,12 +1810,12 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>Group wordmark with local suffix; no standalone compact symbol</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K8" s="8" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
-          <t>Asset not sourced - egress blocked this session; verify against OJK/BI registry.</t>
+          <t>Verify: OJK/BI register.</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>Wordmark is the recognised mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K9" s="8" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>MUFG-controlled. Asset not sourced - egress blocked this session.</t>
+          <t>MUFG-controlled.</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>Wordmark lockup is the public mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K10" s="8" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>Owned by Bangkok Bank. Asset not sourced - egress blocked this session.</t>
+          <t>Owned by Bangkok Bank.</t>
         </is>
       </c>
     </row>
@@ -1990,12 +1990,12 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>Traditional bank wordmark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J11" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K11" s="8" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>Asset not sourced - egress blocked this session; verify against OJK/BI registry.</t>
+          <t>Verify: OJK/BI register.</t>
         </is>
       </c>
     </row>
@@ -2050,12 +2050,12 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>Group wordmark; dropped "NISP" in 2023 rebrand</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K12" s="8" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>Rebranded from OCBC NISP (2023) - do not use pre-rebrand asset. Egress blocked this session.</t>
+          <t>Rebranded from OCBC NISP (2023) - do not use pre-rebrand asset.</t>
         </is>
       </c>
     </row>
@@ -2110,12 +2110,12 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>Group tiger-head + wordmark lockup</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J13" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K13" s="8" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>Asset not sourced - egress blocked this session.</t>
+          <t>Candidate row; regulator check and asset sourcing outstanding.</t>
         </is>
       </c>
     </row>
@@ -2166,12 +2166,12 @@
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>Group SMBC wordmark post-rebrand</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K14" s="8" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>Renamed from Bank BTPN effective 2 Oct 2024 - do NOT use BTPN asset. Official domain changed post-rebrand; confirm before sourcing. Egress blocked this session.</t>
+          <t>Renamed from Bank BTPN effective 2 Oct 2024 - do NOT use BTPN asset. Official domain changed post-rebrand; confirm before sourcing.</t>
         </is>
       </c>
     </row>
@@ -2226,12 +2226,12 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>Wordmark with symbol lockup</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J15" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K15" s="8" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>CT Corp group. Asset not sourced - egress blocked this session.</t>
+          <t>CT Corp group.</t>
         </is>
       </c>
     </row>
@@ -2286,12 +2286,12 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>KB group wordmark post-rebrand</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K16" s="8" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
-          <t>Rebranded from KB Bukopin (2024) - confirm current name/domain. Egress blocked this session.</t>
+          <t>Rebranded from KB Bukopin (2024) - confirm current name/domain.</t>
         </is>
       </c>
     </row>
@@ -2346,12 +2346,12 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>Wordmark lockup</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K17" s="8" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
-          <t>Retains BTPN Syariah name despite parent rebrand - confirm. Egress blocked this session.</t>
+          <t>Retains BTPN Syariah name despite parent rebrand - confirm.</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>Wordmark lockup</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K18" s="8" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
-          <t>Asset not sourced - egress blocked this session.</t>
+          <t>Candidate row; regulator check and asset sourcing outstanding.</t>
         </is>
       </c>
     </row>
@@ -2466,12 +2466,12 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>Regional development bank wordmark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K19" s="8" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
-          <t>Regional (BPD West Java). Asset not sourced - egress blocked this session.</t>
+          <t>Regional (BPD West Java).</t>
         </is>
       </c>
     </row>
@@ -2526,12 +2526,12 @@
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>Regional development bank wordmark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K20" s="8" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="N20" s="6" t="inlineStr">
         <is>
-          <t>Regional (Jakarta). Asset not sourced - egress blocked this session.</t>
+          <t>Regional (Jakarta).</t>
         </is>
       </c>
     </row>
@@ -2586,12 +2586,12 @@
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>Regional development bank wordmark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K21" s="8" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>Regional (East Java). Asset not sourced - egress blocked this session.</t>
+          <t>Regional (East Java).</t>
         </is>
       </c>
     </row>
@@ -2646,12 +2646,12 @@
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>Wordmark lockup</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K22" s="8" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="N22" s="6" t="inlineStr">
         <is>
-          <t>First Indonesian sharia bank. Asset not sourced - egress blocked this session.</t>
+          <t>First Indonesian sharia bank.</t>
         </is>
       </c>
     </row>
@@ -2706,12 +2706,12 @@
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>Digital-first bank; app icon is the most recognised public mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K23" s="8" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
-          <t>Digital bank. Asset not sourced - egress blocked this session.</t>
+          <t>Digital bank.</t>
         </is>
       </c>
     </row>
@@ -2766,12 +2766,12 @@
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>Digital bank; app icon dominates consumer recognition</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K24" s="8" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="N24" s="6" t="inlineStr">
         <is>
-          <t>Sea Group. Asset not sourced - egress blocked this session.</t>
+          <t>Sea Group.</t>
         </is>
       </c>
     </row>
@@ -2826,12 +2826,12 @@
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>Digital bank; app icon is the primary consumer mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K25" s="8" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="N25" s="6" t="inlineStr">
         <is>
-          <t>CT Corp group. Asset not sourced - egress blocked this session.</t>
+          <t>CT Corp group.</t>
         </is>
       </c>
     </row>
@@ -2886,12 +2886,12 @@
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>Digital bank; app icon is the primary consumer mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K26" s="8" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
-          <t>Grab/Singtel/Emtek backed. Asset not sourced - egress blocked this session.</t>
+          <t>Grab/Singtel/Emtek backed.</t>
         </is>
       </c>
     </row>
@@ -2946,12 +2946,12 @@
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>Digital bank; app icon is the primary consumer mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K27" s="8" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="N27" s="6" t="inlineStr">
         <is>
-          <t>Asset not sourced - egress blocked this session.</t>
+          <t>Candidate row; regulator check and asset sourcing outstanding.</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>Digital sub-brand; app icon is the recognised mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K28" s="8" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>Distinct brand from BCA parent - keep separate row. Egress blocked this session.</t>
+          <t>Distinct brand from BCA parent - keep separate row.</t>
         </is>
       </c>
     </row>
@@ -3066,12 +3066,12 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>HSBC hexagon symbol is used standalone in compact UI</t>
+          <t>Standalone symbol, reads well compact</t>
         </is>
       </c>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square-ish icon)</t>
+          <t>TBD (square-ish)</t>
         </is>
       </c>
       <c r="K29" s="8" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>Local arm of global group. Asset not sourced - egress blocked this session.</t>
+          <t>Local arm of global group.</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>Group wordmark lockup</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K30" s="8" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>Acquired Citi Indonesia consumer business (2023). Egress blocked this session.</t>
+          <t>Acquired Citi Indonesia consumer business (2023).</t>
         </is>
       </c>
     </row>
@@ -3186,12 +3186,12 @@
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>Citi wordmark with arc is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K31" s="8" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>E-wallet whose rounded-square app icon is its most recognised public mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K32" s="8" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="N32" s="6" t="inlineStr">
         <is>
-          <t>Top-5 wallet (GoTo group). Asset not sourced - egress blocked this session; verify against BI e-money licence list.</t>
+          <t>Top-5 wallet (GoTo group). Verify: BI e-money licence list.</t>
         </is>
       </c>
     </row>
@@ -3306,12 +3306,12 @@
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>Purple app icon is the dominant consumer mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J33" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="N33" s="6" t="inlineStr">
         <is>
-          <t>Top-5 wallet (Grab-controlled). Asset not sourced - egress blocked this session.</t>
+          <t>Top-5 wallet (Grab-controlled).</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>App icon is the dominant consumer mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J34" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K34" s="8" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="N34" s="6" t="inlineStr">
         <is>
-          <t>Top-5 wallet (Ant Group backed). Asset not sourced - egress blocked this session.</t>
+          <t>Top-5 wallet (Ant Group backed).</t>
         </is>
       </c>
     </row>
@@ -3426,12 +3426,12 @@
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>In-app wallet brand; app-icon style mark used at checkout</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J35" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K35" s="8" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>App icon is the dominant consumer mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K36" s="8" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="N36" s="6" t="inlineStr">
         <is>
-          <t>Top-5 wallet (Telkomsel/state-linked). Asset not sourced - egress blocked this session.</t>
+          <t>Top-5 wallet (Telkomsel/state-linked).</t>
         </is>
       </c>
     </row>
@@ -3546,12 +3546,12 @@
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>App icon is the primary consumer mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K37" s="8" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="N37" s="6" t="inlineStr">
         <is>
-          <t>Astra group. Asset not sourced - egress blocked this session.</t>
+          <t>Astra group.</t>
         </is>
       </c>
     </row>
@@ -3606,12 +3606,12 @@
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>App icon is the primary consumer mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K38" s="8" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="N38" s="6" t="inlineStr">
         <is>
-          <t>Indomaret-affiliated wallet. Confirm current operating status. Egress blocked this session.</t>
+          <t>Indomaret-affiliated wallet. Confirm current operating status.</t>
         </is>
       </c>
     </row>
@@ -3666,12 +3666,12 @@
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>Primarily a PSP brand; wordmark is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J39" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K39" s="8" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="N39" s="6" t="inlineStr">
         <is>
-          <t>Payment gateway + wallet. Asset not sourced - egress blocked this session.</t>
+          <t>Payment gateway + wallet.</t>
         </is>
       </c>
     </row>
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>App icon is the primary consumer mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K40" s="8" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="N40" s="6" t="inlineStr">
         <is>
-          <t>Transfer/remittance app. Asset not sourced - egress blocked this session.</t>
+          <t>Transfer/remittance app.</t>
         </is>
       </c>
     </row>
@@ -3786,12 +3786,12 @@
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>App icon is the primary consumer mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J41" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K41" s="8" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>Retail chain identity is a horizontal wordmark used on storefront and checkout</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J43" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K43" s="8" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="N43" s="6" t="inlineStr">
         <is>
-          <t>Market leader. Also now operates acquired Lawson Indonesia stores. Egress blocked this session.</t>
+          <t>Market leader. Also now operates acquired Lawson Indonesia stores.</t>
         </is>
       </c>
     </row>
@@ -3950,12 +3950,12 @@
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>Horizontal wordmark is the storefront and payment-channel mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J44" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K44" s="8" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="N44" s="6" t="inlineStr">
         <is>
-          <t>Market leader. Asset not sourced - egress blocked this session.</t>
+          <t>Market leader.</t>
         </is>
       </c>
     </row>
@@ -4010,12 +4010,12 @@
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>Horizontal wordmark, same family as Alfamart</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J45" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K45" s="8" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="N45" s="6" t="inlineStr">
         <is>
-          <t>Confirm official domain. Asset not sourced - egress blocked this session.</t>
+          <t>Confirm official domain.</t>
         </is>
       </c>
     </row>
@@ -4070,12 +4070,12 @@
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>Circle K roundel is used standalone and reads well compact</t>
+          <t>Standalone symbol, reads well compact</t>
         </is>
       </c>
       <c r="J46" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square-ish icon)</t>
+          <t>TBD (square-ish)</t>
         </is>
       </c>
       <c r="K46" s="8" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="N46" s="6" t="inlineStr">
         <is>
-          <t>Confirm current franchise status in Indonesia. Egress blocked this session.</t>
+          <t>Confirm current franchise status in Indonesia.</t>
         </is>
       </c>
     </row>
@@ -4130,12 +4130,12 @@
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>Milk-can roundel is the recognised standalone mark</t>
+          <t>Standalone symbol, reads well compact</t>
         </is>
       </c>
       <c r="J47" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square-ish icon)</t>
+          <t>TBD (square-ish)</t>
         </is>
       </c>
       <c r="K47" s="8" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>Wordmark with green/blue stripes is the standard storefront mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J48" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K48" s="8" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="N48" s="6" t="inlineStr">
         <is>
-          <t>Confirm current footprint in Indonesia. Egress blocked this session.</t>
+          <t>Confirm current footprint in Indonesia.</t>
         </is>
       </c>
     </row>
@@ -4330,12 +4330,12 @@
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>Orange bag app icon is the dominant consumer mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J51" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K51" s="8" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="N51" s="6" t="inlineStr">
         <is>
-          <t>Market leader. Asset not sourced - egress blocked this session.</t>
+          <t>Market leader.</t>
         </is>
       </c>
     </row>
@@ -4390,12 +4390,12 @@
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>Green owl app icon is the dominant consumer mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J52" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K52" s="8" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="N52" s="6" t="inlineStr">
         <is>
-          <t>TikTok acquired majority stake (2024); brand still operates. Egress blocked this session.</t>
+          <t>TikTok acquired majority stake (2024); brand still operates.</t>
         </is>
       </c>
     </row>
@@ -4450,12 +4450,12 @@
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>App icon is the dominant consumer mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J53" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K53" s="8" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="N53" s="6" t="inlineStr">
         <is>
-          <t>Alibaba group. Asset not sourced - egress blocked this session.</t>
+          <t>Alibaba group.</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>App icon is the dominant consumer mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J54" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K54" s="8" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>App icon is the dominant consumer mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J55" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K55" s="8" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="N55" s="6" t="inlineStr">
         <is>
-          <t>Djarum/GDP Venture group. Asset not sourced - egress blocked this session.</t>
+          <t>Djarum/GDP Venture group.</t>
         </is>
       </c>
     </row>
@@ -4630,12 +4630,12 @@
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>Fashion brand uses a horizontal wordmark as primary mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J56" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K56" s="8" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="N56" s="6" t="inlineStr">
         <is>
-          <t>Asset not sourced - egress blocked this session.</t>
+          <t>Candidate row; regulator check and asset sourcing outstanding.</t>
         </is>
       </c>
     </row>
@@ -4690,12 +4690,12 @@
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>Note mark is the recognised compact brand</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J57" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K57" s="8" t="inlineStr">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>App icon is the primary consumer mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J58" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K58" s="8" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="N58" s="6" t="inlineStr">
         <is>
-          <t>Primarily BNPL/paylater rather than pure marketplace - confirm category fit. Egress blocked this session.</t>
+          <t>Primarily BNPL/paylater rather than pure marketplace - confirm category fit.</t>
         </is>
       </c>
     </row>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>Wordmark is the primary brand mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J59" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K59" s="8" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="N59" s="6" t="inlineStr">
         <is>
-          <t>Mother/baby vertical (Sirclo group). Confirm current status. Egress blocked this session.</t>
+          <t>Mother/baby vertical (Sirclo group). Confirm current status.</t>
         </is>
       </c>
     </row>
@@ -4870,12 +4870,12 @@
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t>Wordmark is the primary brand mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J60" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K60" s="8" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="N60" s="6" t="inlineStr">
         <is>
-          <t>Beauty vertical. Asset not sourced - egress blocked this session.</t>
+          <t>Beauty vertical.</t>
         </is>
       </c>
     </row>
@@ -5014,12 +5014,12 @@
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
-          <t>Red "DBS" wordmark is the standard mark; no separate symbol in common compact use</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J63" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K63" s="8" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="N63" s="6" t="inlineStr">
         <is>
-          <t>Verify against MAS licensed-banks register. Asset not sourced - egress blocked this session.</t>
+          <t>Verify: MAS register.</t>
         </is>
       </c>
     </row>
@@ -5078,12 +5078,12 @@
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
-          <t>Group wordmark is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J64" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K64" s="8" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="N64" s="6" t="inlineStr">
         <is>
-          <t>Verify against MAS register. Asset not sourced - egress blocked this session.</t>
+          <t>Verify: MAS register.</t>
         </is>
       </c>
     </row>
@@ -5142,12 +5142,12 @@
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>Wordmark lockup is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J65" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K65" s="8" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="N65" s="6" t="inlineStr">
         <is>
-          <t>Verify against MAS register. Asset not sourced - egress blocked this session.</t>
+          <t>Verify: MAS register.</t>
         </is>
       </c>
     </row>
@@ -5206,12 +5206,12 @@
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>Group wordmark with twist symbol</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J66" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K66" s="8" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="N66" s="6" t="inlineStr">
         <is>
-          <t>Verify against MAS register. Consider whether local variants duplicate the international row.</t>
+          <t>Verify: MAS register. Consider whether local variants duplicate the international row.</t>
         </is>
       </c>
     </row>
@@ -5270,12 +5270,12 @@
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>Citi wordmark with arc</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J67" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K67" s="8" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="N67" s="6" t="inlineStr">
         <is>
-          <t>Verify against MAS register. Consider whether local variants duplicate the international row.</t>
+          <t>Verify: MAS register. Consider whether local variants duplicate the international row.</t>
         </is>
       </c>
     </row>
@@ -5334,12 +5334,12 @@
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
-          <t>Group tiger-head + wordmark lockup</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J68" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K68" s="8" t="inlineStr">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="N68" s="6" t="inlineStr">
         <is>
-          <t>Verify against MAS register. Same group mark as Maybank MY - confirm whether a distinct SG asset is needed.</t>
+          <t>Verify: MAS register. Same group mark as Maybank MY - confirm whether a distinct SG asset is needed.</t>
         </is>
       </c>
     </row>
@@ -5398,12 +5398,12 @@
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>Tiger-head + wordmark lockup is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J69" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K69" s="8" t="inlineStr">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="N69" s="6" t="inlineStr">
         <is>
-          <t>Verify against BNM licensed-institutions list. Asset not sourced - egress blocked this session.</t>
+          <t>Verify: BNM list.</t>
         </is>
       </c>
     </row>
@@ -5462,12 +5462,12 @@
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
-          <t>Group wordmark is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J70" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K70" s="8" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="N70" s="6" t="inlineStr">
         <is>
-          <t>Verify against BNM list. Asset not sourced - egress blocked this session.</t>
+          <t>Verify: BNM list.</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>Traditional bank wordmark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J71" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K71" s="8" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="N71" s="6" t="inlineStr">
         <is>
-          <t>Verify against BNM list. Asset not sourced - egress blocked this session.</t>
+          <t>Verify: BNM list.</t>
         </is>
       </c>
     </row>
@@ -5590,12 +5590,12 @@
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
-          <t>Group wordmark is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J72" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K72" s="8" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="N72" s="6" t="inlineStr">
         <is>
-          <t>Verify against BNM list. Asset not sourced - egress blocked this session.</t>
+          <t>Verify: BNM list.</t>
         </is>
       </c>
     </row>
@@ -5654,12 +5654,12 @@
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>Traditional bank wordmark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J73" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K73" s="8" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="N73" s="6" t="inlineStr">
         <is>
-          <t>Verify against BNM list. Asset not sourced - egress blocked this session.</t>
+          <t>Verify: BNM list.</t>
         </is>
       </c>
     </row>
@@ -5718,12 +5718,12 @@
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
-          <t>Group wordmark is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J74" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K74" s="8" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="N74" s="6" t="inlineStr">
         <is>
-          <t>Verify against BNM list. Asset not sourced - egress blocked this session.</t>
+          <t>Verify: BNM list.</t>
         </is>
       </c>
     </row>
@@ -5782,12 +5782,12 @@
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
-          <t>Wordmark lockup is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J75" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K75" s="8" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="N75" s="6" t="inlineStr">
         <is>
-          <t>Verify against BNM list. Asset not sourced - egress blocked this session.</t>
+          <t>Verify: BNM list.</t>
         </is>
       </c>
     </row>
@@ -5846,12 +5846,12 @@
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
-          <t>Blue magnolia/leaf symbol is used standalone in Thai checkout UI</t>
+          <t>Standalone symbol, reads well compact</t>
         </is>
       </c>
       <c r="J76" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square-ish icon)</t>
+          <t>TBD (square-ish)</t>
         </is>
       </c>
       <c r="K76" s="8" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="N76" s="6" t="inlineStr">
         <is>
-          <t>Verify against Bank of Thailand register. Owns PermataBank Indonesia. Egress blocked this session.</t>
+          <t>Verify: BOT register. Owns PermataBank Indonesia.</t>
         </is>
       </c>
     </row>
@@ -5910,12 +5910,12 @@
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
-          <t>Green sheaf symbol is used standalone and is highly recognised in Thai UI</t>
+          <t>Standalone symbol, reads well compact</t>
         </is>
       </c>
       <c r="J77" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square-ish icon)</t>
+          <t>TBD (square-ish)</t>
         </is>
       </c>
       <c r="K77" s="8" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="N77" s="6" t="inlineStr">
         <is>
-          <t>Verify against BOT register. Asset not sourced - egress blocked this session.</t>
+          <t>Verify: BOT register.</t>
         </is>
       </c>
     </row>
@@ -5974,12 +5974,12 @@
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
-          <t>Purple shield/leaf symbol is used standalone in Thai UI</t>
+          <t>Standalone symbol, reads well compact</t>
         </is>
       </c>
       <c r="J78" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square-ish icon)</t>
+          <t>TBD (square-ish)</t>
         </is>
       </c>
       <c r="K78" s="8" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="N78" s="6" t="inlineStr">
         <is>
-          <t>Verify against BOT register. Asset not sourced - egress blocked this session.</t>
+          <t>Verify: BOT register.</t>
         </is>
       </c>
     </row>
@@ -6038,12 +6038,12 @@
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
-          <t>Blue symbol used standalone in Thai UI</t>
+          <t>Standalone symbol, reads well compact</t>
         </is>
       </c>
       <c r="J79" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square-ish icon)</t>
+          <t>TBD (square-ish)</t>
         </is>
       </c>
       <c r="K79" s="8" t="inlineStr">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="N79" s="6" t="inlineStr">
         <is>
-          <t>Verify against BOT register. State-owned. Egress blocked this session.</t>
+          <t>Verify: BOT register. State-owned.</t>
         </is>
       </c>
     </row>
@@ -6102,12 +6102,12 @@
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
-          <t>Yellow symbol used standalone in Thai UI</t>
+          <t>Standalone symbol, reads well compact</t>
         </is>
       </c>
       <c r="J80" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square-ish icon)</t>
+          <t>TBD (square-ish)</t>
         </is>
       </c>
       <c r="K80" s="8" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="N80" s="6" t="inlineStr">
         <is>
-          <t>Verify against BOT register. MUFG-controlled. Egress blocked this session.</t>
+          <t>Verify: BOT register. MUFG-controlled.</t>
         </is>
       </c>
     </row>
@@ -6166,12 +6166,12 @@
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
-          <t>Lowercase "ttb" wordmark is the post-merger mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J81" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K81" s="8" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="N81" s="6" t="inlineStr">
         <is>
-          <t>Formed from TMB + Thanachart merger - do NOT use legacy TMB or Thanachart assets. Verify against BOT register.</t>
+          <t>Formed from TMB + Thanachart merger - do NOT use legacy TMB or Thanachart assets. Verify: BOT register.</t>
         </is>
       </c>
     </row>
@@ -6230,12 +6230,12 @@
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
-          <t>Wordmark lockup is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J82" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K82" s="8" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="N82" s="6" t="inlineStr">
         <is>
-          <t>Verify against BSP directory. Asset not sourced - egress blocked this session.</t>
+          <t>Verify: BSP directory.</t>
         </is>
       </c>
     </row>
@@ -6294,12 +6294,12 @@
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
-          <t>Wordmark is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J83" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K83" s="8" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="N83" s="6" t="inlineStr">
         <is>
-          <t>Verify against BSP directory. Rebranded identity in recent years - use current asset only.</t>
+          <t>Verify: BSP directory. Rebranded identity in recent years - use current asset only.</t>
         </is>
       </c>
     </row>
@@ -6358,12 +6358,12 @@
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
-          <t>Wordmark lockup is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J84" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K84" s="8" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="N84" s="6" t="inlineStr">
         <is>
-          <t>Verify against BSP directory. Asset not sourced - egress blocked this session.</t>
+          <t>Verify: BSP directory.</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
-          <t>Wordmark lockup is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J85" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K85" s="8" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="N85" s="6" t="inlineStr">
         <is>
-          <t>State-owned. Verify against BSP directory. Egress blocked this session.</t>
+          <t>State-owned. Verify: BSP directory.</t>
         </is>
       </c>
     </row>
@@ -6486,12 +6486,12 @@
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
-          <t>Wordmark lockup is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J86" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K86" s="8" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="N86" s="6" t="inlineStr">
         <is>
-          <t>Verify against BSP directory. Asset not sourced - egress blocked this session.</t>
+          <t>Verify: BSP directory.</t>
         </is>
       </c>
     </row>
@@ -6550,12 +6550,12 @@
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
-          <t>Wordmark lockup is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J87" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K87" s="8" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="N87" s="6" t="inlineStr">
         <is>
-          <t>Verify against BSP directory. Asset not sourced - egress blocked this session.</t>
+          <t>Verify: BSP directory.</t>
         </is>
       </c>
     </row>
@@ -6614,12 +6614,12 @@
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
-          <t>Green/gold wordmark lockup is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J88" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K88" s="8" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="N88" s="6" t="inlineStr">
         <is>
-          <t>Verify against State Bank of Vietnam list. Asset not sourced - egress blocked this session.</t>
+          <t>Verify: SBV list.</t>
         </is>
       </c>
     </row>
@@ -6678,12 +6678,12 @@
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
-          <t>Wordmark lockup is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J89" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K89" s="8" t="inlineStr">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="N89" s="6" t="inlineStr">
         <is>
-          <t>Verify against SBV list. Asset not sourced - egress blocked this session.</t>
+          <t>Verify: SBV list.</t>
         </is>
       </c>
     </row>
@@ -6742,12 +6742,12 @@
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
-          <t>Wordmark lockup is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J90" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K90" s="8" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="N90" s="6" t="inlineStr">
         <is>
-          <t>Verify against SBV list. Asset not sourced - egress blocked this session.</t>
+          <t>Verify: SBV list.</t>
         </is>
       </c>
     </row>
@@ -6806,12 +6806,12 @@
       </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
-          <t>Red wordmark is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J91" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K91" s="8" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="N91" s="6" t="inlineStr">
         <is>
-          <t>Verify against SBV list. Asset not sourced - egress blocked this session.</t>
+          <t>Verify: SBV list.</t>
         </is>
       </c>
     </row>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
-          <t>Wordmark lockup is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J92" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K92" s="8" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="N92" s="6" t="inlineStr">
         <is>
-          <t>Verify against SBV list. Asset not sourced - egress blocked this session.</t>
+          <t>Verify: SBV list.</t>
         </is>
       </c>
     </row>
@@ -6934,12 +6934,12 @@
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
-          <t>Wordmark lockup is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J93" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K93" s="8" t="inlineStr">
@@ -6955,7 +6955,7 @@
       </c>
       <c r="N93" s="6" t="inlineStr">
         <is>
-          <t>Verify against SBV list. Asset not sourced - egress blocked this session.</t>
+          <t>Verify: SBV list.</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
-          <t>Wordmark lockup is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J94" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K94" s="8" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="N94" s="6" t="inlineStr">
         <is>
-          <t>Verify against SBV list. Asset not sourced - egress blocked this session.</t>
+          <t>Verify: SBV list.</t>
         </is>
       </c>
     </row>
@@ -7062,12 +7062,12 @@
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
-          <t>Wordmark lockup is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J95" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K95" s="8" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="N95" s="6" t="inlineStr">
         <is>
-          <t>Verify against National Bank of Cambodia list. Lower-priority market per brief.</t>
+          <t>Verify: NBC list. Lower-priority market per brief.</t>
         </is>
       </c>
     </row>
@@ -7126,12 +7126,12 @@
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
-          <t>Wordmark lockup is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J96" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K96" s="8" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="N96" s="6" t="inlineStr">
         <is>
-          <t>Verify against Bank of the Lao PDR. Lower-priority market; limited asset availability expected.</t>
+          <t>Verify: BOL list. Lower-priority market; limited asset availability expected.</t>
         </is>
       </c>
     </row>
@@ -7190,12 +7190,12 @@
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
-          <t>Wordmark lockup is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J97" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K97" s="8" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="N97" s="6" t="inlineStr">
         <is>
-          <t>Verify against Brunei Darussalam Central Bank. Lower-priority market per brief.</t>
+          <t>Verify: BDCB list. Lower-priority market per brief.</t>
         </is>
       </c>
     </row>
@@ -7298,12 +7298,12 @@
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
-          <t>Grab green app-icon style mark is the recognised wallet brand</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J99" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K99" s="8" t="inlineStr">
@@ -7362,12 +7362,12 @@
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
-          <t>App icon is the recognised consumer mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J100" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K100" s="8" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="N100" s="6" t="inlineStr">
         <is>
-          <t>Verify against MAS e-money/major payment institution register. Egress blocked this session.</t>
+          <t>Verify: MAS register.</t>
         </is>
       </c>
     </row>
@@ -7426,12 +7426,12 @@
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
-          <t>App icon is the recognised consumer mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J101" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K101" s="8" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
-          <t>App icon is the recognised consumer mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J102" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K102" s="8" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="N102" s="6" t="inlineStr">
         <is>
-          <t>Confirm current operating status and ownership (Pine Labs group) before sourcing. Egress blocked this session.</t>
+          <t>Confirm current operating status and ownership (Pine Labs group) before sourcing.</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
-          <t>App icon is the recognised consumer mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J103" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K103" s="8" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="N103" s="6" t="inlineStr">
         <is>
-          <t>Multi-currency card/wallet. Verify against MAS register. Egress blocked this session.</t>
+          <t>Multi-currency card/wallet. Verify: MAS register.</t>
         </is>
       </c>
     </row>
@@ -7618,12 +7618,12 @@
       </c>
       <c r="I104" s="6" t="inlineStr">
         <is>
-          <t>App icon is the dominant consumer mark in Malaysia</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J104" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K104" s="8" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="N104" s="6" t="inlineStr">
         <is>
-          <t>Market leader MY. Verify against BNM e-money licensee list. Egress blocked this session.</t>
+          <t>Market leader MY. Verify: BNM list.</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
-          <t>Grab app-icon style mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J105" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K105" s="8" t="inlineStr">
@@ -7746,12 +7746,12 @@
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
-          <t>App icon is the recognised consumer mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J106" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K106" s="8" t="inlineStr">
@@ -7767,7 +7767,7 @@
       </c>
       <c r="N106" s="6" t="inlineStr">
         <is>
-          <t>Axiata group. Verify against BNM list. Egress blocked this session.</t>
+          <t>Axiata group. Verify: BNM list.</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="I107" s="6" t="inlineStr">
         <is>
-          <t>In-app wallet brand; app-icon style mark used at checkout</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J107" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K107" s="8" t="inlineStr">
@@ -7874,12 +7874,12 @@
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
-          <t>App icon is the recognised consumer mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J108" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K108" s="8" t="inlineStr">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="N108" s="6" t="inlineStr">
         <is>
-          <t>Capital A/AirAsia group. Verify against BNM list. Egress blocked this session.</t>
+          <t>Capital A/AirAsia group. Verify: BNM list.</t>
         </is>
       </c>
     </row>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
-          <t>App icon is the dominant consumer mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J109" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K109" s="8" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="N109" s="6" t="inlineStr">
         <is>
-          <t>Ascend Money group; operates across SEA incl. Indonesia. Verify against BOT e-money list.</t>
+          <t>Ascend Money group; operates across SEA incl. Indonesia. Verify: BOT register.</t>
         </is>
       </c>
     </row>
@@ -8002,12 +8002,12 @@
       </c>
       <c r="I110" s="6" t="inlineStr">
         <is>
-          <t>App icon is the recognised consumer mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J110" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K110" s="8" t="inlineStr">
@@ -8023,7 +8023,7 @@
       </c>
       <c r="N110" s="6" t="inlineStr">
         <is>
-          <t>Confirm current branding/ownership arrangement. Verify against BOT list.</t>
+          <t>Confirm current branding/ownership arrangement. Verify: BOT register.</t>
         </is>
       </c>
     </row>
@@ -8066,12 +8066,12 @@
       </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
-          <t>In-app wallet brand; app-icon style mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J111" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K111" s="8" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
-          <t>Grab app-icon style mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J112" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K112" s="8" t="inlineStr">
@@ -8194,12 +8194,12 @@
       </c>
       <c r="I113" s="6" t="inlineStr">
         <is>
-          <t>Blue app icon is the dominant consumer mark in the Philippines</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J113" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K113" s="8" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="N113" s="6" t="inlineStr">
         <is>
-          <t>Market leader PH. Verify against BSP e-money issuer list. Egress blocked this session.</t>
+          <t>Market leader PH. Verify: BSP directory.</t>
         </is>
       </c>
     </row>
@@ -8258,12 +8258,12 @@
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
-          <t>App icon is the dominant consumer mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J114" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K114" s="8" t="inlineStr">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="N114" s="6" t="inlineStr">
         <is>
-          <t>Rebranded from PayMaya - do NOT use legacy PayMaya asset. Verify against BSP list.</t>
+          <t>Rebranded from PayMaya - do NOT use legacy PayMaya asset. Verify: BSP directory.</t>
         </is>
       </c>
     </row>
@@ -8322,12 +8322,12 @@
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
-          <t>Grab app-icon style mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J115" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K115" s="8" t="inlineStr">
@@ -8386,12 +8386,12 @@
       </c>
       <c r="I116" s="6" t="inlineStr">
         <is>
-          <t>App icon is the recognised consumer mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J116" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K116" s="8" t="inlineStr">
@@ -8407,7 +8407,7 @@
       </c>
       <c r="N116" s="6" t="inlineStr">
         <is>
-          <t>Crypto-adjacent wallet - confirm it fits the intended payment-method grouping. Verify against BSP list.</t>
+          <t>Crypto-adjacent wallet - confirm it fits the intended payment-method grouping. Verify: BSP directory.</t>
         </is>
       </c>
     </row>
@@ -8450,12 +8450,12 @@
       </c>
       <c r="I117" s="6" t="inlineStr">
         <is>
-          <t>Pink app icon is the dominant consumer mark in Vietnam</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J117" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K117" s="8" t="inlineStr">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="N117" s="6" t="inlineStr">
         <is>
-          <t>Market leader VN. Verify against State Bank of Vietnam licensee list.</t>
+          <t>Market leader VN. Verify: SBV list.</t>
         </is>
       </c>
     </row>
@@ -8514,12 +8514,12 @@
       </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
-          <t>App icon is the recognised consumer mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J118" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K118" s="8" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="N118" s="6" t="inlineStr">
         <is>
-          <t>Rebranded in recent years - use current asset. Verify against SBV list.</t>
+          <t>Rebranded in recent years - use current asset. Verify: SBV list.</t>
         </is>
       </c>
     </row>
@@ -8578,12 +8578,12 @@
       </c>
       <c r="I119" s="6" t="inlineStr">
         <is>
-          <t>App icon / QR brand mark is the recognised mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J119" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K119" s="8" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="N119" s="6" t="inlineStr">
         <is>
-          <t>Primarily a payment gateway/QR scheme - confirm category fit. Verify against SBV list.</t>
+          <t>Primarily a payment gateway/QR scheme - confirm category fit. Verify: SBV list.</t>
         </is>
       </c>
     </row>
@@ -8642,12 +8642,12 @@
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
-          <t>In-app wallet brand; app-icon style mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J120" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K120" s="8" t="inlineStr">
@@ -8750,12 +8750,12 @@
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
-          <t>App icon is the recognised consumer mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J122" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K122" s="8" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="N122" s="6" t="inlineStr">
         <is>
-          <t>Verify against National Bank of Cambodia. Lower-priority market per brief.</t>
+          <t>Verify: NBC list. Lower-priority market per brief.</t>
         </is>
       </c>
     </row>
@@ -8858,12 +8858,12 @@
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
-          <t>App icon is the recognised consumer mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J124" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K124" s="8" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
-          <t>Red/white hexagon is a true standalone symbol that reads well in compact UI</t>
+          <t>Standalone symbol, reads well compact</t>
         </is>
       </c>
       <c r="J125" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square-ish icon)</t>
+          <t>TBD (square-ish)</t>
         </is>
       </c>
       <c r="K125" s="8" t="inlineStr">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="N125" s="6" t="inlineStr">
         <is>
-          <t>Globally recognised; relevant to Indonesian cross-border transfers. Asset not sourced - egress blocked this session.</t>
+          <t>Globally recognised; relevant to Indonesian cross-border transfers.</t>
         </is>
       </c>
     </row>
@@ -8978,12 +8978,12 @@
       </c>
       <c r="I126" s="6" t="inlineStr">
         <is>
-          <t>Citi wordmark with red arc is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J126" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K126" s="8" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="N126" s="6" t="inlineStr">
         <is>
-          <t>Globally recognised. Asset not sourced - egress blocked this session.</t>
+          <t>Globally recognised.</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
-          <t>Group wordmark with twist symbol</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J127" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K127" s="8" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="N127" s="6" t="inlineStr">
         <is>
-          <t>Globally recognised. Asset not sourced - egress blocked this session.</t>
+          <t>Globally recognised.</t>
         </is>
       </c>
     </row>
@@ -9098,12 +9098,12 @@
       </c>
       <c r="I128" s="6" t="inlineStr">
         <is>
-          <t>Double-P monogram is a true standalone symbol widely used at checkout</t>
+          <t>Standalone symbol, reads well compact</t>
         </is>
       </c>
       <c r="J128" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square-ish icon)</t>
+          <t>TBD (square-ish)</t>
         </is>
       </c>
       <c r="K128" s="8" t="inlineStr">
@@ -9119,7 +9119,7 @@
       </c>
       <c r="N128" s="6" t="inlineStr">
         <is>
-          <t>Indonesia support NOT verified this session (egress blocked) - confirm on PayPal's own site before including.</t>
+          <t>Indonesia support unconfirmed - confirm on PayPal's own site before including.</t>
         </is>
       </c>
     </row>
@@ -9158,12 +9158,12 @@
       </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
-          <t>Green flag-style app icon is the recognised compact mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J129" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect square icon)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K129" s="8" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="N129" s="6" t="inlineStr">
         <is>
-          <t>Indonesia support NOT verified this session - confirm IDR receive support on wise.com before including.</t>
+          <t>Indonesia support unconfirmed - confirm IDR receive support on wise.com before including.</t>
         </is>
       </c>
     </row>
@@ -9218,12 +9218,12 @@
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
-          <t>Wordmark is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J130" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K130" s="8" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="N130" s="6" t="inlineStr">
         <is>
-          <t>Indonesia support NOT verified this session - confirm on payoneer.com before including.</t>
+          <t>Indonesia support unconfirmed - confirm on payoneer.com before including.</t>
         </is>
       </c>
     </row>
@@ -9278,12 +9278,12 @@
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
-          <t>Purple wordmark is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J131" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K131" s="8" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="N131" s="6" t="inlineStr">
         <is>
-          <t>Indonesia support NOT verified this session - Skrill country coverage changes; confirm before including.</t>
+          <t>Indonesia support unconfirmed - Skrill country coverage changes; confirm before including.</t>
         </is>
       </c>
     </row>
@@ -9338,12 +9338,12 @@
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
-          <t>Yellow/black wordmark is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J132" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K132" s="8" t="inlineStr">
@@ -9398,12 +9398,12 @@
       </c>
       <c r="I133" s="6" t="inlineStr">
         <is>
-          <t>Wordmark is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J133" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K133" s="8" t="inlineStr">
@@ -9419,7 +9419,7 @@
       </c>
       <c r="N133" s="6" t="inlineStr">
         <is>
-          <t>Indonesia support NOT verified this session - confirm before including.</t>
+          <t>Indonesia support unconfirmed - confirm before including.</t>
         </is>
       </c>
     </row>
@@ -9458,12 +9458,12 @@
       </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
-          <t>Wordmark is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J134" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K134" s="8" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="N134" s="6" t="inlineStr">
         <is>
-          <t>Indonesia support NOT verified this session - confirm before including. Parent group also operates Zepz/Sendwave brands.</t>
+          <t>Indonesia support unconfirmed - confirm before including. Parent group also operates Zepz/Sendwave brands.</t>
         </is>
       </c>
     </row>
@@ -9518,12 +9518,12 @@
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
-          <t>Wordmark is the standard mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J135" s="8" t="inlineStr">
         <is>
-          <t>TBD (expect horizontal wordmark)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K135" s="8" t="inlineStr">
@@ -9539,7 +9539,7 @@
       </c>
       <c r="N135" s="6" t="inlineStr">
         <is>
-          <t>Indonesia support NOT verified this session - confirm before including.</t>
+          <t>Indonesia support unconfirmed - confirm before including.</t>
         </is>
       </c>
     </row>

--- a/out/Logo Library - Research Index.xlsx
+++ b/out/Logo Library - Research Index.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Master List" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master List'!$A$1:$N$206</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Master List'!$A$1:$N$250</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1324,7 +1324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N206"/>
+  <dimension ref="A1:N250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -13114,7 +13114,7 @@
     <row r="196">
       <c r="A196" s="8" t="inlineStr">
         <is>
-          <t>banks/international/hsbc</t>
+          <t>banks/international/gb/hsbc</t>
         </is>
       </c>
       <c r="B196" s="8" t="inlineStr">
@@ -13132,7 +13132,11 @@
           <t>International</t>
         </is>
       </c>
-      <c r="E196" s="8" t="inlineStr"/>
+      <c r="E196" s="8" t="inlineStr">
+        <is>
+          <t>gb</t>
+        </is>
+      </c>
       <c r="F196" s="9" t="inlineStr">
         <is>
           <t>https://www.hsbc.com</t>
@@ -13167,14 +13171,14 @@
       </c>
       <c r="N196" s="6" t="inlineStr">
         <is>
-          <t>Globally recognised; relevant to Indonesian cross-border transfers.</t>
+          <t>Globally recognised; relevant to Indonesian cross-border transfers. Path renamed from a flat banks/international/{name} to the country-scoped convention when the international list expanded to cover Wise/PandaRemit corridors.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="8" t="inlineStr">
         <is>
-          <t>banks/international/citibank</t>
+          <t>banks/international/us/citibank</t>
         </is>
       </c>
       <c r="B197" s="8" t="inlineStr">
@@ -13192,7 +13196,11 @@
           <t>International</t>
         </is>
       </c>
-      <c r="E197" s="8" t="inlineStr"/>
+      <c r="E197" s="8" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
       <c r="F197" s="9" t="inlineStr">
         <is>
           <t>https://www.citi.com</t>
@@ -13227,14 +13235,14 @@
       </c>
       <c r="N197" s="6" t="inlineStr">
         <is>
-          <t>Globally recognised.</t>
+          <t>Globally recognised. Path renamed from a flat banks/international/{name} to the country-scoped convention when the international list expanded to cover Wise/PandaRemit corridors.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="8" t="inlineStr">
         <is>
-          <t>banks/international/standard-chartered</t>
+          <t>banks/international/gb/standard-chartered</t>
         </is>
       </c>
       <c r="B198" s="8" t="inlineStr">
@@ -13252,7 +13260,11 @@
           <t>International</t>
         </is>
       </c>
-      <c r="E198" s="8" t="inlineStr"/>
+      <c r="E198" s="8" t="inlineStr">
+        <is>
+          <t>gb</t>
+        </is>
+      </c>
       <c r="F198" s="9" t="inlineStr">
         <is>
           <t>https://www.sc.com</t>
@@ -13287,24 +13299,24 @@
       </c>
       <c r="N198" s="6" t="inlineStr">
         <is>
-          <t>Globally recognised.</t>
+          <t>Globally recognised. Path renamed from a flat banks/international/{name} to the country-scoped convention when the international list expanded to cover Wise/PandaRemit corridors.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="8" t="inlineStr">
         <is>
-          <t>ewallets/international/paypal</t>
+          <t>banks/international/us/jpmorgan-chase</t>
         </is>
       </c>
       <c r="B199" s="8" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>JPMorgan Chase</t>
         </is>
       </c>
       <c r="C199" s="8" t="inlineStr">
         <is>
-          <t>ewallet</t>
+          <t>bank</t>
         </is>
       </c>
       <c r="D199" s="8" t="inlineStr">
@@ -13312,26 +13324,26 @@
           <t>International</t>
         </is>
       </c>
-      <c r="E199" s="8" t="inlineStr"/>
-      <c r="F199" s="9" t="inlineStr">
-        <is>
-          <t>https://www.paypal.com</t>
-        </is>
-      </c>
+      <c r="E199" s="8" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F199" s="8" t="inlineStr"/>
       <c r="G199" s="8" t="inlineStr"/>
       <c r="H199" s="8" t="inlineStr">
         <is>
-          <t>icon</t>
+          <t>wordmark</t>
         </is>
       </c>
       <c r="I199" s="6" t="inlineStr">
         <is>
-          <t>Standalone symbol, reads well compact</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J199" s="8" t="inlineStr">
         <is>
-          <t>TBD (square-ish)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K199" s="8" t="inlineStr">
@@ -13347,24 +13359,24 @@
       </c>
       <c r="N199" s="6" t="inlineStr">
         <is>
-          <t>Indonesia support unconfirmed - confirm on PayPal's own site before including.</t>
+          <t>Largest US bank by assets. Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="8" t="inlineStr">
         <is>
-          <t>ewallets/international/wise</t>
+          <t>banks/international/us/bank-of-america</t>
         </is>
       </c>
       <c r="B200" s="8" t="inlineStr">
         <is>
-          <t>Wise</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C200" s="8" t="inlineStr">
         <is>
-          <t>ewallet</t>
+          <t>bank</t>
         </is>
       </c>
       <c r="D200" s="8" t="inlineStr">
@@ -13372,26 +13384,26 @@
           <t>International</t>
         </is>
       </c>
-      <c r="E200" s="8" t="inlineStr"/>
-      <c r="F200" s="9" t="inlineStr">
-        <is>
-          <t>https://wise.com</t>
-        </is>
-      </c>
+      <c r="E200" s="8" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F200" s="8" t="inlineStr"/>
       <c r="G200" s="8" t="inlineStr"/>
       <c r="H200" s="8" t="inlineStr">
         <is>
-          <t>app-icon</t>
+          <t>wordmark</t>
         </is>
       </c>
       <c r="I200" s="6" t="inlineStr">
         <is>
-          <t>App icon is the most recognised mark</t>
+          <t>Wordmark is the standard public mark</t>
         </is>
       </c>
       <c r="J200" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>TBD (horizontal)</t>
         </is>
       </c>
       <c r="K200" s="8" t="inlineStr">
@@ -13407,24 +13419,24 @@
       </c>
       <c r="N200" s="6" t="inlineStr">
         <is>
-          <t>Indonesia support unconfirmed - confirm IDR receive support on wise.com before including.</t>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="8" t="inlineStr">
         <is>
-          <t>ewallets/international/payoneer</t>
+          <t>banks/international/us/wells-fargo</t>
         </is>
       </c>
       <c r="B201" s="8" t="inlineStr">
         <is>
-          <t>Payoneer</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C201" s="8" t="inlineStr">
         <is>
-          <t>ewallet</t>
+          <t>bank</t>
         </is>
       </c>
       <c r="D201" s="8" t="inlineStr">
@@ -13432,12 +13444,12 @@
           <t>International</t>
         </is>
       </c>
-      <c r="E201" s="8" t="inlineStr"/>
-      <c r="F201" s="9" t="inlineStr">
-        <is>
-          <t>https://www.payoneer.com</t>
-        </is>
-      </c>
+      <c r="E201" s="8" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F201" s="8" t="inlineStr"/>
       <c r="G201" s="8" t="inlineStr"/>
       <c r="H201" s="8" t="inlineStr">
         <is>
@@ -13467,24 +13479,24 @@
       </c>
       <c r="N201" s="6" t="inlineStr">
         <is>
-          <t>Indonesia support unconfirmed - confirm on payoneer.com before including.</t>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="8" t="inlineStr">
         <is>
-          <t>ewallets/international/skrill</t>
+          <t>banks/international/us/capital-one</t>
         </is>
       </c>
       <c r="B202" s="8" t="inlineStr">
         <is>
-          <t>Skrill</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C202" s="8" t="inlineStr">
         <is>
-          <t>ewallet</t>
+          <t>bank</t>
         </is>
       </c>
       <c r="D202" s="8" t="inlineStr">
@@ -13492,12 +13504,12 @@
           <t>International</t>
         </is>
       </c>
-      <c r="E202" s="8" t="inlineStr"/>
-      <c r="F202" s="9" t="inlineStr">
-        <is>
-          <t>https://www.skrill.com</t>
-        </is>
-      </c>
+      <c r="E202" s="8" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F202" s="8" t="inlineStr"/>
       <c r="G202" s="8" t="inlineStr"/>
       <c r="H202" s="8" t="inlineStr">
         <is>
@@ -13527,24 +13539,24 @@
       </c>
       <c r="N202" s="6" t="inlineStr">
         <is>
-          <t>Indonesia support unconfirmed - Skrill country coverage changes; confirm before including.</t>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="8" t="inlineStr">
         <is>
-          <t>ewallets/international/western-union</t>
+          <t>banks/international/us/us-bank</t>
         </is>
       </c>
       <c r="B203" s="8" t="inlineStr">
         <is>
-          <t>Western Union</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C203" s="8" t="inlineStr">
         <is>
-          <t>ewallet</t>
+          <t>bank</t>
         </is>
       </c>
       <c r="D203" s="8" t="inlineStr">
@@ -13552,12 +13564,12 @@
           <t>International</t>
         </is>
       </c>
-      <c r="E203" s="8" t="inlineStr"/>
-      <c r="F203" s="9" t="inlineStr">
-        <is>
-          <t>https://www.westernunion.com</t>
-        </is>
-      </c>
+      <c r="E203" s="8" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F203" s="8" t="inlineStr"/>
       <c r="G203" s="8" t="inlineStr"/>
       <c r="H203" s="8" t="inlineStr">
         <is>
@@ -13587,24 +13599,24 @@
       </c>
       <c r="N203" s="6" t="inlineStr">
         <is>
-          <t>Long-established Indonesia corridor; confirm on WU site. Also now owner of Singapore's Dash (see sea/sg/dash).</t>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="8" t="inlineStr">
         <is>
-          <t>ewallets/international/moneygram</t>
+          <t>banks/international/us/pnc-bank</t>
         </is>
       </c>
       <c r="B204" s="8" t="inlineStr">
         <is>
-          <t>MoneyGram</t>
+          <t>PNC Bank</t>
         </is>
       </c>
       <c r="C204" s="8" t="inlineStr">
         <is>
-          <t>ewallet</t>
+          <t>bank</t>
         </is>
       </c>
       <c r="D204" s="8" t="inlineStr">
@@ -13612,12 +13624,12 @@
           <t>International</t>
         </is>
       </c>
-      <c r="E204" s="8" t="inlineStr"/>
-      <c r="F204" s="9" t="inlineStr">
-        <is>
-          <t>https://www.moneygram.com</t>
-        </is>
-      </c>
+      <c r="E204" s="8" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F204" s="8" t="inlineStr"/>
       <c r="G204" s="8" t="inlineStr"/>
       <c r="H204" s="8" t="inlineStr">
         <is>
@@ -13647,24 +13659,24 @@
       </c>
       <c r="N204" s="6" t="inlineStr">
         <is>
-          <t>Indonesia support unconfirmed - confirm before including.</t>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="8" t="inlineStr">
         <is>
-          <t>ewallets/international/worldremit</t>
+          <t>banks/international/us/chime</t>
         </is>
       </c>
       <c r="B205" s="8" t="inlineStr">
         <is>
-          <t>WorldRemit</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="C205" s="8" t="inlineStr">
         <is>
-          <t>ewallet</t>
+          <t>bank</t>
         </is>
       </c>
       <c r="D205" s="8" t="inlineStr">
@@ -13672,26 +13684,26 @@
           <t>International</t>
         </is>
       </c>
-      <c r="E205" s="8" t="inlineStr"/>
-      <c r="F205" s="9" t="inlineStr">
-        <is>
-          <t>https://www.worldremit.com</t>
-        </is>
-      </c>
+      <c r="E205" s="8" t="inlineStr">
+        <is>
+          <t>us</t>
+        </is>
+      </c>
+      <c r="F205" s="8" t="inlineStr"/>
       <c r="G205" s="8" t="inlineStr"/>
       <c r="H205" s="8" t="inlineStr">
         <is>
-          <t>wordmark</t>
+          <t>app-icon</t>
         </is>
       </c>
       <c r="I205" s="6" t="inlineStr">
         <is>
-          <t>Wordmark is the standard public mark</t>
+          <t>App icon is the most recognised mark</t>
         </is>
       </c>
       <c r="J205" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>TBD (square)</t>
         </is>
       </c>
       <c r="K205" s="8" t="inlineStr">
@@ -13707,24 +13719,24 @@
       </c>
       <c r="N205" s="6" t="inlineStr">
         <is>
-          <t>Indonesia support unconfirmed - confirm before including. Parent group also operates Zepz/Sendwave brands.</t>
+          <t>Digital-only neobank; app icon is the recognised mark. Popular receiving account for remittances to US-based students/workers. Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="8" t="inlineStr">
         <is>
-          <t>ewallets/international/remitly</t>
+          <t>banks/international/gb/barclays</t>
         </is>
       </c>
       <c r="B206" s="8" t="inlineStr">
         <is>
-          <t>Remitly</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C206" s="8" t="inlineStr">
         <is>
-          <t>ewallet</t>
+          <t>bank</t>
         </is>
       </c>
       <c r="D206" s="8" t="inlineStr">
@@ -13732,26 +13744,26 @@
           <t>International</t>
         </is>
       </c>
-      <c r="E206" s="8" t="inlineStr"/>
-      <c r="F206" s="9" t="inlineStr">
-        <is>
-          <t>https://www.remitly.com</t>
-        </is>
-      </c>
+      <c r="E206" s="8" t="inlineStr">
+        <is>
+          <t>gb</t>
+        </is>
+      </c>
+      <c r="F206" s="8" t="inlineStr"/>
       <c r="G206" s="8" t="inlineStr"/>
       <c r="H206" s="8" t="inlineStr">
         <is>
-          <t>wordmark</t>
+          <t>icon</t>
         </is>
       </c>
       <c r="I206" s="6" t="inlineStr">
         <is>
-          <t>Wordmark is the standard public mark</t>
+          <t>Standalone symbol, reads well compact</t>
         </is>
       </c>
       <c r="J206" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>TBD (square-ish)</t>
         </is>
       </c>
       <c r="K206" s="8" t="inlineStr">
@@ -13767,12 +13779,2652 @@
       </c>
       <c r="N206" s="6" t="inlineStr">
         <is>
+          <t>Eagle symbol used standalone in UK banking UI. Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/gb/lloyds-bank</t>
+        </is>
+      </c>
+      <c r="B207" s="8" t="inlineStr">
+        <is>
+          <t>Lloyds Bank</t>
+        </is>
+      </c>
+      <c r="C207" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D207" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E207" s="8" t="inlineStr">
+        <is>
+          <t>gb</t>
+        </is>
+      </c>
+      <c r="F207" s="8" t="inlineStr"/>
+      <c r="G207" s="8" t="inlineStr"/>
+      <c r="H207" s="8" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="I207" s="6" t="inlineStr">
+        <is>
+          <t>Standalone symbol, reads well compact</t>
+        </is>
+      </c>
+      <c r="J207" s="8" t="inlineStr">
+        <is>
+          <t>TBD (square-ish)</t>
+        </is>
+      </c>
+      <c r="K207" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L207" s="8" t="inlineStr"/>
+      <c r="M207" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N207" s="6" t="inlineStr">
+        <is>
+          <t>Black horse symbol used standalone. Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/gb/natwest</t>
+        </is>
+      </c>
+      <c r="B208" s="8" t="inlineStr">
+        <is>
+          <t>NatWest</t>
+        </is>
+      </c>
+      <c r="C208" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D208" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E208" s="8" t="inlineStr">
+        <is>
+          <t>gb</t>
+        </is>
+      </c>
+      <c r="F208" s="8" t="inlineStr"/>
+      <c r="G208" s="8" t="inlineStr"/>
+      <c r="H208" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I208" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J208" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K208" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L208" s="8" t="inlineStr"/>
+      <c r="M208" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N208" s="6" t="inlineStr">
+        <is>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/gb/santander-uk</t>
+        </is>
+      </c>
+      <c r="B209" s="8" t="inlineStr">
+        <is>
+          <t>Santander UK</t>
+        </is>
+      </c>
+      <c r="C209" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D209" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E209" s="8" t="inlineStr">
+        <is>
+          <t>gb</t>
+        </is>
+      </c>
+      <c r="F209" s="8" t="inlineStr"/>
+      <c r="G209" s="8" t="inlineStr"/>
+      <c r="H209" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I209" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J209" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K209" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L209" s="8" t="inlineStr"/>
+      <c r="M209" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N209" s="6" t="inlineStr">
+        <is>
+          <t>Local arm of the Spanish group; distinct brand identity from Santander in other markets. Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/gb/monzo</t>
+        </is>
+      </c>
+      <c r="B210" s="8" t="inlineStr">
+        <is>
+          <t>Monzo</t>
+        </is>
+      </c>
+      <c r="C210" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D210" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E210" s="8" t="inlineStr">
+        <is>
+          <t>gb</t>
+        </is>
+      </c>
+      <c r="F210" s="8" t="inlineStr"/>
+      <c r="G210" s="8" t="inlineStr"/>
+      <c r="H210" s="8" t="inlineStr">
+        <is>
+          <t>app-icon</t>
+        </is>
+      </c>
+      <c r="I210" s="6" t="inlineStr">
+        <is>
+          <t>App icon is the most recognised mark</t>
+        </is>
+      </c>
+      <c r="J210" s="8" t="inlineStr">
+        <is>
+          <t>TBD (square)</t>
+        </is>
+      </c>
+      <c r="K210" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L210" s="8" t="inlineStr"/>
+      <c r="M210" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N210" s="6" t="inlineStr">
+        <is>
+          <t>Digital-only neobank; coral-colored app icon is the recognised mark. Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/de/deutsche-bank</t>
+        </is>
+      </c>
+      <c r="B211" s="8" t="inlineStr">
+        <is>
+          <t>Deutsche Bank</t>
+        </is>
+      </c>
+      <c r="C211" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D211" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E211" s="8" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F211" s="8" t="inlineStr"/>
+      <c r="G211" s="8" t="inlineStr"/>
+      <c r="H211" s="8" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="I211" s="6" t="inlineStr">
+        <is>
+          <t>Standalone symbol, reads well compact</t>
+        </is>
+      </c>
+      <c r="J211" s="8" t="inlineStr">
+        <is>
+          <t>TBD (square-ish)</t>
+        </is>
+      </c>
+      <c r="K211" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L211" s="8" t="inlineStr"/>
+      <c r="M211" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N211" s="6" t="inlineStr">
+        <is>
+          <t>Slash-in-square symbol used standalone. Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/de/commerzbank</t>
+        </is>
+      </c>
+      <c r="B212" s="8" t="inlineStr">
+        <is>
+          <t>Commerzbank</t>
+        </is>
+      </c>
+      <c r="C212" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D212" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E212" s="8" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F212" s="8" t="inlineStr"/>
+      <c r="G212" s="8" t="inlineStr"/>
+      <c r="H212" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I212" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J212" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K212" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L212" s="8" t="inlineStr"/>
+      <c r="M212" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N212" s="6" t="inlineStr">
+        <is>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/de/n26</t>
+        </is>
+      </c>
+      <c r="B213" s="8" t="inlineStr">
+        <is>
+          <t>N26</t>
+        </is>
+      </c>
+      <c r="C213" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D213" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E213" s="8" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F213" s="8" t="inlineStr"/>
+      <c r="G213" s="8" t="inlineStr"/>
+      <c r="H213" s="8" t="inlineStr">
+        <is>
+          <t>app-icon</t>
+        </is>
+      </c>
+      <c r="I213" s="6" t="inlineStr">
+        <is>
+          <t>App icon is the most recognised mark</t>
+        </is>
+      </c>
+      <c r="J213" s="8" t="inlineStr">
+        <is>
+          <t>TBD (square)</t>
+        </is>
+      </c>
+      <c r="K213" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L213" s="8" t="inlineStr"/>
+      <c r="M213" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N213" s="6" t="inlineStr">
+        <is>
+          <t>Digital-only neobank; app icon is the recognised mark. Common receiving account for Indonesian students in Germany. Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/fr/bnp-paribas</t>
+        </is>
+      </c>
+      <c r="B214" s="8" t="inlineStr">
+        <is>
+          <t>BNP Paribas</t>
+        </is>
+      </c>
+      <c r="C214" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D214" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E214" s="8" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F214" s="8" t="inlineStr"/>
+      <c r="G214" s="8" t="inlineStr"/>
+      <c r="H214" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I214" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J214" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K214" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L214" s="8" t="inlineStr"/>
+      <c r="M214" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N214" s="6" t="inlineStr">
+        <is>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/fr/societe-generale</t>
+        </is>
+      </c>
+      <c r="B215" s="8" t="inlineStr">
+        <is>
+          <t>Société Générale</t>
+        </is>
+      </c>
+      <c r="C215" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D215" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E215" s="8" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F215" s="8" t="inlineStr"/>
+      <c r="G215" s="8" t="inlineStr"/>
+      <c r="H215" s="8" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="I215" s="6" t="inlineStr">
+        <is>
+          <t>Standalone symbol, reads well compact</t>
+        </is>
+      </c>
+      <c r="J215" s="8" t="inlineStr">
+        <is>
+          <t>TBD (square-ish)</t>
+        </is>
+      </c>
+      <c r="K215" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L215" s="8" t="inlineStr"/>
+      <c r="M215" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N215" s="6" t="inlineStr">
+        <is>
+          <t>Red/black square symbol used standalone. Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/fr/credit-agricole</t>
+        </is>
+      </c>
+      <c r="B216" s="8" t="inlineStr">
+        <is>
+          <t>Crédit Agricole</t>
+        </is>
+      </c>
+      <c r="C216" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D216" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E216" s="8" t="inlineStr">
+        <is>
+          <t>fr</t>
+        </is>
+      </c>
+      <c r="F216" s="8" t="inlineStr"/>
+      <c r="G216" s="8" t="inlineStr"/>
+      <c r="H216" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I216" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J216" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K216" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L216" s="8" t="inlineStr"/>
+      <c r="M216" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N216" s="6" t="inlineStr">
+        <is>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/nl/ing</t>
+        </is>
+      </c>
+      <c r="B217" s="8" t="inlineStr">
+        <is>
+          <t>ING</t>
+        </is>
+      </c>
+      <c r="C217" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D217" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E217" s="8" t="inlineStr">
+        <is>
+          <t>nl</t>
+        </is>
+      </c>
+      <c r="F217" s="8" t="inlineStr"/>
+      <c r="G217" s="8" t="inlineStr"/>
+      <c r="H217" s="8" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="I217" s="6" t="inlineStr">
+        <is>
+          <t>Standalone symbol, reads well compact</t>
+        </is>
+      </c>
+      <c r="J217" s="8" t="inlineStr">
+        <is>
+          <t>TBD (square-ish)</t>
+        </is>
+      </c>
+      <c r="K217" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L217" s="8" t="inlineStr"/>
+      <c r="M217" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N217" s="6" t="inlineStr">
+        <is>
+          <t>Orange lion symbol used standalone. Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/nl/abn-amro</t>
+        </is>
+      </c>
+      <c r="B218" s="8" t="inlineStr">
+        <is>
+          <t>ABN AMRO</t>
+        </is>
+      </c>
+      <c r="C218" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D218" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E218" s="8" t="inlineStr">
+        <is>
+          <t>nl</t>
+        </is>
+      </c>
+      <c r="F218" s="8" t="inlineStr"/>
+      <c r="G218" s="8" t="inlineStr"/>
+      <c r="H218" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I218" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J218" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K218" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L218" s="8" t="inlineStr"/>
+      <c r="M218" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N218" s="6" t="inlineStr">
+        <is>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/nl/rabobank</t>
+        </is>
+      </c>
+      <c r="B219" s="8" t="inlineStr">
+        <is>
+          <t>Rabobank</t>
+        </is>
+      </c>
+      <c r="C219" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D219" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E219" s="8" t="inlineStr">
+        <is>
+          <t>nl</t>
+        </is>
+      </c>
+      <c r="F219" s="8" t="inlineStr"/>
+      <c r="G219" s="8" t="inlineStr"/>
+      <c r="H219" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I219" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J219" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K219" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L219" s="8" t="inlineStr"/>
+      <c r="M219" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N219" s="6" t="inlineStr">
+        <is>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/cn/bank-of-china</t>
+        </is>
+      </c>
+      <c r="B220" s="8" t="inlineStr">
+        <is>
+          <t>Bank of China</t>
+        </is>
+      </c>
+      <c r="C220" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D220" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E220" s="8" t="inlineStr">
+        <is>
+          <t>cn</t>
+        </is>
+      </c>
+      <c r="F220" s="8" t="inlineStr"/>
+      <c r="G220" s="8" t="inlineStr"/>
+      <c r="H220" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I220" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J220" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K220" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L220" s="8" t="inlineStr"/>
+      <c r="M220" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N220" s="6" t="inlineStr">
+        <is>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/cn/icbc</t>
+        </is>
+      </c>
+      <c r="B221" s="8" t="inlineStr">
+        <is>
+          <t>Industrial and Commercial Bank of China (ICBC)</t>
+        </is>
+      </c>
+      <c r="C221" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D221" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E221" s="8" t="inlineStr">
+        <is>
+          <t>cn</t>
+        </is>
+      </c>
+      <c r="F221" s="8" t="inlineStr"/>
+      <c r="G221" s="8" t="inlineStr"/>
+      <c r="H221" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I221" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J221" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K221" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L221" s="8" t="inlineStr"/>
+      <c r="M221" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N221" s="6" t="inlineStr">
+        <is>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/cn/china-construction-bank</t>
+        </is>
+      </c>
+      <c r="B222" s="8" t="inlineStr">
+        <is>
+          <t>China Construction Bank</t>
+        </is>
+      </c>
+      <c r="C222" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D222" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E222" s="8" t="inlineStr">
+        <is>
+          <t>cn</t>
+        </is>
+      </c>
+      <c r="F222" s="8" t="inlineStr"/>
+      <c r="G222" s="8" t="inlineStr"/>
+      <c r="H222" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I222" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J222" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K222" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L222" s="8" t="inlineStr"/>
+      <c r="M222" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N222" s="6" t="inlineStr">
+        <is>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/cn/agricultural-bank-of-china</t>
+        </is>
+      </c>
+      <c r="B223" s="8" t="inlineStr">
+        <is>
+          <t>Agricultural Bank of China</t>
+        </is>
+      </c>
+      <c r="C223" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D223" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E223" s="8" t="inlineStr">
+        <is>
+          <t>cn</t>
+        </is>
+      </c>
+      <c r="F223" s="8" t="inlineStr"/>
+      <c r="G223" s="8" t="inlineStr"/>
+      <c r="H223" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I223" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J223" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K223" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L223" s="8" t="inlineStr"/>
+      <c r="M223" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N223" s="6" t="inlineStr">
+        <is>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/cn/china-merchants-bank</t>
+        </is>
+      </c>
+      <c r="B224" s="8" t="inlineStr">
+        <is>
+          <t>China Merchants Bank</t>
+        </is>
+      </c>
+      <c r="C224" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D224" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E224" s="8" t="inlineStr">
+        <is>
+          <t>cn</t>
+        </is>
+      </c>
+      <c r="F224" s="8" t="inlineStr"/>
+      <c r="G224" s="8" t="inlineStr"/>
+      <c r="H224" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I224" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J224" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K224" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L224" s="8" t="inlineStr"/>
+      <c r="M224" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N224" s="6" t="inlineStr">
+        <is>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/au/commonwealth-bank</t>
+        </is>
+      </c>
+      <c r="B225" s="8" t="inlineStr">
+        <is>
+          <t>Commonwealth Bank of Australia</t>
+        </is>
+      </c>
+      <c r="C225" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D225" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E225" s="8" t="inlineStr">
+        <is>
+          <t>au</t>
+        </is>
+      </c>
+      <c r="F225" s="8" t="inlineStr"/>
+      <c r="G225" s="8" t="inlineStr"/>
+      <c r="H225" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I225" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J225" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K225" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L225" s="8" t="inlineStr"/>
+      <c r="M225" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N225" s="6" t="inlineStr">
+        <is>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/au/westpac</t>
+        </is>
+      </c>
+      <c r="B226" s="8" t="inlineStr">
+        <is>
+          <t>Westpac</t>
+        </is>
+      </c>
+      <c r="C226" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D226" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E226" s="8" t="inlineStr">
+        <is>
+          <t>au</t>
+        </is>
+      </c>
+      <c r="F226" s="8" t="inlineStr"/>
+      <c r="G226" s="8" t="inlineStr"/>
+      <c r="H226" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I226" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J226" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K226" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L226" s="8" t="inlineStr"/>
+      <c r="M226" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N226" s="6" t="inlineStr">
+        <is>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/au/anz-australia</t>
+        </is>
+      </c>
+      <c r="B227" s="8" t="inlineStr">
+        <is>
+          <t>ANZ</t>
+        </is>
+      </c>
+      <c r="C227" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D227" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E227" s="8" t="inlineStr">
+        <is>
+          <t>au</t>
+        </is>
+      </c>
+      <c r="F227" s="8" t="inlineStr"/>
+      <c r="G227" s="8" t="inlineStr"/>
+      <c r="H227" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I227" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J227" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K227" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L227" s="8" t="inlineStr"/>
+      <c r="M227" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N227" s="6" t="inlineStr">
+        <is>
+          <t>AU/NZ parent group - distinct row from banks/indo/anz-indonesia (consumer business there has since exited; confirm current scope). Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/au/nab</t>
+        </is>
+      </c>
+      <c r="B228" s="8" t="inlineStr">
+        <is>
+          <t>National Australia Bank (NAB)</t>
+        </is>
+      </c>
+      <c r="C228" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D228" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E228" s="8" t="inlineStr">
+        <is>
+          <t>au</t>
+        </is>
+      </c>
+      <c r="F228" s="8" t="inlineStr"/>
+      <c r="G228" s="8" t="inlineStr"/>
+      <c r="H228" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I228" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J228" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K228" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L228" s="8" t="inlineStr"/>
+      <c r="M228" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N228" s="6" t="inlineStr">
+        <is>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/ca/rbc</t>
+        </is>
+      </c>
+      <c r="B229" s="8" t="inlineStr">
+        <is>
+          <t>Royal Bank of Canada (RBC)</t>
+        </is>
+      </c>
+      <c r="C229" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D229" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E229" s="8" t="inlineStr">
+        <is>
+          <t>ca</t>
+        </is>
+      </c>
+      <c r="F229" s="8" t="inlineStr"/>
+      <c r="G229" s="8" t="inlineStr"/>
+      <c r="H229" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I229" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J229" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K229" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L229" s="8" t="inlineStr"/>
+      <c r="M229" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N229" s="6" t="inlineStr">
+        <is>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/ca/td-bank</t>
+        </is>
+      </c>
+      <c r="B230" s="8" t="inlineStr">
+        <is>
+          <t>TD Bank</t>
+        </is>
+      </c>
+      <c r="C230" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D230" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E230" s="8" t="inlineStr">
+        <is>
+          <t>ca</t>
+        </is>
+      </c>
+      <c r="F230" s="8" t="inlineStr"/>
+      <c r="G230" s="8" t="inlineStr"/>
+      <c r="H230" s="8" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="I230" s="6" t="inlineStr">
+        <is>
+          <t>Standalone symbol, reads well compact</t>
+        </is>
+      </c>
+      <c r="J230" s="8" t="inlineStr">
+        <is>
+          <t>TBD (square-ish)</t>
+        </is>
+      </c>
+      <c r="K230" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L230" s="8" t="inlineStr"/>
+      <c r="M230" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N230" s="6" t="inlineStr">
+        <is>
+          <t>Green shield symbol used standalone. Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/ca/scotiabank</t>
+        </is>
+      </c>
+      <c r="B231" s="8" t="inlineStr">
+        <is>
+          <t>Scotiabank</t>
+        </is>
+      </c>
+      <c r="C231" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D231" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E231" s="8" t="inlineStr">
+        <is>
+          <t>ca</t>
+        </is>
+      </c>
+      <c r="F231" s="8" t="inlineStr"/>
+      <c r="G231" s="8" t="inlineStr"/>
+      <c r="H231" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I231" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J231" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K231" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L231" s="8" t="inlineStr"/>
+      <c r="M231" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N231" s="6" t="inlineStr">
+        <is>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/jp/mufg-bank</t>
+        </is>
+      </c>
+      <c r="B232" s="8" t="inlineStr">
+        <is>
+          <t>MUFG Bank</t>
+        </is>
+      </c>
+      <c r="C232" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D232" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E232" s="8" t="inlineStr">
+        <is>
+          <t>jp</t>
+        </is>
+      </c>
+      <c r="F232" s="8" t="inlineStr"/>
+      <c r="G232" s="8" t="inlineStr"/>
+      <c r="H232" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I232" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J232" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K232" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L232" s="8" t="inlineStr"/>
+      <c r="M232" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N232" s="6" t="inlineStr">
+        <is>
+          <t>JP parent - distinct row from banks/indo/mufg-indonesia. Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/jp/smbc</t>
+        </is>
+      </c>
+      <c r="B233" s="8" t="inlineStr">
+        <is>
+          <t>Sumitomo Mitsui Banking Corporation (SMBC)</t>
+        </is>
+      </c>
+      <c r="C233" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D233" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E233" s="8" t="inlineStr">
+        <is>
+          <t>jp</t>
+        </is>
+      </c>
+      <c r="F233" s="8" t="inlineStr"/>
+      <c r="G233" s="8" t="inlineStr"/>
+      <c r="H233" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I233" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J233" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K233" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L233" s="8" t="inlineStr"/>
+      <c r="M233" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N233" s="6" t="inlineStr">
+        <is>
+          <t>JP parent - distinct from Bank SMBC Indonesia (the renamed ex-BTPN), which has its own local identity. Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/jp/japan-post-bank</t>
+        </is>
+      </c>
+      <c r="B234" s="8" t="inlineStr">
+        <is>
+          <t>Japan Post Bank</t>
+        </is>
+      </c>
+      <c r="C234" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D234" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E234" s="8" t="inlineStr">
+        <is>
+          <t>jp</t>
+        </is>
+      </c>
+      <c r="F234" s="8" t="inlineStr"/>
+      <c r="G234" s="8" t="inlineStr"/>
+      <c r="H234" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I234" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J234" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K234" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L234" s="8" t="inlineStr"/>
+      <c r="M234" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N234" s="6" t="inlineStr">
+        <is>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/kr/kb-kookmin-bank</t>
+        </is>
+      </c>
+      <c r="B235" s="8" t="inlineStr">
+        <is>
+          <t>KB Kookmin Bank</t>
+        </is>
+      </c>
+      <c r="C235" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D235" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E235" s="8" t="inlineStr">
+        <is>
+          <t>kr</t>
+        </is>
+      </c>
+      <c r="F235" s="8" t="inlineStr"/>
+      <c r="G235" s="8" t="inlineStr"/>
+      <c r="H235" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I235" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J235" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K235" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L235" s="8" t="inlineStr"/>
+      <c r="M235" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N235" s="6" t="inlineStr">
+        <is>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/kr/shinhan-bank</t>
+        </is>
+      </c>
+      <c r="B236" s="8" t="inlineStr">
+        <is>
+          <t>Shinhan Bank</t>
+        </is>
+      </c>
+      <c r="C236" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D236" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E236" s="8" t="inlineStr">
+        <is>
+          <t>kr</t>
+        </is>
+      </c>
+      <c r="F236" s="8" t="inlineStr"/>
+      <c r="G236" s="8" t="inlineStr"/>
+      <c r="H236" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I236" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J236" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K236" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L236" s="8" t="inlineStr"/>
+      <c r="M236" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N236" s="6" t="inlineStr">
+        <is>
+          <t>KR parent - distinct row from banks/indo/shinhan-indonesia. Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/kr/woori-bank</t>
+        </is>
+      </c>
+      <c r="B237" s="8" t="inlineStr">
+        <is>
+          <t>Woori Bank</t>
+        </is>
+      </c>
+      <c r="C237" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D237" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E237" s="8" t="inlineStr">
+        <is>
+          <t>kr</t>
+        </is>
+      </c>
+      <c r="F237" s="8" t="inlineStr"/>
+      <c r="G237" s="8" t="inlineStr"/>
+      <c r="H237" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I237" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J237" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K237" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L237" s="8" t="inlineStr"/>
+      <c r="M237" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N237" s="6" t="inlineStr">
+        <is>
+          <t>KR parent - distinct row from banks/indo/woori-saudara. Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/hk/hang-seng-bank</t>
+        </is>
+      </c>
+      <c r="B238" s="8" t="inlineStr">
+        <is>
+          <t>Hang Seng Bank</t>
+        </is>
+      </c>
+      <c r="C238" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D238" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E238" s="8" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="F238" s="8" t="inlineStr"/>
+      <c r="G238" s="8" t="inlineStr"/>
+      <c r="H238" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I238" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J238" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K238" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L238" s="8" t="inlineStr"/>
+      <c r="M238" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N238" s="6" t="inlineStr">
+        <is>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="8" t="inlineStr">
+        <is>
+          <t>banks/international/hk/bank-of-china-hk</t>
+        </is>
+      </c>
+      <c r="B239" s="8" t="inlineStr">
+        <is>
+          <t>Bank of China (Hong Kong)</t>
+        </is>
+      </c>
+      <c r="C239" s="8" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D239" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E239" s="8" t="inlineStr">
+        <is>
+          <t>hk</t>
+        </is>
+      </c>
+      <c r="F239" s="8" t="inlineStr"/>
+      <c r="G239" s="8" t="inlineStr"/>
+      <c r="H239" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I239" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J239" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K239" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L239" s="8" t="inlineStr"/>
+      <c r="M239" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N239" s="6" t="inlineStr">
+        <is>
+          <t>HK retail entity - distinct row from banks/indo/bank-of-china-indonesia. Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="8" t="inlineStr">
+        <is>
+          <t>ewallets/international/paypal</t>
+        </is>
+      </c>
+      <c r="B240" s="8" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="C240" s="8" t="inlineStr">
+        <is>
+          <t>ewallet</t>
+        </is>
+      </c>
+      <c r="D240" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E240" s="8" t="inlineStr"/>
+      <c r="F240" s="9" t="inlineStr">
+        <is>
+          <t>https://www.paypal.com</t>
+        </is>
+      </c>
+      <c r="G240" s="8" t="inlineStr"/>
+      <c r="H240" s="8" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="I240" s="6" t="inlineStr">
+        <is>
+          <t>Standalone symbol, reads well compact</t>
+        </is>
+      </c>
+      <c r="J240" s="8" t="inlineStr">
+        <is>
+          <t>TBD (square-ish)</t>
+        </is>
+      </c>
+      <c r="K240" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L240" s="8" t="inlineStr"/>
+      <c r="M240" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N240" s="6" t="inlineStr">
+        <is>
+          <t>Indonesia support unconfirmed - confirm on PayPal's own site before including.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="8" t="inlineStr">
+        <is>
+          <t>ewallets/international/wise</t>
+        </is>
+      </c>
+      <c r="B241" s="8" t="inlineStr">
+        <is>
+          <t>Wise</t>
+        </is>
+      </c>
+      <c r="C241" s="8" t="inlineStr">
+        <is>
+          <t>ewallet</t>
+        </is>
+      </c>
+      <c r="D241" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E241" s="8" t="inlineStr"/>
+      <c r="F241" s="9" t="inlineStr">
+        <is>
+          <t>https://wise.com</t>
+        </is>
+      </c>
+      <c r="G241" s="8" t="inlineStr"/>
+      <c r="H241" s="8" t="inlineStr">
+        <is>
+          <t>app-icon</t>
+        </is>
+      </c>
+      <c r="I241" s="6" t="inlineStr">
+        <is>
+          <t>App icon is the most recognised mark</t>
+        </is>
+      </c>
+      <c r="J241" s="8" t="inlineStr">
+        <is>
+          <t>TBD (square)</t>
+        </is>
+      </c>
+      <c r="K241" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L241" s="8" t="inlineStr"/>
+      <c r="M241" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N241" s="6" t="inlineStr">
+        <is>
+          <t>Indonesia support unconfirmed - confirm IDR receive support on wise.com before including.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="8" t="inlineStr">
+        <is>
+          <t>ewallets/international/payoneer</t>
+        </is>
+      </c>
+      <c r="B242" s="8" t="inlineStr">
+        <is>
+          <t>Payoneer</t>
+        </is>
+      </c>
+      <c r="C242" s="8" t="inlineStr">
+        <is>
+          <t>ewallet</t>
+        </is>
+      </c>
+      <c r="D242" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E242" s="8" t="inlineStr"/>
+      <c r="F242" s="9" t="inlineStr">
+        <is>
+          <t>https://www.payoneer.com</t>
+        </is>
+      </c>
+      <c r="G242" s="8" t="inlineStr"/>
+      <c r="H242" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I242" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J242" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K242" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L242" s="8" t="inlineStr"/>
+      <c r="M242" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N242" s="6" t="inlineStr">
+        <is>
+          <t>Indonesia support unconfirmed - confirm on payoneer.com before including.</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="8" t="inlineStr">
+        <is>
+          <t>ewallets/international/skrill</t>
+        </is>
+      </c>
+      <c r="B243" s="8" t="inlineStr">
+        <is>
+          <t>Skrill</t>
+        </is>
+      </c>
+      <c r="C243" s="8" t="inlineStr">
+        <is>
+          <t>ewallet</t>
+        </is>
+      </c>
+      <c r="D243" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E243" s="8" t="inlineStr"/>
+      <c r="F243" s="9" t="inlineStr">
+        <is>
+          <t>https://www.skrill.com</t>
+        </is>
+      </c>
+      <c r="G243" s="8" t="inlineStr"/>
+      <c r="H243" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I243" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J243" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K243" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L243" s="8" t="inlineStr"/>
+      <c r="M243" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N243" s="6" t="inlineStr">
+        <is>
+          <t>Indonesia support unconfirmed - Skrill country coverage changes; confirm before including.</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="8" t="inlineStr">
+        <is>
+          <t>ewallets/international/western-union</t>
+        </is>
+      </c>
+      <c r="B244" s="8" t="inlineStr">
+        <is>
+          <t>Western Union</t>
+        </is>
+      </c>
+      <c r="C244" s="8" t="inlineStr">
+        <is>
+          <t>ewallet</t>
+        </is>
+      </c>
+      <c r="D244" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E244" s="8" t="inlineStr"/>
+      <c r="F244" s="9" t="inlineStr">
+        <is>
+          <t>https://www.westernunion.com</t>
+        </is>
+      </c>
+      <c r="G244" s="8" t="inlineStr"/>
+      <c r="H244" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I244" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J244" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K244" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L244" s="8" t="inlineStr"/>
+      <c r="M244" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N244" s="6" t="inlineStr">
+        <is>
+          <t>Long-established Indonesia corridor; confirm on WU site. Also now owner of Singapore's Dash (see sea/sg/dash).</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="8" t="inlineStr">
+        <is>
+          <t>ewallets/international/moneygram</t>
+        </is>
+      </c>
+      <c r="B245" s="8" t="inlineStr">
+        <is>
+          <t>MoneyGram</t>
+        </is>
+      </c>
+      <c r="C245" s="8" t="inlineStr">
+        <is>
+          <t>ewallet</t>
+        </is>
+      </c>
+      <c r="D245" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E245" s="8" t="inlineStr"/>
+      <c r="F245" s="9" t="inlineStr">
+        <is>
+          <t>https://www.moneygram.com</t>
+        </is>
+      </c>
+      <c r="G245" s="8" t="inlineStr"/>
+      <c r="H245" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I245" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J245" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K245" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L245" s="8" t="inlineStr"/>
+      <c r="M245" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N245" s="6" t="inlineStr">
+        <is>
           <t>Indonesia support unconfirmed - confirm before including.</t>
         </is>
       </c>
     </row>
+    <row r="246">
+      <c r="A246" s="8" t="inlineStr">
+        <is>
+          <t>ewallets/international/worldremit</t>
+        </is>
+      </c>
+      <c r="B246" s="8" t="inlineStr">
+        <is>
+          <t>WorldRemit</t>
+        </is>
+      </c>
+      <c r="C246" s="8" t="inlineStr">
+        <is>
+          <t>ewallet</t>
+        </is>
+      </c>
+      <c r="D246" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E246" s="8" t="inlineStr"/>
+      <c r="F246" s="9" t="inlineStr">
+        <is>
+          <t>https://www.worldremit.com</t>
+        </is>
+      </c>
+      <c r="G246" s="8" t="inlineStr"/>
+      <c r="H246" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I246" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J246" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K246" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L246" s="8" t="inlineStr"/>
+      <c r="M246" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N246" s="6" t="inlineStr">
+        <is>
+          <t>Indonesia support unconfirmed - confirm before including. Parent group also operates Zepz/Sendwave brands.</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="8" t="inlineStr">
+        <is>
+          <t>ewallets/international/remitly</t>
+        </is>
+      </c>
+      <c r="B247" s="8" t="inlineStr">
+        <is>
+          <t>Remitly</t>
+        </is>
+      </c>
+      <c r="C247" s="8" t="inlineStr">
+        <is>
+          <t>ewallet</t>
+        </is>
+      </c>
+      <c r="D247" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E247" s="8" t="inlineStr"/>
+      <c r="F247" s="9" t="inlineStr">
+        <is>
+          <t>https://www.remitly.com</t>
+        </is>
+      </c>
+      <c r="G247" s="8" t="inlineStr"/>
+      <c r="H247" s="8" t="inlineStr">
+        <is>
+          <t>wordmark</t>
+        </is>
+      </c>
+      <c r="I247" s="6" t="inlineStr">
+        <is>
+          <t>Wordmark is the standard public mark</t>
+        </is>
+      </c>
+      <c r="J247" s="8" t="inlineStr">
+        <is>
+          <t>TBD (horizontal)</t>
+        </is>
+      </c>
+      <c r="K247" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L247" s="8" t="inlineStr"/>
+      <c r="M247" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N247" s="6" t="inlineStr">
+        <is>
+          <t>Indonesia support unconfirmed - confirm before including.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="8" t="inlineStr">
+        <is>
+          <t>ewallets/international/cn/alipay</t>
+        </is>
+      </c>
+      <c r="B248" s="8" t="inlineStr">
+        <is>
+          <t>Alipay</t>
+        </is>
+      </c>
+      <c r="C248" s="8" t="inlineStr">
+        <is>
+          <t>ewallet</t>
+        </is>
+      </c>
+      <c r="D248" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E248" s="8" t="inlineStr">
+        <is>
+          <t>cn</t>
+        </is>
+      </c>
+      <c r="F248" s="8" t="inlineStr"/>
+      <c r="G248" s="8" t="inlineStr"/>
+      <c r="H248" s="8" t="inlineStr">
+        <is>
+          <t>app-icon</t>
+        </is>
+      </c>
+      <c r="I248" s="6" t="inlineStr">
+        <is>
+          <t>App icon is the most recognised mark</t>
+        </is>
+      </c>
+      <c r="J248" s="8" t="inlineStr">
+        <is>
+          <t>TBD (square)</t>
+        </is>
+      </c>
+      <c r="K248" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L248" s="8" t="inlineStr"/>
+      <c r="M248" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N248" s="6" t="inlineStr">
+        <is>
+          <t>Dominant China mobile wallet; PandaRemit and similar corridors deliver into it directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="8" t="inlineStr">
+        <is>
+          <t>ewallets/international/cn/wechat-pay</t>
+        </is>
+      </c>
+      <c r="B249" s="8" t="inlineStr">
+        <is>
+          <t>WeChat Pay</t>
+        </is>
+      </c>
+      <c r="C249" s="8" t="inlineStr">
+        <is>
+          <t>ewallet</t>
+        </is>
+      </c>
+      <c r="D249" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E249" s="8" t="inlineStr">
+        <is>
+          <t>cn</t>
+        </is>
+      </c>
+      <c r="F249" s="8" t="inlineStr"/>
+      <c r="G249" s="8" t="inlineStr"/>
+      <c r="H249" s="8" t="inlineStr">
+        <is>
+          <t>app-icon</t>
+        </is>
+      </c>
+      <c r="I249" s="6" t="inlineStr">
+        <is>
+          <t>App icon is the most recognised mark</t>
+        </is>
+      </c>
+      <c r="J249" s="8" t="inlineStr">
+        <is>
+          <t>TBD (square)</t>
+        </is>
+      </c>
+      <c r="K249" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L249" s="8" t="inlineStr"/>
+      <c r="M249" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N249" s="6" t="inlineStr">
+        <is>
+          <t>Dominant China mobile wallet alongside Alipay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="8" t="inlineStr">
+        <is>
+          <t>ewallets/international/gb/revolut</t>
+        </is>
+      </c>
+      <c r="B250" s="8" t="inlineStr">
+        <is>
+          <t>Revolut</t>
+        </is>
+      </c>
+      <c r="C250" s="8" t="inlineStr">
+        <is>
+          <t>ewallet</t>
+        </is>
+      </c>
+      <c r="D250" s="8" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E250" s="8" t="inlineStr">
+        <is>
+          <t>gb</t>
+        </is>
+      </c>
+      <c r="F250" s="8" t="inlineStr"/>
+      <c r="G250" s="8" t="inlineStr"/>
+      <c r="H250" s="8" t="inlineStr">
+        <is>
+          <t>app-icon</t>
+        </is>
+      </c>
+      <c r="I250" s="6" t="inlineStr">
+        <is>
+          <t>App icon is the most recognised mark</t>
+        </is>
+      </c>
+      <c r="J250" s="8" t="inlineStr">
+        <is>
+          <t>TBD (square)</t>
+        </is>
+      </c>
+      <c r="K250" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="L250" s="8" t="inlineStr"/>
+      <c r="M250" s="10" t="inlineStr">
+        <is>
+          <t>Needs Review</t>
+        </is>
+      </c>
+      <c r="N250" s="6" t="inlineStr">
+        <is>
+          <t>UK-licensed digital bank/wallet; app icon is the recognised mark. Common Wise-adjacent receiving account in Europe.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N206"/>
+  <autoFilter ref="A1:N250"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
@@ -13955,14 +16607,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F196" r:id="rId179"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F197" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F198" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F199" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F200" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F201" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F202" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F203" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F204" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F205" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F206" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F240" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F241" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F242" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F243" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F244" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F245" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F246" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F247" r:id="rId189"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/out/Logo Library - Research Index.xlsx
+++ b/out/Logo Library - Research Index.xlsx
@@ -13329,7 +13329,11 @@
           <t>us</t>
         </is>
       </c>
-      <c r="F199" s="8" t="inlineStr"/>
+      <c r="F199" s="9" t="inlineStr">
+        <is>
+          <t>https://www.chase.com</t>
+        </is>
+      </c>
       <c r="G199" s="8" t="inlineStr"/>
       <c r="H199" s="8" t="inlineStr">
         <is>
@@ -13389,7 +13393,11 @@
           <t>us</t>
         </is>
       </c>
-      <c r="F200" s="8" t="inlineStr"/>
+      <c r="F200" s="9" t="inlineStr">
+        <is>
+          <t>https://www.bankofamerica.com</t>
+        </is>
+      </c>
       <c r="G200" s="8" t="inlineStr"/>
       <c r="H200" s="8" t="inlineStr">
         <is>
@@ -13449,7 +13457,11 @@
           <t>us</t>
         </is>
       </c>
-      <c r="F201" s="8" t="inlineStr"/>
+      <c r="F201" s="9" t="inlineStr">
+        <is>
+          <t>https://www.wellsfargo.com</t>
+        </is>
+      </c>
       <c r="G201" s="8" t="inlineStr"/>
       <c r="H201" s="8" t="inlineStr">
         <is>
@@ -13509,7 +13521,11 @@
           <t>us</t>
         </is>
       </c>
-      <c r="F202" s="8" t="inlineStr"/>
+      <c r="F202" s="9" t="inlineStr">
+        <is>
+          <t>https://www.capitalone.com</t>
+        </is>
+      </c>
       <c r="G202" s="8" t="inlineStr"/>
       <c r="H202" s="8" t="inlineStr">
         <is>
@@ -13569,7 +13585,11 @@
           <t>us</t>
         </is>
       </c>
-      <c r="F203" s="8" t="inlineStr"/>
+      <c r="F203" s="9" t="inlineStr">
+        <is>
+          <t>https://www.usbank.com</t>
+        </is>
+      </c>
       <c r="G203" s="8" t="inlineStr"/>
       <c r="H203" s="8" t="inlineStr">
         <is>
@@ -13629,7 +13649,11 @@
           <t>us</t>
         </is>
       </c>
-      <c r="F204" s="8" t="inlineStr"/>
+      <c r="F204" s="9" t="inlineStr">
+        <is>
+          <t>https://www.pnc.com</t>
+        </is>
+      </c>
       <c r="G204" s="8" t="inlineStr"/>
       <c r="H204" s="8" t="inlineStr">
         <is>
@@ -13689,7 +13713,11 @@
           <t>us</t>
         </is>
       </c>
-      <c r="F205" s="8" t="inlineStr"/>
+      <c r="F205" s="9" t="inlineStr">
+        <is>
+          <t>https://www.chime.com</t>
+        </is>
+      </c>
       <c r="G205" s="8" t="inlineStr"/>
       <c r="H205" s="8" t="inlineStr">
         <is>
@@ -13749,7 +13777,11 @@
           <t>gb</t>
         </is>
       </c>
-      <c r="F206" s="8" t="inlineStr"/>
+      <c r="F206" s="9" t="inlineStr">
+        <is>
+          <t>https://www.barclays.co.uk</t>
+        </is>
+      </c>
       <c r="G206" s="8" t="inlineStr"/>
       <c r="H206" s="8" t="inlineStr">
         <is>
@@ -13809,7 +13841,11 @@
           <t>gb</t>
         </is>
       </c>
-      <c r="F207" s="8" t="inlineStr"/>
+      <c r="F207" s="9" t="inlineStr">
+        <is>
+          <t>https://www.lloydsbank.com</t>
+        </is>
+      </c>
       <c r="G207" s="8" t="inlineStr"/>
       <c r="H207" s="8" t="inlineStr">
         <is>
@@ -13869,7 +13905,11 @@
           <t>gb</t>
         </is>
       </c>
-      <c r="F208" s="8" t="inlineStr"/>
+      <c r="F208" s="9" t="inlineStr">
+        <is>
+          <t>https://www.natwest.com</t>
+        </is>
+      </c>
       <c r="G208" s="8" t="inlineStr"/>
       <c r="H208" s="8" t="inlineStr">
         <is>
@@ -13929,7 +13969,11 @@
           <t>gb</t>
         </is>
       </c>
-      <c r="F209" s="8" t="inlineStr"/>
+      <c r="F209" s="9" t="inlineStr">
+        <is>
+          <t>https://www.santander.co.uk</t>
+        </is>
+      </c>
       <c r="G209" s="8" t="inlineStr"/>
       <c r="H209" s="8" t="inlineStr">
         <is>
@@ -13989,7 +14033,11 @@
           <t>gb</t>
         </is>
       </c>
-      <c r="F210" s="8" t="inlineStr"/>
+      <c r="F210" s="9" t="inlineStr">
+        <is>
+          <t>https://monzo.com</t>
+        </is>
+      </c>
       <c r="G210" s="8" t="inlineStr"/>
       <c r="H210" s="8" t="inlineStr">
         <is>
@@ -14049,7 +14097,11 @@
           <t>de</t>
         </is>
       </c>
-      <c r="F211" s="8" t="inlineStr"/>
+      <c r="F211" s="9" t="inlineStr">
+        <is>
+          <t>https://www.deutsche-bank.de</t>
+        </is>
+      </c>
       <c r="G211" s="8" t="inlineStr"/>
       <c r="H211" s="8" t="inlineStr">
         <is>
@@ -14109,7 +14161,11 @@
           <t>de</t>
         </is>
       </c>
-      <c r="F212" s="8" t="inlineStr"/>
+      <c r="F212" s="9" t="inlineStr">
+        <is>
+          <t>https://www.commerzbank.de</t>
+        </is>
+      </c>
       <c r="G212" s="8" t="inlineStr"/>
       <c r="H212" s="8" t="inlineStr">
         <is>
@@ -14169,7 +14225,11 @@
           <t>de</t>
         </is>
       </c>
-      <c r="F213" s="8" t="inlineStr"/>
+      <c r="F213" s="9" t="inlineStr">
+        <is>
+          <t>https://n26.com</t>
+        </is>
+      </c>
       <c r="G213" s="8" t="inlineStr"/>
       <c r="H213" s="8" t="inlineStr">
         <is>
@@ -14229,7 +14289,11 @@
           <t>fr</t>
         </is>
       </c>
-      <c r="F214" s="8" t="inlineStr"/>
+      <c r="F214" s="9" t="inlineStr">
+        <is>
+          <t>https://www.bnpparibas.com</t>
+        </is>
+      </c>
       <c r="G214" s="8" t="inlineStr"/>
       <c r="H214" s="8" t="inlineStr">
         <is>
@@ -14289,7 +14353,11 @@
           <t>fr</t>
         </is>
       </c>
-      <c r="F215" s="8" t="inlineStr"/>
+      <c r="F215" s="9" t="inlineStr">
+        <is>
+          <t>https://www.societegenerale.com</t>
+        </is>
+      </c>
       <c r="G215" s="8" t="inlineStr"/>
       <c r="H215" s="8" t="inlineStr">
         <is>
@@ -14349,7 +14417,11 @@
           <t>fr</t>
         </is>
       </c>
-      <c r="F216" s="8" t="inlineStr"/>
+      <c r="F216" s="9" t="inlineStr">
+        <is>
+          <t>https://www.credit-agricole.com</t>
+        </is>
+      </c>
       <c r="G216" s="8" t="inlineStr"/>
       <c r="H216" s="8" t="inlineStr">
         <is>
@@ -14409,7 +14481,11 @@
           <t>nl</t>
         </is>
       </c>
-      <c r="F217" s="8" t="inlineStr"/>
+      <c r="F217" s="9" t="inlineStr">
+        <is>
+          <t>https://www.ing.nl</t>
+        </is>
+      </c>
       <c r="G217" s="8" t="inlineStr"/>
       <c r="H217" s="8" t="inlineStr">
         <is>
@@ -14469,7 +14545,11 @@
           <t>nl</t>
         </is>
       </c>
-      <c r="F218" s="8" t="inlineStr"/>
+      <c r="F218" s="9" t="inlineStr">
+        <is>
+          <t>https://www.abnamro.nl</t>
+        </is>
+      </c>
       <c r="G218" s="8" t="inlineStr"/>
       <c r="H218" s="8" t="inlineStr">
         <is>
@@ -14529,7 +14609,11 @@
           <t>nl</t>
         </is>
       </c>
-      <c r="F219" s="8" t="inlineStr"/>
+      <c r="F219" s="9" t="inlineStr">
+        <is>
+          <t>https://www.rabobank.nl</t>
+        </is>
+      </c>
       <c r="G219" s="8" t="inlineStr"/>
       <c r="H219" s="8" t="inlineStr">
         <is>
@@ -14589,7 +14673,11 @@
           <t>cn</t>
         </is>
       </c>
-      <c r="F220" s="8" t="inlineStr"/>
+      <c r="F220" s="9" t="inlineStr">
+        <is>
+          <t>https://www.boc.cn</t>
+        </is>
+      </c>
       <c r="G220" s="8" t="inlineStr"/>
       <c r="H220" s="8" t="inlineStr">
         <is>
@@ -14649,7 +14737,11 @@
           <t>cn</t>
         </is>
       </c>
-      <c r="F221" s="8" t="inlineStr"/>
+      <c r="F221" s="9" t="inlineStr">
+        <is>
+          <t>https://www.icbc.com.cn</t>
+        </is>
+      </c>
       <c r="G221" s="8" t="inlineStr"/>
       <c r="H221" s="8" t="inlineStr">
         <is>
@@ -14709,7 +14801,11 @@
           <t>cn</t>
         </is>
       </c>
-      <c r="F222" s="8" t="inlineStr"/>
+      <c r="F222" s="9" t="inlineStr">
+        <is>
+          <t>https://www.ccb.com</t>
+        </is>
+      </c>
       <c r="G222" s="8" t="inlineStr"/>
       <c r="H222" s="8" t="inlineStr">
         <is>
@@ -14769,7 +14865,11 @@
           <t>cn</t>
         </is>
       </c>
-      <c r="F223" s="8" t="inlineStr"/>
+      <c r="F223" s="9" t="inlineStr">
+        <is>
+          <t>https://www.abchina.com</t>
+        </is>
+      </c>
       <c r="G223" s="8" t="inlineStr"/>
       <c r="H223" s="8" t="inlineStr">
         <is>
@@ -14829,7 +14929,11 @@
           <t>cn</t>
         </is>
       </c>
-      <c r="F224" s="8" t="inlineStr"/>
+      <c r="F224" s="9" t="inlineStr">
+        <is>
+          <t>https://www.cmbchina.com</t>
+        </is>
+      </c>
       <c r="G224" s="8" t="inlineStr"/>
       <c r="H224" s="8" t="inlineStr">
         <is>
@@ -14889,7 +14993,11 @@
           <t>au</t>
         </is>
       </c>
-      <c r="F225" s="8" t="inlineStr"/>
+      <c r="F225" s="9" t="inlineStr">
+        <is>
+          <t>https://www.commbank.com.au</t>
+        </is>
+      </c>
       <c r="G225" s="8" t="inlineStr"/>
       <c r="H225" s="8" t="inlineStr">
         <is>
@@ -14949,7 +15057,11 @@
           <t>au</t>
         </is>
       </c>
-      <c r="F226" s="8" t="inlineStr"/>
+      <c r="F226" s="9" t="inlineStr">
+        <is>
+          <t>https://www.westpac.com.au</t>
+        </is>
+      </c>
       <c r="G226" s="8" t="inlineStr"/>
       <c r="H226" s="8" t="inlineStr">
         <is>
@@ -15009,7 +15121,11 @@
           <t>au</t>
         </is>
       </c>
-      <c r="F227" s="8" t="inlineStr"/>
+      <c r="F227" s="9" t="inlineStr">
+        <is>
+          <t>https://www.anz.com.au</t>
+        </is>
+      </c>
       <c r="G227" s="8" t="inlineStr"/>
       <c r="H227" s="8" t="inlineStr">
         <is>
@@ -15069,7 +15185,11 @@
           <t>au</t>
         </is>
       </c>
-      <c r="F228" s="8" t="inlineStr"/>
+      <c r="F228" s="9" t="inlineStr">
+        <is>
+          <t>https://www.nab.com.au</t>
+        </is>
+      </c>
       <c r="G228" s="8" t="inlineStr"/>
       <c r="H228" s="8" t="inlineStr">
         <is>
@@ -15129,7 +15249,11 @@
           <t>ca</t>
         </is>
       </c>
-      <c r="F229" s="8" t="inlineStr"/>
+      <c r="F229" s="9" t="inlineStr">
+        <is>
+          <t>https://www.rbc.com</t>
+        </is>
+      </c>
       <c r="G229" s="8" t="inlineStr"/>
       <c r="H229" s="8" t="inlineStr">
         <is>
@@ -15189,7 +15313,11 @@
           <t>ca</t>
         </is>
       </c>
-      <c r="F230" s="8" t="inlineStr"/>
+      <c r="F230" s="9" t="inlineStr">
+        <is>
+          <t>https://www.td.com</t>
+        </is>
+      </c>
       <c r="G230" s="8" t="inlineStr"/>
       <c r="H230" s="8" t="inlineStr">
         <is>
@@ -15249,7 +15377,11 @@
           <t>ca</t>
         </is>
       </c>
-      <c r="F231" s="8" t="inlineStr"/>
+      <c r="F231" s="9" t="inlineStr">
+        <is>
+          <t>https://www.scotiabank.com</t>
+        </is>
+      </c>
       <c r="G231" s="8" t="inlineStr"/>
       <c r="H231" s="8" t="inlineStr">
         <is>
@@ -15309,7 +15441,11 @@
           <t>jp</t>
         </is>
       </c>
-      <c r="F232" s="8" t="inlineStr"/>
+      <c r="F232" s="9" t="inlineStr">
+        <is>
+          <t>https://www.bk.mufg.jp</t>
+        </is>
+      </c>
       <c r="G232" s="8" t="inlineStr"/>
       <c r="H232" s="8" t="inlineStr">
         <is>
@@ -15369,7 +15505,11 @@
           <t>jp</t>
         </is>
       </c>
-      <c r="F233" s="8" t="inlineStr"/>
+      <c r="F233" s="9" t="inlineStr">
+        <is>
+          <t>https://www.smbc.co.jp</t>
+        </is>
+      </c>
       <c r="G233" s="8" t="inlineStr"/>
       <c r="H233" s="8" t="inlineStr">
         <is>
@@ -15429,7 +15569,11 @@
           <t>jp</t>
         </is>
       </c>
-      <c r="F234" s="8" t="inlineStr"/>
+      <c r="F234" s="9" t="inlineStr">
+        <is>
+          <t>https://www.jp-bank.japanpost.jp</t>
+        </is>
+      </c>
       <c r="G234" s="8" t="inlineStr"/>
       <c r="H234" s="8" t="inlineStr">
         <is>
@@ -15489,7 +15633,11 @@
           <t>kr</t>
         </is>
       </c>
-      <c r="F235" s="8" t="inlineStr"/>
+      <c r="F235" s="9" t="inlineStr">
+        <is>
+          <t>https://www.kbstar.com</t>
+        </is>
+      </c>
       <c r="G235" s="8" t="inlineStr"/>
       <c r="H235" s="8" t="inlineStr">
         <is>
@@ -15549,7 +15697,11 @@
           <t>kr</t>
         </is>
       </c>
-      <c r="F236" s="8" t="inlineStr"/>
+      <c r="F236" s="9" t="inlineStr">
+        <is>
+          <t>https://www.shinhan.com</t>
+        </is>
+      </c>
       <c r="G236" s="8" t="inlineStr"/>
       <c r="H236" s="8" t="inlineStr">
         <is>
@@ -15609,7 +15761,11 @@
           <t>kr</t>
         </is>
       </c>
-      <c r="F237" s="8" t="inlineStr"/>
+      <c r="F237" s="9" t="inlineStr">
+        <is>
+          <t>https://www.wooribank.com</t>
+        </is>
+      </c>
       <c r="G237" s="8" t="inlineStr"/>
       <c r="H237" s="8" t="inlineStr">
         <is>
@@ -15669,7 +15825,11 @@
           <t>hk</t>
         </is>
       </c>
-      <c r="F238" s="8" t="inlineStr"/>
+      <c r="F238" s="9" t="inlineStr">
+        <is>
+          <t>https://www.hangseng.com</t>
+        </is>
+      </c>
       <c r="G238" s="8" t="inlineStr"/>
       <c r="H238" s="8" t="inlineStr">
         <is>
@@ -15729,7 +15889,11 @@
           <t>hk</t>
         </is>
       </c>
-      <c r="F239" s="8" t="inlineStr"/>
+      <c r="F239" s="9" t="inlineStr">
+        <is>
+          <t>https://www.bochk.com</t>
+        </is>
+      </c>
       <c r="G239" s="8" t="inlineStr"/>
       <c r="H239" s="8" t="inlineStr">
         <is>
@@ -16269,7 +16433,11 @@
           <t>cn</t>
         </is>
       </c>
-      <c r="F248" s="8" t="inlineStr"/>
+      <c r="F248" s="9" t="inlineStr">
+        <is>
+          <t>https://www.alipay.com</t>
+        </is>
+      </c>
       <c r="G248" s="8" t="inlineStr"/>
       <c r="H248" s="8" t="inlineStr">
         <is>
@@ -16329,7 +16497,11 @@
           <t>cn</t>
         </is>
       </c>
-      <c r="F249" s="8" t="inlineStr"/>
+      <c r="F249" s="9" t="inlineStr">
+        <is>
+          <t>https://pay.weixin.qq.com</t>
+        </is>
+      </c>
       <c r="G249" s="8" t="inlineStr"/>
       <c r="H249" s="8" t="inlineStr">
         <is>
@@ -16389,7 +16561,11 @@
           <t>gb</t>
         </is>
       </c>
-      <c r="F250" s="8" t="inlineStr"/>
+      <c r="F250" s="9" t="inlineStr">
+        <is>
+          <t>https://www.revolut.com</t>
+        </is>
+      </c>
       <c r="G250" s="8" t="inlineStr"/>
       <c r="H250" s="8" t="inlineStr">
         <is>
@@ -16607,14 +16783,58 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F196" r:id="rId179"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F197" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F198" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F240" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F241" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F242" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F243" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F244" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F245" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F246" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F247" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F199" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F200" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F201" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F202" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F203" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F204" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F205" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F206" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F207" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F208" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F209" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F210" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F211" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F212" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F213" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F214" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F215" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F216" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F217" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F218" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F219" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F220" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F221" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F222" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F223" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F224" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F225" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F226" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F227" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F228" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F229" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F230" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F231" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F232" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F233" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F234" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F235" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F236" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F237" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F238" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F239" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F240" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F241" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F242" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F243" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F244" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F245" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F246" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F247" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F248" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F249" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F250" r:id="rId233"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/out/Logo Library - Research Index.xlsx
+++ b/out/Logo Library - Research Index.xlsx
@@ -1442,7 +1442,11 @@
           <t>https://www.bankmandiri.co.id</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr"/>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/32/e9/73/32e97344-be52-db91-23ee-42a3c82aa6eb/AppIcon-0-0-1x_U007emarketing-0-7-0-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H2" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -1455,15 +1459,19 @@
       </c>
       <c r="J2" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L2" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L2" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bank-mandiri.png</t>
+        </is>
+      </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -1471,7 +1479,7 @@
       </c>
       <c r="N2" s="6" t="inlineStr">
         <is>
-          <t>State-owned (KBMI 4).</t>
+          <t>State-owned (KBMI 4). Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1510,11 @@
           <t>https://www.bri.co.id</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>https://www.bri.co.id/web/guest/_next/image?url=https%3A%2F%2Fbri.co.id%2Fweb%2Fguest%2Fapi%2Ffiles%2F%3Fpath%3D%2Fsites%2Fdefault%2Ffiles%2Fimages%2FLogo%2520BRI_updated_blue%2520%25282%2529.png&amp;w=256&amp;q=75</t>
+        </is>
+      </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -1515,15 +1527,19 @@
       </c>
       <c r="J3" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.88:1 (horizontal, 256x136)</t>
         </is>
       </c>
       <c r="K3" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L3" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bri.png</t>
+        </is>
+      </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -1531,7 +1547,7 @@
       </c>
       <c r="N3" s="6" t="inlineStr">
         <is>
-          <t>State-owned (KBMI 4). Verify: OJK/BI register.</t>
+          <t>State-owned (KBMI 4). Verify: OJK/BI register. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1638,11 @@
           <t>https://www.bca.co.id</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>https://www.bca.co.id/-/media/Feature/Header/Header-Logo/logo-bca.svg?v=1</t>
+        </is>
+      </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
           <t>icon</t>
@@ -1635,15 +1655,19 @@
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
-          <t>TBD (square-ish)</t>
+          <t>2.24:1 (horizontal, 123x55)</t>
         </is>
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L5" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bca.svg</t>
+        </is>
+      </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -1651,7 +1675,7 @@
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>Largest private bank. Verify: OJK/BI register.</t>
+          <t>Largest private bank. Verify: OJK/BI register. Auto-sourced via brand-press.</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1706,11 @@
           <t>https://www.btn.co.id</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>https://www.btn.co.id/-/media/Images/Corporate/Flags/flags/flag_us.svg?h=24&amp;w=28&amp;hash=9B9730C8C0550B8BE8E6DFAD9C6FD0F5</t>
+        </is>
+      </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -1695,15 +1723,19 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.47:1 (horizontal, 22x15)</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/btn.svg</t>
+        </is>
+      </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -1711,7 +1743,7 @@
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>State-owned. Verify: OJK/BI register.</t>
+          <t>State-owned. Verify: OJK/BI register. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1774,11 @@
           <t>https://www.bankbsi.co.id</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr"/>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>https://www.bankbsi.co.id/img/logo bewize.png</t>
+        </is>
+      </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -1755,15 +1791,19 @@
       </c>
       <c r="J7" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>2.41:1 (horizontal, 3058x1271)</t>
         </is>
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L7" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bsi.png</t>
+        </is>
+      </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -1771,7 +1811,7 @@
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>Formed 2021 from BRIsyariah/BNI Syariah/Mandiri Syariah merger.</t>
+          <t>Formed 2021 from BRIsyariah/BNI Syariah/Mandiri Syariah merger. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1842,11 @@
           <t>https://www.cimbniaga.co.id</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr"/>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>https://www.cimbniaga.co.id/content/dam/cimb/revamp/cimb-logo/logo-cimb-syariah.svg</t>
+        </is>
+      </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -1815,15 +1859,19 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>4.07:1 (horizontal, 183x45)</t>
         </is>
       </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/cimb-niaga.svg</t>
+        </is>
+      </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -1831,7 +1879,7 @@
       </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
-          <t>Verify: OJK/BI register.</t>
+          <t>Verify: OJK/BI register. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1910,11 @@
           <t>https://www.danamon.co.id</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr"/>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>https://www.danamon.co.id/-/media/Project/Danamon/DCWCOID/v1/Header/Logo/Logo-Danamon-Default-v1.svg?h=29&amp;w=28</t>
+        </is>
+      </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -1875,15 +1927,19 @@
       </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.49:1 (horizontal, 91x61)</t>
         </is>
       </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L9" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/danamon.svg</t>
+        </is>
+      </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -1891,7 +1947,7 @@
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>MUFG-controlled.</t>
+          <t>MUFG-controlled. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1978,11 @@
           <t>https://www.permatabank.com</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr"/>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>https://www.permatabank.com/favicon.ico</t>
+        </is>
+      </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -1935,15 +1995,19 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 256x256)</t>
         </is>
       </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L10" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/permata.png</t>
+        </is>
+      </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -1951,7 +2015,7 @@
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>Owned by Bangkok Bank.</t>
+          <t>Owned by Bangkok Bank. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2106,11 @@
           <t>https://www.ocbc.id</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr"/>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>https://cdn1.ocbc.id/asset/media/Project/OCBC/OCBCID/V1/Header/Logo-Menu/ocbc-white.png?h=392&amp;w=1452&amp;rev=31388dd61e9a4ea0a80496439349020b</t>
+        </is>
+      </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -2055,15 +2123,19 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>3.70:1 (horizontal, 1452x392)</t>
         </is>
       </c>
       <c r="K12" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L12" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/ocbc-indonesia.png</t>
+        </is>
+      </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -2071,7 +2143,7 @@
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>Rebranded from OCBC NISP (2023) - do not use pre-rebrand asset.</t>
+          <t>Rebranded from OCBC NISP (2023) - do not use pre-rebrand asset. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2174,11 @@
           <t>https://www.maybank.co.id</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr"/>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>https://www.maybank.co.id/-/media/Feature/Content/Header/lock.svg?iar=0&amp;hash=16FFE81C2F66D0261C501493371E0446</t>
+        </is>
+      </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -2115,15 +2191,19 @@
       </c>
       <c r="J13" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 27x27)</t>
         </is>
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L13" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/maybank-indonesia.svg</t>
+        </is>
+      </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -2131,7 +2211,7 @@
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>Candidate row; regulator check and asset sourcing outstanding.</t>
+          <t>Candidate row; regulator check and asset sourcing outstanding. Auto-sourced via brand-press.</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2298,11 @@
           <t>https://www.bankmega.com</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr"/>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>https://bankmega.com/static/img/bank_mega_logo.png</t>
+        </is>
+      </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -2231,15 +2315,19 @@
       </c>
       <c r="J15" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.71:1 (horizontal, 1200x701)</t>
         </is>
       </c>
       <c r="K15" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L15" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/mega.png</t>
+        </is>
+      </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -2247,7 +2335,7 @@
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>CT Corp group.</t>
+          <t>CT Corp group. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2366,11 @@
           <t>https://www.kbbank.co.id</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr"/>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/37/60/0f/37600fd4-96a8-b3ab-04fd-2625a8e540b3/AppIcon-0-1x_U007emarketing-0-11-0-85-220-0.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -2291,15 +2383,19 @@
       </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L16" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L16" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/kb-bank.png</t>
+        </is>
+      </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -2307,7 +2403,7 @@
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
-          <t>Rebranded from KB Bukopin (2024) - confirm current name/domain.</t>
+          <t>Rebranded from KB Bukopin (2024) - confirm current name/domain. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2434,11 @@
           <t>https://www.btpnsyariah.com</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr"/>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>https://www.btpnsyariah.com/api/asset/tag/path/logo</t>
+        </is>
+      </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -2351,15 +2451,19 @@
       </c>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.65:1 (horizontal, 312x189)</t>
         </is>
       </c>
       <c r="K17" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L17" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/btpn-syariah.png</t>
+        </is>
+      </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -2367,7 +2471,7 @@
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
-          <t>Retains BTPN Syariah name despite parent rebrand - confirm.</t>
+          <t>Retains BTPN Syariah name despite parent rebrand - confirm. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2562,11 @@
           <t>https://www.bankbjb.co.id</t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr"/>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/04/18/66/04186657-1a13-1a34-5e9f-d98908fbbfb6/AppIcon-0-0-1x_U007emarketing-0-8-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -2471,15 +2579,19 @@
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K19" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L19" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bjb.png</t>
+        </is>
+      </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -2487,7 +2599,7 @@
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
-          <t>Regional (BPD West Java).</t>
+          <t>Regional (BPD West Java). Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2630,11 @@
           <t>https://www.bankdki.co.id</t>
         </is>
       </c>
-      <c r="G20" s="8" t="inlineStr"/>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/af/c7/f9/afc7f987-e7b7-ef06-65a5-3d929a34c02c/AppIcon-0-0-1x_U007emarketing-0-11-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -2531,15 +2647,19 @@
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L20" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L20" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bank-dki.png</t>
+        </is>
+      </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -2547,7 +2667,7 @@
       </c>
       <c r="N20" s="6" t="inlineStr">
         <is>
-          <t>Regional (Jakarta).</t>
+          <t>Regional (Jakarta). Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2698,11 @@
           <t>https://www.bankjatim.co.id</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr"/>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>https://www.bankjatim.co.id/themes/bjtm07/assets/img/logo.png</t>
+        </is>
+      </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -2591,15 +2715,19 @@
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>4.00:1 (horizontal, 160x40)</t>
         </is>
       </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L21" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bank-jatim.png</t>
+        </is>
+      </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -2607,7 +2735,7 @@
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>Regional (East Java).</t>
+          <t>Regional (East Java). Auto-sourced via brand-press.</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2766,11 @@
           <t>https://www.bankmuamalat.co.id</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr"/>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/ee/bd/1e/eebd1efa-f525-1ab2-a107-88e60c6e9fab/AppIcon-0-0-1x_U007emarketing-0-6-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -2651,15 +2783,19 @@
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K22" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L22" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/muamalat.png</t>
+        </is>
+      </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -2667,7 +2803,7 @@
       </c>
       <c r="N22" s="6" t="inlineStr">
         <is>
-          <t>First Indonesian sharia bank.</t>
+          <t>First Indonesian sharia bank. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2834,11 @@
           <t>https://www.jago.com</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr"/>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>https://www.jago.com/images/brand/logo-jago-re.svg</t>
+        </is>
+      </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -2711,15 +2851,19 @@
       </c>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>2.37:1 (horizontal, 1386x584)</t>
         </is>
       </c>
       <c r="K23" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L23" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L23" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/jago.svg</t>
+        </is>
+      </c>
       <c r="M23" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -2727,7 +2871,7 @@
       </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
-          <t>Digital bank.</t>
+          <t>Digital bank. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -2758,7 +2902,11 @@
           <t>https://www.seabank.co.id</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr"/>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>https://appmanager.seabank.co.id/seamoney/bke/app-manager/live/front_low_code/20230920/40abe4c7131b49d2bd27d9994c405e58.svg</t>
+        </is>
+      </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -2771,15 +2919,19 @@
       </c>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>3.11:1 (horizontal, 252x81)</t>
         </is>
       </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L24" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L24" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/seabank.svg</t>
+        </is>
+      </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -2787,7 +2939,7 @@
       </c>
       <c r="N24" s="6" t="inlineStr">
         <is>
-          <t>Sea Group.</t>
+          <t>Sea Group. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -2818,7 +2970,11 @@
           <t>https://www.allobank.com</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr"/>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/e4/26/62/e4266263-377c-9ebe-e076-cf4bac09aed8/AppIcon-0-0-1x_U007emarketing-0-8-0-sRGB-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -2831,15 +2987,19 @@
       </c>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L25" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/allo-bank.png</t>
+        </is>
+      </c>
       <c r="M25" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -2847,7 +3007,7 @@
       </c>
       <c r="N25" s="6" t="inlineStr">
         <is>
-          <t>CT Corp group.</t>
+          <t>CT Corp group. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -2878,7 +3038,11 @@
           <t>https://superbank.id</t>
         </is>
       </c>
-      <c r="G26" s="8" t="inlineStr"/>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/b0/22/19/b0221973-f44f-f5be-02b2-7a6ba46a24f5/AppIcon-0-0-1x_U007emarketing-0-11-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -2891,15 +3055,19 @@
       </c>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K26" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L26" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/superbank.png</t>
+        </is>
+      </c>
       <c r="M26" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -2907,7 +3075,7 @@
       </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
-          <t>Grab/Singtel/Emtek backed.</t>
+          <t>Grab/Singtel/Emtek backed. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -2938,7 +3106,11 @@
           <t>https://www.bankneocommerce.co.id</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr"/>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>https://www-cms.bankneo.co.id/storage/photos/1/logo/logo_bnc_dark.png</t>
+        </is>
+      </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -2951,15 +3123,19 @@
       </c>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>2.30:1 (horizontal, 184x80)</t>
         </is>
       </c>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L27" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/neo-commerce.png</t>
+        </is>
+      </c>
       <c r="M27" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -2967,7 +3143,7 @@
       </c>
       <c r="N27" s="6" t="inlineStr">
         <is>
-          <t>Candidate row; regulator check and asset sourcing outstanding.</t>
+          <t>Candidate row; regulator check and asset sourcing outstanding. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -2998,7 +3174,11 @@
           <t>https://blubybcadigital.id</t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr"/>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>https://blubybcadigital.id/cms/uploads/twitter_logo_new_white_e56fec9cd5.png</t>
+        </is>
+      </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -3011,15 +3191,19 @@
       </c>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 1080x1080)</t>
         </is>
       </c>
       <c r="K28" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L28" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/blu-bca.png</t>
+        </is>
+      </c>
       <c r="M28" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -3027,7 +3211,7 @@
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>Distinct brand from BCA parent - keep separate row.</t>
+          <t>Distinct brand from BCA parent - keep separate row. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3242,11 @@
           <t>https://www.hsbc.co.id</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr"/>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>https://www.hsbc.co.id/etc.clientlibs/dpws/clientlibs-public/clientlib-site/resources/favicons/safari-pinned-tab.svg</t>
+        </is>
+      </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
           <t>icon</t>
@@ -3071,15 +3259,19 @@
       </c>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>TBD (square-ish)</t>
+          <t>1.00:1 (square, 195x195)</t>
         </is>
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L29" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/hsbc-indonesia.svg</t>
+        </is>
+      </c>
       <c r="M29" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -3087,7 +3279,7 @@
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>Local arm of global group.</t>
+          <t>Local arm of global group. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3310,11 @@
           <t>https://www.uob.co.id</t>
         </is>
       </c>
-      <c r="G30" s="8" t="inlineStr"/>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/e1/bd/02/e1bd0225-46b8-a3a1-7c3b-2009769a4742/AppIcon-1x_U007emarketing-0-6-0-85-220-0.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -3131,15 +3327,19 @@
       </c>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L30" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L30" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/uob-indonesia.png</t>
+        </is>
+      </c>
       <c r="M30" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -3147,7 +3347,7 @@
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>Acquired Citi Indonesia consumer business (2023).</t>
+          <t>Acquired Citi Indonesia consumer business (2023). Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -3178,7 +3378,11 @@
           <t>https://www.citibank.co.id</t>
         </is>
       </c>
-      <c r="G31" s="8" t="inlineStr"/>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>https://www.citigroup.com/rcs/v1/media/citigpa/akpublic/storage/retrieveMediaFile/6359ebbc69e8b35a2eae8fa0.jpg</t>
+        </is>
+      </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -3191,15 +3395,19 @@
       </c>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>3.15:1 (horizontal, 1400x445)</t>
         </is>
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L31" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L31" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/citibank-indonesia.jpg</t>
+        </is>
+      </c>
       <c r="M31" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -3207,7 +3415,7 @@
       </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
-          <t>Consumer banking sold to UOB in 2023; institutional only. Confirm whether still in scope for a consumer payment UI before including.</t>
+          <t>Consumer banking sold to UOB in 2023; institutional only. Confirm whether still in scope for a consumer payment UI before including. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3446,11 @@
           <t>https://www.bankraya.co.id</t>
         </is>
       </c>
-      <c r="G32" s="8" t="inlineStr"/>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>https://www.bankraya.co.id/img/logo.svg</t>
+        </is>
+      </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -3251,15 +3463,19 @@
       </c>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.83:1 (horizontal, 1485x812)</t>
         </is>
       </c>
       <c r="K32" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L32" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bank-raya.svg</t>
+        </is>
+      </c>
       <c r="M32" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -3267,7 +3483,7 @@
       </c>
       <c r="N32" s="6" t="inlineStr">
         <is>
-          <t>Digital bank; ex-BRI Agroniaga (rebranded 2021). BRI group.</t>
+          <t>Digital bank; ex-BRI Agroniaga (rebranded 2021). BRI group. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3514,11 @@
           <t>https://www.amarbank.co.id</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr"/>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>https://storage.googleapis.com/amarbank-new/prod/image/comp/favicon_io/apple-touch-icon.png</t>
+        </is>
+      </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -3311,15 +3531,19 @@
       </c>
       <c r="J33" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 180x180)</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L33" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L33" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/amar-bank.png</t>
+        </is>
+      </c>
       <c r="M33" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -3327,7 +3551,7 @@
       </c>
       <c r="N33" s="6" t="inlineStr">
         <is>
-          <t>Digital bank (Senyumku / Tunaiku).</t>
+          <t>Digital bank (Senyumku / Tunaiku). Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3582,11 @@
           <t>https://www.krombank.com</t>
         </is>
       </c>
-      <c r="G34" s="8" t="inlineStr"/>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>https://i0.wp.com/krom.id/wp-content/uploads/2022/08/cropped-ic_krom_logo.png?fit=180%2C180&amp;ssl=1</t>
+        </is>
+      </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -3371,15 +3599,19 @@
       </c>
       <c r="J34" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 180x180)</t>
         </is>
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L34" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L34" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/krom-bank.png</t>
+        </is>
+      </c>
       <c r="M34" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -3387,7 +3619,7 @@
       </c>
       <c r="N34" s="6" t="inlineStr">
         <is>
-          <t>Digital bank; ex-Bank Bisnis Internasional. Kredivo group.</t>
+          <t>Digital bank; ex-Bank Bisnis Internasional. Kredivo group. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3650,11 @@
           <t>https://www.banksaqu.co.id</t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr"/>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>https://banksaqu.co.id/icons/apple-icon.png</t>
+        </is>
+      </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -3431,15 +3667,19 @@
       </c>
       <c r="J35" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 192x192)</t>
         </is>
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L35" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bank-saqu.png</t>
+        </is>
+      </c>
       <c r="M35" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -3447,7 +3687,7 @@
       </c>
       <c r="N35" s="6" t="inlineStr">
         <is>
-          <t>Digital bank; ex-Bank Jasa Jakarta. Astra + WeLab.</t>
+          <t>Digital bank; ex-Bank Jasa Jakarta. Astra + WeLab. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3718,11 @@
           <t>https://www.hibank.co.id</t>
         </is>
       </c>
-      <c r="G36" s="8" t="inlineStr"/>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/3e/bc/62/3ebc624a-929b-07f3-37db-d845752f4c84/AppIcon-0-0-1x_U007emarketing-0-11-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -3491,15 +3735,19 @@
       </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K36" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L36" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L36" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/hibank.png</t>
+        </is>
+      </c>
       <c r="M36" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -3507,7 +3755,7 @@
       </c>
       <c r="N36" s="6" t="inlineStr">
         <is>
-          <t>Digital bank; ex-Bank Mayora. BNI subsidiary. Lowercase wordmark - preserve casing.</t>
+          <t>Digital bank; ex-Bank Mayora. BNI subsidiary. Lowercase wordmark - preserve casing. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -3538,7 +3786,11 @@
           <t>https://www.aladinbank.id</t>
         </is>
       </c>
-      <c r="G37" s="8" t="inlineStr"/>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>https://aladinbank.id/themes/aladin/assets/favicon/apple-icon-152x152.png</t>
+        </is>
+      </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -3551,15 +3803,19 @@
       </c>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 152x152)</t>
         </is>
       </c>
       <c r="K37" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L37" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L37" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/aladin-syariah.png</t>
+        </is>
+      </c>
       <c r="M37" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -3567,7 +3823,7 @@
       </c>
       <c r="N37" s="6" t="inlineStr">
         <is>
-          <t>Digital sharia bank; ex-Bank Net Indonesia Syariah.</t>
+          <t>Digital sharia bank; ex-Bank Net Indonesia Syariah. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3854,11 @@
           <t>https://www.nobubank.com</t>
         </is>
       </c>
-      <c r="G38" s="8" t="inlineStr"/>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>https://storage.googleapis.com/web-nobu-prod/images/Logo_color.height-60.png</t>
+        </is>
+      </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -3611,15 +3871,19 @@
       </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>2.42:1 (horizontal, 145x60)</t>
         </is>
       </c>
       <c r="K38" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L38" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L38" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/nobu-bank.png</t>
+        </is>
+      </c>
       <c r="M38" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -3627,7 +3891,7 @@
       </c>
       <c r="N38" s="6" t="inlineStr">
         <is>
-          <t>Lippo group.</t>
+          <t>Lippo group. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3922,11 @@
           <t>https://www.bankmayapada.com</t>
         </is>
       </c>
-      <c r="G39" s="8" t="inlineStr"/>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>https://www.bankmayapada.com/images/headers/logo Admin white.png</t>
+        </is>
+      </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -3671,15 +3939,19 @@
       </c>
       <c r="J39" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>4.09:1 (horizontal, 3428x838)</t>
         </is>
       </c>
       <c r="K39" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L39" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L39" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/mayapada.png</t>
+        </is>
+      </c>
       <c r="M39" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -3687,7 +3959,7 @@
       </c>
       <c r="N39" s="6" t="inlineStr">
         <is>
-          <t>Candidate row; regulator check and asset sourcing outstanding.</t>
+          <t>Candidate row; regulator check and asset sourcing outstanding. Auto-sourced via brand-press.</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3990,11 @@
           <t>https://www.arthagraha.com</t>
         </is>
       </c>
-      <c r="G40" s="8" t="inlineStr"/>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>https://www.arthagraha.com/themes/arthagraha/assets/images/logo/Logo-BAG-samping-2-baris-hitam (1).png</t>
+        </is>
+      </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -3731,15 +4007,19 @@
       </c>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>5.67:1 (horizontal, 3467x611)</t>
         </is>
       </c>
       <c r="K40" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L40" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L40" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/artha-graha.png</t>
+        </is>
+      </c>
       <c r="M40" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -3747,7 +4027,7 @@
       </c>
       <c r="N40" s="6" t="inlineStr">
         <is>
-          <t>Candidate row; regulator check and asset sourcing outstanding.</t>
+          <t>Candidate row; regulator check and asset sourcing outstanding. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -3778,7 +4058,11 @@
           <t>https://www.bankmaspion.co.id</t>
         </is>
       </c>
-      <c r="G41" s="8" t="inlineStr"/>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>https://www.bankmaspion.co.id/assets/img/logo-bank-maspion.png</t>
+        </is>
+      </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -3791,15 +4075,19 @@
       </c>
       <c r="J41" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>9.20:1 (horizontal, 368x40)</t>
         </is>
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L41" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L41" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/maspion.png</t>
+        </is>
+      </c>
       <c r="M41" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -3807,7 +4095,7 @@
       </c>
       <c r="N41" s="6" t="inlineStr">
         <is>
-          <t>Kasikornbank (TH) controlled.</t>
+          <t>Kasikornbank (TH) controlled. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -3838,7 +4126,11 @@
           <t>https://www.bankbba.co.id</t>
         </is>
       </c>
-      <c r="G42" s="8" t="inlineStr"/>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>https://www.bankbba.co.id/bumiarta/assets/image/logo-bba.png</t>
+        </is>
+      </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -3851,15 +4143,19 @@
       </c>
       <c r="J42" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>6.58:1 (horizontal, 711x108)</t>
         </is>
       </c>
       <c r="K42" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L42" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L42" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bumi-arta.png</t>
+        </is>
+      </c>
       <c r="M42" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -3867,7 +4163,7 @@
       </c>
       <c r="N42" s="6" t="inlineStr">
         <is>
-          <t>Candidate row; regulator check and asset sourcing outstanding.</t>
+          <t>Candidate row; regulator check and asset sourcing outstanding. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -3898,7 +4194,11 @@
           <t>https://www.bankmestika.co.id</t>
         </is>
       </c>
-      <c r="G43" s="8" t="inlineStr"/>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/4f/c3/b6/4fc3b6a6-8678-b612-a28f-34f6a78f9842/AppIcon-0-0-1x_U007emarketing-0-6-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -3911,15 +4211,19 @@
       </c>
       <c r="J43" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K43" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L43" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L43" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/mestika.png</t>
+        </is>
+      </c>
       <c r="M43" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -3927,7 +4231,7 @@
       </c>
       <c r="N43" s="6" t="inlineStr">
         <is>
-          <t>Candidate row; regulator check and asset sourcing outstanding.</t>
+          <t>Candidate row; regulator check and asset sourcing outstanding. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -3958,7 +4262,11 @@
           <t>https://www.bankganesha.co.id</t>
         </is>
       </c>
-      <c r="G44" s="8" t="inlineStr"/>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>https://www.bankganesha.co.id/assets/images/logo-ayo-menabung-2024.png</t>
+        </is>
+      </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -3971,15 +4279,19 @@
       </c>
       <c r="J44" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.90:1 (horizontal, 1027x540)</t>
         </is>
       </c>
       <c r="K44" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L44" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L44" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/ganesha.png</t>
+        </is>
+      </c>
       <c r="M44" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -3987,7 +4299,7 @@
       </c>
       <c r="N44" s="6" t="inlineStr">
         <is>
-          <t>Candidate row; regulator check and asset sourcing outstanding.</t>
+          <t>Candidate row; regulator check and asset sourcing outstanding. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4330,11 @@
           <t>https://www.bankina.co.id</t>
         </is>
       </c>
-      <c r="G45" s="8" t="inlineStr"/>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>https://www.bankina.co.id/favicon.svg</t>
+        </is>
+      </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -4031,15 +4347,19 @@
       </c>
       <c r="J45" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 24x24)</t>
         </is>
       </c>
       <c r="K45" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L45" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L45" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/ina-perdana.svg</t>
+        </is>
+      </c>
       <c r="M45" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -4047,7 +4367,7 @@
       </c>
       <c r="N45" s="6" t="inlineStr">
         <is>
-          <t>Candidate row; regulator check and asset sourcing outstanding.</t>
+          <t>Candidate row; regulator check and asset sourcing outstanding. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4398,11 @@
           <t>https://www.victoriabank.co.id</t>
         </is>
       </c>
-      <c r="G46" s="8" t="inlineStr"/>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>https://victoriabank.co.id/images/logo2.png</t>
+        </is>
+      </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -4091,15 +4415,19 @@
       </c>
       <c r="J46" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>5.71:1 (horizontal, 800x140)</t>
         </is>
       </c>
       <c r="K46" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L46" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L46" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/victoria.png</t>
+        </is>
+      </c>
       <c r="M46" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -4107,7 +4435,7 @@
       </c>
       <c r="N46" s="6" t="inlineStr">
         <is>
-          <t>Candidate row; regulator check and asset sourcing outstanding.</t>
+          <t>Candidate row; regulator check and asset sourcing outstanding. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -4138,7 +4466,11 @@
           <t>https://www.bankcapital.co.id</t>
         </is>
       </c>
-      <c r="G47" s="8" t="inlineStr"/>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>https://www.bankcapital.co.id/files/logo-1737007262.png</t>
+        </is>
+      </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -4151,15 +4483,19 @@
       </c>
       <c r="J47" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>6.67:1 (horizontal, 1280x192)</t>
         </is>
       </c>
       <c r="K47" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L47" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L47" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/capital.png</t>
+        </is>
+      </c>
       <c r="M47" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -4167,7 +4503,7 @@
       </c>
       <c r="N47" s="6" t="inlineStr">
         <is>
-          <t>Candidate row; regulator check and asset sourcing outstanding.</t>
+          <t>Candidate row; regulator check and asset sourcing outstanding. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4654,11 @@
           <t>https://www.bankmas.co.id</t>
         </is>
       </c>
-      <c r="G50" s="8" t="inlineStr"/>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/e4/69/22/e46922e9-0aae-b94d-ca63-4c879a8fd67f/AppIcon-prod-0-0-1x_U007emarketing-0-11-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -4331,15 +4671,19 @@
       </c>
       <c r="J50" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K50" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L50" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L50" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/multiarta-sentosa.png</t>
+        </is>
+      </c>
       <c r="M50" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -4347,7 +4691,7 @@
       </c>
       <c r="N50" s="6" t="inlineStr">
         <is>
-          <t>Candidate row; regulator check and asset sourcing outstanding.</t>
+          <t>Candidate row; regulator check and asset sourcing outstanding. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -4378,7 +4722,11 @@
           <t>https://www.banksampoerna.com</t>
         </is>
       </c>
-      <c r="G51" s="8" t="inlineStr"/>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>https://statics.banksampoerna.com/assets/images/logo.png</t>
+        </is>
+      </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -4391,15 +4739,19 @@
       </c>
       <c r="J51" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>2.95:1 (horizontal, 233x79)</t>
         </is>
       </c>
       <c r="K51" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L51" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L51" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/sahabat-sampoerna.png</t>
+        </is>
+      </c>
       <c r="M51" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -4407,7 +4759,7 @@
       </c>
       <c r="N51" s="6" t="inlineStr">
         <is>
-          <t>Candidate row; regulator check and asset sourcing outstanding.</t>
+          <t>Candidate row; regulator check and asset sourcing outstanding. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -4498,7 +4850,11 @@
           <t>https://www.jtrustbank.co.id</t>
         </is>
       </c>
-      <c r="G53" s="8" t="inlineStr"/>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>https://www.jtrustbank.co.id/theme/Site/img/2024/logo-jtrust-call.png</t>
+        </is>
+      </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -4511,15 +4867,19 @@
       </c>
       <c r="J53" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>2.58:1 (horizontal, 1276x494)</t>
         </is>
       </c>
       <c r="K53" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L53" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L53" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/jtrust.png</t>
+        </is>
+      </c>
       <c r="M53" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -4527,7 +4887,7 @@
       </c>
       <c r="N53" s="6" t="inlineStr">
         <is>
-          <t>J Trust Group (JP).</t>
+          <t>J Trust Group (JP). Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4918,11 @@
           <t>https://www.bankmantap.co.id</t>
         </is>
       </c>
-      <c r="G54" s="8" t="inlineStr"/>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/10/de/b1/10deb16e-983b-cc28-d587-aea017840775/AppIcon-0-0-1x_U007emarketing-0-7-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -4571,15 +4935,19 @@
       </c>
       <c r="J54" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K54" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L54" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L54" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/mandiri-taspen.png</t>
+        </is>
+      </c>
       <c r="M54" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -4587,7 +4955,7 @@
       </c>
       <c r="N54" s="6" t="inlineStr">
         <is>
-          <t>Mandiri group.</t>
+          <t>Mandiri group. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -4738,7 +5106,11 @@
           <t>https://www.qnb.co.id</t>
         </is>
       </c>
-      <c r="G57" s="8" t="inlineStr"/>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>https://www.qnb.co.id/site/default/master/_/asset/id.co.qnb:00000198819655d0/img/logo.png</t>
+        </is>
+      </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -4751,15 +5123,19 @@
       </c>
       <c r="J57" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>3.20:1 (horizontal, 307x96)</t>
         </is>
       </c>
       <c r="K57" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L57" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L57" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/qnb-indonesia.png</t>
+        </is>
+      </c>
       <c r="M57" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -4767,7 +5143,7 @@
       </c>
       <c r="N57" s="6" t="inlineStr">
         <is>
-          <t>Candidate row; regulator check and asset sourcing outstanding.</t>
+          <t>Candidate row; regulator check and asset sourcing outstanding. Auto-sourced via brand-press.</t>
         </is>
       </c>
     </row>
@@ -4858,7 +5234,11 @@
           <t>https://www.shinhan.co.id</t>
         </is>
       </c>
-      <c r="G59" s="8" t="inlineStr"/>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/6b/fc/67/6bfc6783-da45-1370-fcdb-155c1a890557/AppIcon-0-0-1x_U007emarketing-0-2-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -4871,15 +5251,19 @@
       </c>
       <c r="J59" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K59" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L59" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L59" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/shinhan-indonesia.png</t>
+        </is>
+      </c>
       <c r="M59" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -4887,7 +5271,7 @@
       </c>
       <c r="N59" s="6" t="inlineStr">
         <is>
-          <t>Candidate row; regulator check and asset sourcing outstanding.</t>
+          <t>Candidate row; regulator check and asset sourcing outstanding. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -4918,7 +5302,11 @@
           <t>https://www.hanabank.co.id</t>
         </is>
       </c>
-      <c r="G60" s="8" t="inlineStr"/>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/37/9b/a9/379ba998-ca47-5b3d-8239-a2c22fe368df/AppIcon-0-0-1x_U007emarketing-0-8-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -4931,15 +5319,19 @@
       </c>
       <c r="J60" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K60" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L60" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L60" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/keb-hana.png</t>
+        </is>
+      </c>
       <c r="M60" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -4947,7 +5339,7 @@
       </c>
       <c r="N60" s="6" t="inlineStr">
         <is>
-          <t>Candidate row; regulator check and asset sourcing outstanding.</t>
+          <t>Candidate row; regulator check and asset sourcing outstanding. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -4978,7 +5370,11 @@
           <t>https://www.ibk.co.id</t>
         </is>
       </c>
-      <c r="G61" s="8" t="inlineStr"/>
+      <c r="G61" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/4c/51/55/4c51552b-8970-ed0e-58ec-1eda98a9ba6d/AppIconIndo-0-0-1x_U007emarketing-0-0-0-5-0-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -4991,15 +5387,19 @@
       </c>
       <c r="J61" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K61" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L61" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L61" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/ibk-indonesia.png</t>
+        </is>
+      </c>
       <c r="M61" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -5007,7 +5407,7 @@
       </c>
       <c r="N61" s="6" t="inlineStr">
         <is>
-          <t>Candidate row; regulator check and asset sourcing outstanding.</t>
+          <t>Candidate row; regulator check and asset sourcing outstanding. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -5038,7 +5438,11 @@
           <t>https://www.ctbcbank.co.id</t>
         </is>
       </c>
-      <c r="G62" s="8" t="inlineStr"/>
+      <c r="G62" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/bb/45/46/bb4546cf-4831-a225-85c8-faa36eeaf456/AppIcon-0-0-1x_U007emarketing-0-7-85-220.jpeg/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -5051,15 +5455,19 @@
       </c>
       <c r="J62" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K62" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L62" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L62" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/ctbc-indonesia.png</t>
+        </is>
+      </c>
       <c r="M62" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -5067,7 +5475,7 @@
       </c>
       <c r="N62" s="6" t="inlineStr">
         <is>
-          <t>Candidate row; regulator check and asset sourcing outstanding.</t>
+          <t>Candidate row; regulator check and asset sourcing outstanding. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5618,11 @@
           <t>https://www.perdania.co.id</t>
         </is>
       </c>
-      <c r="G65" s="8" t="inlineStr"/>
+      <c r="G65" s="8" t="inlineStr">
+        <is>
+          <t>https://www.perdania.co.id/images/resona-logo-bg.svg</t>
+        </is>
+      </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -5223,15 +5635,19 @@
       </c>
       <c r="J65" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1:1.27 (vertical, 760x966)</t>
         </is>
       </c>
       <c r="K65" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L65" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L65" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/resona-perdania.svg</t>
+        </is>
+      </c>
       <c r="M65" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -5239,7 +5655,7 @@
       </c>
       <c r="N65" s="6" t="inlineStr">
         <is>
-          <t>Candidate row; regulator check and asset sourcing outstanding.</t>
+          <t>Candidate row; regulator check and asset sourcing outstanding. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5742,11 @@
       </c>
       <c r="E67" s="8" t="inlineStr"/>
       <c r="F67" s="8" t="inlineStr"/>
-      <c r="G67" s="8" t="inlineStr"/>
+      <c r="G67" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/7b/44/8f/7b448fcc-a91a-ac74-0be8-4426f652d51a/AppIcon-0-0-1x_U007emarketing-0-6-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -5339,15 +5759,19 @@
       </c>
       <c r="J67" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K67" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L67" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L67" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bnp-paribas-indonesia.png</t>
+        </is>
+      </c>
       <c r="M67" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -5355,7 +5779,7 @@
       </c>
       <c r="N67" s="6" t="inlineStr">
         <is>
-          <t>Wholesale/corporate only - confirm it belongs in a consumer payment UI.</t>
+          <t>Wholesale/corporate only - confirm it belongs in a consumer payment UI. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -5386,7 +5810,11 @@
           <t>https://www.dbs.id</t>
         </is>
       </c>
-      <c r="G68" s="8" t="inlineStr"/>
+      <c r="G68" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/d1/4e/17/d14e179c-2251-4a9a-b83a-dd55bf08755f/AppIcon-0-0-1x_U007emarketing-0-8-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -5399,15 +5827,19 @@
       </c>
       <c r="J68" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K68" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L68" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L68" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/dbs-indonesia.png</t>
+        </is>
+      </c>
       <c r="M68" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -5415,7 +5847,7 @@
       </c>
       <c r="N68" s="6" t="inlineStr">
         <is>
-          <t>Local arm of DBS - distinct row from banks/sea/sg/dbs.</t>
+          <t>Local arm of DBS - distinct row from banks/sea/sg/dbs. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -5502,7 +5934,11 @@
           <t>https://www.sc.com/id</t>
         </is>
       </c>
-      <c r="G70" s="8" t="inlineStr"/>
+      <c r="G70" s="8" t="inlineStr">
+        <is>
+          <t>https://av.sc.com/id/content/images/content/images/cropped-512x512-new-200x200.png</t>
+        </is>
+      </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -5515,15 +5951,19 @@
       </c>
       <c r="J70" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 200x200)</t>
         </is>
       </c>
       <c r="K70" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L70" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L70" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/standard-chartered-indonesia.png</t>
+        </is>
+      </c>
       <c r="M70" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -5531,7 +5971,7 @@
       </c>
       <c r="N70" s="6" t="inlineStr">
         <is>
-          <t>Local arm - distinct row from banks/international/standard-chartered.</t>
+          <t>Local arm - distinct row from banks/international/standard-chartered. Auto-sourced via brand-press.</t>
         </is>
       </c>
     </row>
@@ -5614,7 +6054,11 @@
       </c>
       <c r="E72" s="8" t="inlineStr"/>
       <c r="F72" s="8" t="inlineStr"/>
-      <c r="G72" s="8" t="inlineStr"/>
+      <c r="G72" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/ea/0d/8b/ea0d8bf5-1c1b-9518-b7dd-26ca2d06adab/AppIcon-1x_U007emarketing-0-11-0-85-220-0.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -5627,15 +6071,19 @@
       </c>
       <c r="J72" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K72" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L72" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L72" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/commonwealth.png</t>
+        </is>
+      </c>
       <c r="M72" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -5643,7 +6091,7 @@
       </c>
       <c r="N72" s="6" t="inlineStr">
         <is>
-          <t>OCBC acquired and has been merging this entity into OCBC Indonesia - brand likely retired. Recommend moving to Flagged - Excluded once confirmed.</t>
+          <t>OCBC acquired and has been merging this entity into OCBC Indonesia - brand likely retired. Recommend moving to Flagged - Excluded once confirmed. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -5674,7 +6122,11 @@
           <t>https://www.bcasyariah.co.id</t>
         </is>
       </c>
-      <c r="G73" s="8" t="inlineStr"/>
+      <c r="G73" s="8" t="inlineStr">
+        <is>
+          <t>https://www.bcasyariah.co.id/cfind/source/images/logo-bcas-full-color.png</t>
+        </is>
+      </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -5687,15 +6139,19 @@
       </c>
       <c r="J73" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>5.86:1 (horizontal, 1941x331)</t>
         </is>
       </c>
       <c r="K73" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L73" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L73" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bca-syariah.png</t>
+        </is>
+      </c>
       <c r="M73" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -5703,7 +6159,7 @@
       </c>
       <c r="N73" s="6" t="inlineStr">
         <is>
-          <t>Candidate row; regulator check and asset sourcing outstanding.</t>
+          <t>Candidate row; regulator check and asset sourcing outstanding. Auto-sourced via brand-press.</t>
         </is>
       </c>
     </row>
@@ -5734,7 +6190,11 @@
           <t>https://www.megasyariah.co.id</t>
         </is>
       </c>
-      <c r="G74" s="8" t="inlineStr"/>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t>https://www.megasyariah.co.id/bms-new/asset/images/LogoColor.svg</t>
+        </is>
+      </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -5747,15 +6207,19 @@
       </c>
       <c r="J74" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.34:1 (horizontal, 94x70)</t>
         </is>
       </c>
       <c r="K74" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L74" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L74" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/mega-syariah.svg</t>
+        </is>
+      </c>
       <c r="M74" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -5763,7 +6227,7 @@
       </c>
       <c r="N74" s="6" t="inlineStr">
         <is>
-          <t>CT Corp group.</t>
+          <t>CT Corp group. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -5854,7 +6318,11 @@
           <t>https://www.bjbsyariah.co.id</t>
         </is>
       </c>
-      <c r="G76" s="8" t="inlineStr"/>
+      <c r="G76" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/05/f7/04/05f70408-4a27-1bc5-9224-d5c5ebbda2d5/AppIcon-0-0-1x_U007emarketing-0-7-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -5867,15 +6335,19 @@
       </c>
       <c r="J76" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K76" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L76" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L76" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bjb-syariah.png</t>
+        </is>
+      </c>
       <c r="M76" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -5883,7 +6355,7 @@
       </c>
       <c r="N76" s="6" t="inlineStr">
         <is>
-          <t>Candidate row; regulator check and asset sourcing outstanding.</t>
+          <t>Candidate row; regulator check and asset sourcing outstanding. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6498,11 @@
           <t>https://www.bankjateng.co.id</t>
         </is>
       </c>
-      <c r="G79" s="8" t="inlineStr"/>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>https://www.bankjateng.co.id/media/Logo_Bank_Jateng_Putih_Transparan.png</t>
+        </is>
+      </c>
       <c r="H79" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -6039,15 +6515,19 @@
       </c>
       <c r="J79" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.98:1 (horizontal, 2143x1084)</t>
         </is>
       </c>
       <c r="K79" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L79" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L79" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bank-jateng.png</t>
+        </is>
+      </c>
       <c r="M79" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -6055,7 +6535,7 @@
       </c>
       <c r="N79" s="6" t="inlineStr">
         <is>
-          <t>Regional development bank (Central Java).</t>
+          <t>Regional development bank (Central Java). Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -6086,7 +6566,11 @@
           <t>https://www.bpddiy.co.id</t>
         </is>
       </c>
-      <c r="G80" s="8" t="inlineStr"/>
+      <c r="G80" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/df/9c/4c/df9c4c4d-aff5-5fe0-e72c-aa99706717f9/AppIcon-0-0-1x_U007emarketing-0-11-0-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H80" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -6099,15 +6583,19 @@
       </c>
       <c r="J80" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K80" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L80" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L80" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bank-bpd-diy.png</t>
+        </is>
+      </c>
       <c r="M80" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -6115,7 +6603,7 @@
       </c>
       <c r="N80" s="6" t="inlineStr">
         <is>
-          <t>Regional development bank (Yogyakarta).</t>
+          <t>Regional development bank (Yogyakarta). Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6634,11 @@
           <t>https://www.bankbanten.co.id</t>
         </is>
       </c>
-      <c r="G81" s="8" t="inlineStr"/>
+      <c r="G81" s="8" t="inlineStr">
+        <is>
+          <t>https://www.bankbanten.co.id/assets/uploads/2026/08/1_LOGO-Baru-Bank-Banten_2026.png</t>
+        </is>
+      </c>
       <c r="H81" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -6159,15 +6651,19 @@
       </c>
       <c r="J81" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>2.58:1 (horizontal, 1000x388)</t>
         </is>
       </c>
       <c r="K81" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L81" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L81" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bank-banten.png</t>
+        </is>
+      </c>
       <c r="M81" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -6175,7 +6671,7 @@
       </c>
       <c r="N81" s="6" t="inlineStr">
         <is>
-          <t>Regional development bank (Banten). Has had capital difficulties - confirm operating status.</t>
+          <t>Regional development bank (Banten). Has had capital difficulties - confirm operating status. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6702,11 @@
           <t>https://www.banksumut.co.id</t>
         </is>
       </c>
-      <c r="G82" s="8" t="inlineStr"/>
+      <c r="G82" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/ac/29/ba/ac29baf3-fb6c-98a8-fb11-6bb9e01824ac/AppIcon-0-0-1x_U007emarketing-0-11-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H82" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -6219,15 +6719,19 @@
       </c>
       <c r="J82" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K82" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L82" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L82" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bank-sumut.png</t>
+        </is>
+      </c>
       <c r="M82" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -6235,7 +6739,7 @@
       </c>
       <c r="N82" s="6" t="inlineStr">
         <is>
-          <t>Regional development bank (North Sumatra).</t>
+          <t>Regional development bank (North Sumatra). Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6770,11 @@
           <t>https://www.banknagari.co.id</t>
         </is>
       </c>
-      <c r="G83" s="8" t="inlineStr"/>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/6c/92/39/6c923967-5b8b-89ad-92c6-6b3e60dda57a/AppIcon-0-0-1x_U007emarketing-0-8-0-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H83" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -6279,15 +6787,19 @@
       </c>
       <c r="J83" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K83" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L83" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L83" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bank-nagari.png</t>
+        </is>
+      </c>
       <c r="M83" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -6295,7 +6807,7 @@
       </c>
       <c r="N83" s="6" t="inlineStr">
         <is>
-          <t>Regional development bank (West Sumatra).</t>
+          <t>Regional development bank (West Sumatra). Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6898,11 @@
           <t>https://www.bankjambi.co.id</t>
         </is>
       </c>
-      <c r="G85" s="8" t="inlineStr"/>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/32/35/ef/3235ef96-6161-3205-e436-74ada10681df/AppIcon-0-0-1x_U007emarketing-0-11-0-85-220.jpeg/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H85" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -6399,15 +6915,19 @@
       </c>
       <c r="J85" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K85" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L85" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L85" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bank-jambi.png</t>
+        </is>
+      </c>
       <c r="M85" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -6415,7 +6935,7 @@
       </c>
       <c r="N85" s="6" t="inlineStr">
         <is>
-          <t>Regional development bank (Jambi).</t>
+          <t>Regional development bank (Jambi). Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -6446,7 +6966,11 @@
           <t>https://www.banksumselbabel.com</t>
         </is>
       </c>
-      <c r="G86" s="8" t="inlineStr"/>
+      <c r="G86" s="8" t="inlineStr">
+        <is>
+          <t>https://www.banksumselbabel.com/img/logo.png</t>
+        </is>
+      </c>
       <c r="H86" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -6459,15 +6983,19 @@
       </c>
       <c r="J86" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>3.80:1 (horizontal, 1141x300)</t>
         </is>
       </c>
       <c r="K86" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L86" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L86" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bank-sumsel-babel.png</t>
+        </is>
+      </c>
       <c r="M86" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -6475,7 +7003,7 @@
       </c>
       <c r="N86" s="6" t="inlineStr">
         <is>
-          <t>Regional development bank (South Sumatra / Bangka Belitung).</t>
+          <t>Regional development bank (South Sumatra / Bangka Belitung). Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -6506,7 +7034,11 @@
           <t>https://www.bankbengkulu.co.id</t>
         </is>
       </c>
-      <c r="G87" s="8" t="inlineStr"/>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/15/46/ed/1546ede8-964c-6d16-968c-7cb6415b04f8/AppIcon-0-0-1x_U007emarketing-0-8-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H87" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -6519,15 +7051,19 @@
       </c>
       <c r="J87" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K87" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L87" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L87" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bank-bengkulu.png</t>
+        </is>
+      </c>
       <c r="M87" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -6535,7 +7071,7 @@
       </c>
       <c r="N87" s="6" t="inlineStr">
         <is>
-          <t>Regional development bank (Bengkulu).</t>
+          <t>Regional development bank (Bengkulu). Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -6566,7 +7102,11 @@
           <t>https://www.banklampung.co.id</t>
         </is>
       </c>
-      <c r="G88" s="8" t="inlineStr"/>
+      <c r="G88" s="8" t="inlineStr">
+        <is>
+          <t>https://www.banklampung.co.id/assets/images/banklampung/meta_default.png</t>
+        </is>
+      </c>
       <c r="H88" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -6579,15 +7119,19 @@
       </c>
       <c r="J88" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.91:1 (horizontal, 1200x628)</t>
         </is>
       </c>
       <c r="K88" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L88" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L88" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bank-lampung.png</t>
+        </is>
+      </c>
       <c r="M88" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -6595,7 +7139,7 @@
       </c>
       <c r="N88" s="6" t="inlineStr">
         <is>
-          <t>Regional development bank (Lampung).</t>
+          <t>Regional development bank (Lampung). Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -6626,7 +7170,11 @@
           <t>https://www.bankaceh.co.id</t>
         </is>
       </c>
-      <c r="G89" s="8" t="inlineStr"/>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t>https://bankaceh.co.id/wp-content/uploads/2024/05/Logo-Bank-Aceh-Putih.png</t>
+        </is>
+      </c>
       <c r="H89" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -6639,15 +7187,19 @@
       </c>
       <c r="J89" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>3.81:1 (horizontal, 2402x630)</t>
         </is>
       </c>
       <c r="K89" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L89" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L89" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bank-aceh-syariah.png</t>
+        </is>
+      </c>
       <c r="M89" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -6655,7 +7207,7 @@
       </c>
       <c r="N89" s="6" t="inlineStr">
         <is>
-          <t>Regional development bank (Aceh); converted to sharia in 2016 - do not use the pre-conversion asset.</t>
+          <t>Regional development bank (Aceh); converted to sharia in 2016 - do not use the pre-conversion asset. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -6686,7 +7238,11 @@
           <t>https://www.bankkalbar.co.id</t>
         </is>
       </c>
-      <c r="G90" s="8" t="inlineStr"/>
+      <c r="G90" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/5a/ed/c3/5aedc3fc-294a-a873-9e49-1bd5aa5986e0/AppIcon-BKalbar-0-0-1x_U007emarketing-0-11-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H90" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -6699,15 +7255,19 @@
       </c>
       <c r="J90" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K90" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L90" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L90" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bank-kalbar.png</t>
+        </is>
+      </c>
       <c r="M90" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -6715,7 +7275,7 @@
       </c>
       <c r="N90" s="6" t="inlineStr">
         <is>
-          <t>Regional development bank (West Kalimantan).</t>
+          <t>Regional development bank (West Kalimantan). Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -6746,7 +7306,11 @@
           <t>https://www.bankkalsel.co.id</t>
         </is>
       </c>
-      <c r="G91" s="8" t="inlineStr"/>
+      <c r="G91" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/89/53/b7/8953b785-9695-048e-5692-d2a92aef8f83/AppIcon-0-0-1x_U007emarketing-0-7-0-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H91" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -6759,15 +7323,19 @@
       </c>
       <c r="J91" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K91" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L91" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L91" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bank-kalsel.png</t>
+        </is>
+      </c>
       <c r="M91" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -6775,7 +7343,7 @@
       </c>
       <c r="N91" s="6" t="inlineStr">
         <is>
-          <t>Regional development bank (South Kalimantan).</t>
+          <t>Regional development bank (South Kalimantan). Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -6806,7 +7374,11 @@
           <t>https://www.bankkalteng.co.id</t>
         </is>
       </c>
-      <c r="G92" s="8" t="inlineStr"/>
+      <c r="G92" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/49/d1/42/49d1428d-68d0-c5eb-9e62-1fb8a69796a6/AppIcon-0-0-1x_U007emarketing-0-8-0-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H92" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -6819,15 +7391,19 @@
       </c>
       <c r="J92" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K92" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L92" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L92" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bank-kalteng.png</t>
+        </is>
+      </c>
       <c r="M92" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -6835,7 +7411,7 @@
       </c>
       <c r="N92" s="6" t="inlineStr">
         <is>
-          <t>Regional development bank (Central Kalimantan).</t>
+          <t>Regional development bank (Central Kalimantan). Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -6926,7 +7502,11 @@
           <t>https://www.banksulselbar.co.id</t>
         </is>
       </c>
-      <c r="G94" s="8" t="inlineStr"/>
+      <c r="G94" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/41/aa/aa/41aaaad8-12f2-3b0f-7336-75fc3dedf3e6/AppIcon-0-0-1x_U007emarketing-0-7-0-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H94" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -6939,15 +7519,19 @@
       </c>
       <c r="J94" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K94" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L94" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L94" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bank-sulselbar.png</t>
+        </is>
+      </c>
       <c r="M94" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -6955,7 +7539,7 @@
       </c>
       <c r="N94" s="6" t="inlineStr">
         <is>
-          <t>Regional development bank (South / West Sulawesi).</t>
+          <t>Regional development bank (South / West Sulawesi). Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -7046,7 +7630,11 @@
           <t>https://www.banksulteng.co.id</t>
         </is>
       </c>
-      <c r="G96" s="8" t="inlineStr"/>
+      <c r="G96" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/cf/df/68/cfdf6848-e3f7-6fd2-162c-104c9375c9a8/AppIcon-0-0-1x_U007emarketing-0-7-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H96" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -7059,15 +7647,19 @@
       </c>
       <c r="J96" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K96" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L96" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L96" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bank-sulteng.png</t>
+        </is>
+      </c>
       <c r="M96" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -7075,7 +7667,7 @@
       </c>
       <c r="N96" s="6" t="inlineStr">
         <is>
-          <t>Regional development bank (Central Sulawesi).</t>
+          <t>Regional development bank (Central Sulawesi). Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7698,11 @@
           <t>https://www.banksultra.co.id</t>
         </is>
       </c>
-      <c r="G97" s="8" t="inlineStr"/>
+      <c r="G97" s="8" t="inlineStr">
+        <is>
+          <t>https://banksultra.co.id/logo_banksultra7.svg</t>
+        </is>
+      </c>
       <c r="H97" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -7119,15 +7715,19 @@
       </c>
       <c r="J97" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>4.29:1 (horizontal, 9000x2100)</t>
         </is>
       </c>
       <c r="K97" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L97" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L97" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bank-sultra.svg</t>
+        </is>
+      </c>
       <c r="M97" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -7135,7 +7735,7 @@
       </c>
       <c r="N97" s="6" t="inlineStr">
         <is>
-          <t>Regional development bank (Southeast Sulawesi).</t>
+          <t>Regional development bank (Southeast Sulawesi). Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -7226,7 +7826,11 @@
           <t>https://www.bankntbsyariah.co.id</t>
         </is>
       </c>
-      <c r="G99" s="8" t="inlineStr"/>
+      <c r="G99" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/55/59/06/5559061d-85a6-551f-79ab-e791e6c345cd/AppIcon-0-0-1x_U007emarketing-0-8-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H99" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -7239,15 +7843,19 @@
       </c>
       <c r="J99" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K99" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L99" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L99" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bank-ntb-syariah.png</t>
+        </is>
+      </c>
       <c r="M99" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -7255,7 +7863,7 @@
       </c>
       <c r="N99" s="6" t="inlineStr">
         <is>
-          <t>Regional development bank (West Nusa Tenggara); converted to sharia in 2018.</t>
+          <t>Regional development bank (West Nusa Tenggara); converted to sharia in 2018. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -7286,7 +7894,11 @@
           <t>https://www.bpdntt.co.id</t>
         </is>
       </c>
-      <c r="G100" s="8" t="inlineStr"/>
+      <c r="G100" s="8" t="inlineStr">
+        <is>
+          <t>https://www.bpdntt.co.id/images/logo_ntt.png</t>
+        </is>
+      </c>
       <c r="H100" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -7299,15 +7911,19 @@
       </c>
       <c r="J100" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.38:1 (horizontal, 1486x1080)</t>
         </is>
       </c>
       <c r="K100" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L100" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L100" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bank-ntt.png</t>
+        </is>
+      </c>
       <c r="M100" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -7315,7 +7931,7 @@
       </c>
       <c r="N100" s="6" t="inlineStr">
         <is>
-          <t>Regional development bank (East Nusa Tenggara).</t>
+          <t>Regional development bank (East Nusa Tenggara). Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7962,11 @@
           <t>https://www.bankmalukumalut.co.id</t>
         </is>
       </c>
-      <c r="G101" s="8" t="inlineStr"/>
+      <c r="G101" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/da/64/b1/da64b10e-abd8-f89c-8b1e-878bc9ebc6e8/AppIcon-0-0-1x_U007emarketing-0-8-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H101" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -7359,15 +7979,19 @@
       </c>
       <c r="J101" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K101" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L101" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L101" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bank-maluku-malut.png</t>
+        </is>
+      </c>
       <c r="M101" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -7375,7 +7999,7 @@
       </c>
       <c r="N101" s="6" t="inlineStr">
         <is>
-          <t>Regional development bank (Maluku / North Maluku).</t>
+          <t>Regional development bank (Maluku / North Maluku). Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -7406,7 +8030,11 @@
           <t>https://www.bankpapua.co.id</t>
         </is>
       </c>
-      <c r="G102" s="8" t="inlineStr"/>
+      <c r="G102" s="8" t="inlineStr">
+        <is>
+          <t>https://www.bankpapua.co.id/asset/images/6e4fe9e6704a107c8730e829aa5732d3.png</t>
+        </is>
+      </c>
       <c r="H102" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -7419,15 +8047,19 @@
       </c>
       <c r="J102" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>5.54:1 (horizontal, 875x158)</t>
         </is>
       </c>
       <c r="K102" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L102" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L102" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/indo/bank-papua.png</t>
+        </is>
+      </c>
       <c r="M102" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -7435,7 +8067,7 @@
       </c>
       <c r="N102" s="6" t="inlineStr">
         <is>
-          <t>Regional development bank (Papua).</t>
+          <t>Regional development bank (Papua). Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -7466,7 +8098,11 @@
           <t>https://www.gopay.co.id</t>
         </is>
       </c>
-      <c r="G103" s="8" t="inlineStr"/>
+      <c r="G103" s="8" t="inlineStr">
+        <is>
+          <t>https://gopay-website.al-gp-id-p.cdn.gtflabs.io/assets/img/homepage/apple-touch-icon.png</t>
+        </is>
+      </c>
       <c r="H103" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -7479,15 +8115,19 @@
       </c>
       <c r="J103" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 180x180)</t>
         </is>
       </c>
       <c r="K103" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L103" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L103" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/indo/gopay.png</t>
+        </is>
+      </c>
       <c r="M103" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -7495,7 +8135,7 @@
       </c>
       <c r="N103" s="6" t="inlineStr">
         <is>
-          <t>Top-5 wallet (GoTo group). Verify: BI e-money licence list.</t>
+          <t>Top-5 wallet (GoTo group). Verify: BI e-money licence list. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -7526,7 +8166,11 @@
           <t>https://www.ovo.id</t>
         </is>
       </c>
-      <c r="G104" s="8" t="inlineStr"/>
+      <c r="G104" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/83/d6/2e/83d62e61-b4d9-e268-8648-5541e0f9c487/AppIcon-0-0-1x_U007emarketing-0-8-0-sRGB-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H104" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -7539,15 +8183,19 @@
       </c>
       <c r="J104" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K104" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L104" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L104" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/indo/ovo.png</t>
+        </is>
+      </c>
       <c r="M104" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -7555,7 +8203,7 @@
       </c>
       <c r="N104" s="6" t="inlineStr">
         <is>
-          <t>Top-5 wallet (Grab-controlled).</t>
+          <t>Top-5 wallet (Grab-controlled). Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -7586,7 +8234,11 @@
           <t>https://www.dana.id</t>
         </is>
       </c>
-      <c r="G105" s="8" t="inlineStr"/>
+      <c r="G105" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/98/77/e5/9877e539-8667-f74e-794e-275559d6bb4c/AppIcon-0-0-1x_U007ephone-0-1-0-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H105" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -7599,15 +8251,19 @@
       </c>
       <c r="J105" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K105" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L105" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L105" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/indo/dana.png</t>
+        </is>
+      </c>
       <c r="M105" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -7615,7 +8271,7 @@
       </c>
       <c r="N105" s="6" t="inlineStr">
         <is>
-          <t>Top-5 wallet (Ant Group backed).</t>
+          <t>Top-5 wallet (Ant Group backed). Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -7646,7 +8302,11 @@
           <t>https://shopee.co.id</t>
         </is>
       </c>
-      <c r="G106" s="8" t="inlineStr"/>
+      <c r="G106" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/0b/c4/2f/0bc42f58-a172-dc71-1133-50f43319be42/AppIcon-1x_U007ephone-0-1-0-0-85-220-0.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H106" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -7659,15 +8319,19 @@
       </c>
       <c r="J106" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K106" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L106" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L106" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/indo/shopeepay.png</t>
+        </is>
+      </c>
       <c r="M106" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -7675,7 +8339,7 @@
       </c>
       <c r="N106" s="6" t="inlineStr">
         <is>
-          <t>Top-5 wallet. Distinguish from Shopee marketplace logo (separate ecommerce row).</t>
+          <t>Top-5 wallet. Distinguish from Shopee marketplace logo (separate ecommerce row). Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -7706,7 +8370,11 @@
           <t>https://www.linkaja.id</t>
         </is>
       </c>
-      <c r="G107" s="8" t="inlineStr"/>
+      <c r="G107" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/17/02/54/17025479-db8a-d0c8-b038-72b4906a8583/AppIconRamadhan-1x_U007emarketing-0-11-0-85-220-0.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H107" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -7719,15 +8387,19 @@
       </c>
       <c r="J107" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K107" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L107" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L107" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/indo/linkaja.png</t>
+        </is>
+      </c>
       <c r="M107" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -7735,7 +8407,7 @@
       </c>
       <c r="N107" s="6" t="inlineStr">
         <is>
-          <t>Top-5 wallet (Telkomsel/state-linked).</t>
+          <t>Top-5 wallet (Telkomsel/state-linked). Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -7766,7 +8438,11 @@
           <t>https://astrapay.com</t>
         </is>
       </c>
-      <c r="G108" s="8" t="inlineStr"/>
+      <c r="G108" s="8" t="inlineStr">
+        <is>
+          <t>https://astrapay.com/static-assets/images/navigation/astrapay-blue-right.svg</t>
+        </is>
+      </c>
       <c r="H108" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -7779,15 +8455,19 @@
       </c>
       <c r="J108" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1:1.01 (square, 197x198)</t>
         </is>
       </c>
       <c r="K108" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L108" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L108" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/indo/astrapay.svg</t>
+        </is>
+      </c>
       <c r="M108" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -7795,7 +8475,7 @@
       </c>
       <c r="N108" s="6" t="inlineStr">
         <is>
-          <t>Astra group.</t>
+          <t>Astra group. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -7826,7 +8506,11 @@
           <t>https://www.isaku.id</t>
         </is>
       </c>
-      <c r="G109" s="8" t="inlineStr"/>
+      <c r="G109" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/40/72/42/407242fe-1e3e-6678-fd80-abd00703ae30/AppIcon-0-0-1x_U007emarketing-0-6-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H109" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -7839,15 +8523,19 @@
       </c>
       <c r="J109" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K109" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L109" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L109" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/indo/i-saku.png</t>
+        </is>
+      </c>
       <c r="M109" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -7855,7 +8543,7 @@
       </c>
       <c r="N109" s="6" t="inlineStr">
         <is>
-          <t>Indomaret-affiliated wallet. Confirm current operating status.</t>
+          <t>Indomaret-affiliated wallet. Confirm current operating status. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -7886,7 +8574,11 @@
           <t>https://www.doku.com</t>
         </is>
       </c>
-      <c r="G110" s="8" t="inlineStr"/>
+      <c r="G110" s="8" t="inlineStr">
+        <is>
+          <t>https://cdn.prod.website-files.com/674ab654de930b217c6389c1/6756a9f7ba44cad5543f87e2_doku-logo-red.svg</t>
+        </is>
+      </c>
       <c r="H110" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -7899,15 +8591,19 @@
       </c>
       <c r="J110" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 500x500)</t>
         </is>
       </c>
       <c r="K110" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L110" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L110" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/indo/doku.svg</t>
+        </is>
+      </c>
       <c r="M110" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -7915,7 +8611,7 @@
       </c>
       <c r="N110" s="6" t="inlineStr">
         <is>
-          <t>Payment gateway + wallet.</t>
+          <t>Payment gateway + wallet. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -7946,7 +8642,11 @@
           <t>https://flip.id</t>
         </is>
       </c>
-      <c r="G111" s="8" t="inlineStr"/>
+      <c r="G111" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/87/63/b5/8763b5c1-e0b1-0823-ddb0-ce8b5d214587/AppIconTemanHemat-0-0-1x_U007epad-0-1-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H111" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -7959,15 +8659,19 @@
       </c>
       <c r="J111" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K111" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L111" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L111" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/indo/flip.png</t>
+        </is>
+      </c>
       <c r="M111" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -7975,7 +8679,7 @@
       </c>
       <c r="N111" s="6" t="inlineStr">
         <is>
-          <t>Transfer/remittance app.</t>
+          <t>Transfer/remittance app. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8710,11 @@
           <t>https://www.jenius.com</t>
         </is>
       </c>
-      <c r="G112" s="8" t="inlineStr"/>
+      <c r="G112" s="8" t="inlineStr">
+        <is>
+          <t>https://www.jenius.com/assets/img/brand/logo_jenius-blue.svg</t>
+        </is>
+      </c>
       <c r="H112" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -8019,15 +8727,19 @@
       </c>
       <c r="J112" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>3.88:1 (horizontal, 163x42)</t>
         </is>
       </c>
       <c r="K112" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L112" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L112" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/indo/jenius-pay.svg</t>
+        </is>
+      </c>
       <c r="M112" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -8035,7 +8747,7 @@
       </c>
       <c r="N112" s="6" t="inlineStr">
         <is>
-          <t>Digital brand of Bank SMBC Indonesia (ex-BTPN); refreshed alongside the Oct 2024 rebrand - use post-rebrand asset only.</t>
+          <t>Digital brand of Bank SMBC Indonesia (ex-BTPN); refreshed alongside the Oct 2024 rebrand - use post-rebrand asset only. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8822,11 @@
           <t>https://alfamart.co.id</t>
         </is>
       </c>
-      <c r="G114" s="8" t="inlineStr"/>
+      <c r="G114" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/92/da/4e/92da4e34-1e16-7573-8391-373b049442f8/AppIcon-0-0-1x_U007emarketing-0-8-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H114" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -8123,15 +8839,19 @@
       </c>
       <c r="J114" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K114" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L114" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L114" s="8" t="inlineStr">
+        <is>
+          <t>assets/minimarkets/indo/alfamart.png</t>
+        </is>
+      </c>
       <c r="M114" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -8139,7 +8859,7 @@
       </c>
       <c r="N114" s="6" t="inlineStr">
         <is>
-          <t>Market leader. Also now operates acquired Lawson Indonesia stores.</t>
+          <t>Market leader. Also now operates acquired Lawson Indonesia stores. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8890,11 @@
           <t>https://indomaret.co.id</t>
         </is>
       </c>
-      <c r="G115" s="8" t="inlineStr"/>
+      <c r="G115" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/d6/35/f3/d635f35e-4eae-83b5-87bd-b00e231100a3/AppIcon-0-0-1x_U007ephone-0-11-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H115" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -8183,15 +8907,19 @@
       </c>
       <c r="J115" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K115" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L115" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L115" s="8" t="inlineStr">
+        <is>
+          <t>assets/minimarkets/indo/indomaret.png</t>
+        </is>
+      </c>
       <c r="M115" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -8199,7 +8927,7 @@
       </c>
       <c r="N115" s="6" t="inlineStr">
         <is>
-          <t>Market leader.</t>
+          <t>Market leader. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -8290,7 +9018,11 @@
           <t>https://circlekindonesia.com</t>
         </is>
       </c>
-      <c r="G117" s="8" t="inlineStr"/>
+      <c r="G117" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/2a/66/7e/2a667e57-f0bb-7c0e-f1ad-543431d9e0c0/AppIcon-0-0-1x_U007emarketing-0-8-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H117" s="8" t="inlineStr">
         <is>
           <t>icon</t>
@@ -8303,15 +9035,19 @@
       </c>
       <c r="J117" s="8" t="inlineStr">
         <is>
-          <t>TBD (square-ish)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K117" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L117" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L117" s="8" t="inlineStr">
+        <is>
+          <t>assets/minimarkets/indo/circle-k-indonesia.png</t>
+        </is>
+      </c>
       <c r="M117" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -8319,7 +9055,7 @@
       </c>
       <c r="N117" s="6" t="inlineStr">
         <is>
-          <t>Confirm current franchise status in Indonesia.</t>
+          <t>Confirm current franchise status in Indonesia. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -8350,7 +9086,11 @@
           <t>https://www.lawsonindonesia.com</t>
         </is>
       </c>
-      <c r="G118" s="8" t="inlineStr"/>
+      <c r="G118" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/a8/14/af/a814afa1-296c-8b0c-3ae5-0ffb5166f3f4/AppIcon-0-0-1x_U007emarketing-0-6-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H118" s="8" t="inlineStr">
         <is>
           <t>icon</t>
@@ -8363,15 +9103,19 @@
       </c>
       <c r="J118" s="8" t="inlineStr">
         <is>
-          <t>TBD (square-ish)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K118" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L118" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L118" s="8" t="inlineStr">
+        <is>
+          <t>assets/minimarkets/indo/lawson-indonesia.png</t>
+        </is>
+      </c>
       <c r="M118" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -8379,7 +9123,7 @@
       </c>
       <c r="N118" s="6" t="inlineStr">
         <is>
-          <t>Alfamart acquired Lawson Indonesia stores - brand may be retained, converted, or retired. Needs human decision before sourcing.</t>
+          <t>Alfamart acquired Lawson Indonesia stores - brand may be retained, converted, or retired. Needs human decision before sourcing. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -8410,7 +9154,11 @@
           <t>https://www.familymart.co.id</t>
         </is>
       </c>
-      <c r="G119" s="8" t="inlineStr"/>
+      <c r="G119" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/37/5c/9d/375c9d31-bad5-d325-e7ef-c1989a348540/AppIcon-0-0-1x_U007emarketing-0-8-0-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H119" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -8423,15 +9171,19 @@
       </c>
       <c r="J119" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K119" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L119" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L119" s="8" t="inlineStr">
+        <is>
+          <t>assets/minimarkets/indo/familymart-indonesia.png</t>
+        </is>
+      </c>
       <c r="M119" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -8439,7 +9191,7 @@
       </c>
       <c r="N119" s="6" t="inlineStr">
         <is>
-          <t>Confirm current footprint in Indonesia.</t>
+          <t>Confirm current footprint in Indonesia. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -8550,7 +9302,11 @@
           <t>https://shopee.co.id</t>
         </is>
       </c>
-      <c r="G122" s="8" t="inlineStr"/>
+      <c r="G122" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/e4/c5/18/e4c518a8-dfb7-0e15-a36d-89f00cb1b06f/AppIcon-0-1x_U007emarketing-0-6-0-0-85-220-0.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H122" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -8563,15 +9319,19 @@
       </c>
       <c r="J122" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K122" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L122" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L122" s="8" t="inlineStr">
+        <is>
+          <t>assets/ecommerce/indo/shopee.png</t>
+        </is>
+      </c>
       <c r="M122" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -8579,7 +9339,7 @@
       </c>
       <c r="N122" s="6" t="inlineStr">
         <is>
-          <t>Market leader.</t>
+          <t>Market leader. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -8610,7 +9370,11 @@
           <t>https://www.tokopedia.com</t>
         </is>
       </c>
-      <c r="G123" s="8" t="inlineStr"/>
+      <c r="G123" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/34/5f/93/345f9387-54f3-bd59-2f88-23ddcb804f33/AppIcon-0-0-1x_U007epad-0-1-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H123" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -8623,15 +9387,19 @@
       </c>
       <c r="J123" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K123" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L123" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L123" s="8" t="inlineStr">
+        <is>
+          <t>assets/ecommerce/indo/tokopedia.png</t>
+        </is>
+      </c>
       <c r="M123" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -8639,7 +9407,7 @@
       </c>
       <c r="N123" s="6" t="inlineStr">
         <is>
-          <t>TikTok acquired majority stake (2024); brand still operates.</t>
+          <t>TikTok acquired majority stake (2024); brand still operates. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -8670,7 +9438,11 @@
           <t>https://www.lazada.co.id</t>
         </is>
       </c>
-      <c r="G124" s="8" t="inlineStr"/>
+      <c r="G124" s="8" t="inlineStr">
+        <is>
+          <t>https://img.lazcdn.com/g/tps/images/ims-web/TB1Hs8GaMFY.1VjSZFnXXcFHXXa.png</t>
+        </is>
+      </c>
       <c r="H124" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -8683,15 +9455,19 @@
       </c>
       <c r="J124" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>3.19:1 (horizontal, 344x108)</t>
         </is>
       </c>
       <c r="K124" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L124" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L124" s="8" t="inlineStr">
+        <is>
+          <t>assets/ecommerce/indo/lazada-indonesia.png</t>
+        </is>
+      </c>
       <c r="M124" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -8699,7 +9475,7 @@
       </c>
       <c r="N124" s="6" t="inlineStr">
         <is>
-          <t>Alibaba group.</t>
+          <t>Alibaba group. Auto-sourced via brand-press.</t>
         </is>
       </c>
     </row>
@@ -8730,7 +9506,11 @@
           <t>https://www.bukalapak.com</t>
         </is>
       </c>
-      <c r="G125" s="8" t="inlineStr"/>
+      <c r="G125" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/fa/28/8a/fa288a52-e5a6-06a7-c5d6-41852d2f2b07/AppIcon-0-0-1x_U007emarketing-0-7-0-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H125" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -8743,15 +9523,19 @@
       </c>
       <c r="J125" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K125" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L125" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L125" s="8" t="inlineStr">
+        <is>
+          <t>assets/ecommerce/indo/bukalapak.png</t>
+        </is>
+      </c>
       <c r="M125" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -8759,7 +9543,7 @@
       </c>
       <c r="N125" s="6" t="inlineStr">
         <is>
-          <t>Ceased physical-goods marketplace Feb 2025; now virtual products/digital services only. Still operating - confirm it belongs in an e-commerce grouping.</t>
+          <t>Ceased physical-goods marketplace Feb 2025; now virtual products/digital services only. Still operating - confirm it belongs in an e-commerce grouping. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -8790,7 +9574,11 @@
           <t>https://www.blibli.com</t>
         </is>
       </c>
-      <c r="G126" s="8" t="inlineStr"/>
+      <c r="G126" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/7a/61/73/7a61735b-fa6a-dca1-915b-f5f8fc95a1fb/AppIcon-0-0-1x_U007epad-0-1-0-sRGB-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H126" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -8803,15 +9591,19 @@
       </c>
       <c r="J126" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K126" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L126" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L126" s="8" t="inlineStr">
+        <is>
+          <t>assets/ecommerce/indo/blibli.png</t>
+        </is>
+      </c>
       <c r="M126" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -8819,7 +9611,7 @@
       </c>
       <c r="N126" s="6" t="inlineStr">
         <is>
-          <t>Djarum/GDP Venture group.</t>
+          <t>Djarum/GDP Venture group. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -8850,7 +9642,11 @@
           <t>https://www.zalora.co.id</t>
         </is>
       </c>
-      <c r="G127" s="8" t="inlineStr"/>
+      <c r="G127" s="8" t="inlineStr">
+        <is>
+          <t>https://static-id.zacdn.com/next-assets/static-assets/images/fav/favicon.svg</t>
+        </is>
+      </c>
       <c r="H127" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -8863,15 +9659,19 @@
       </c>
       <c r="J127" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 40x40)</t>
         </is>
       </c>
       <c r="K127" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L127" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L127" s="8" t="inlineStr">
+        <is>
+          <t>assets/ecommerce/indo/zalora-indonesia.svg</t>
+        </is>
+      </c>
       <c r="M127" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -8879,7 +9679,7 @@
       </c>
       <c r="N127" s="6" t="inlineStr">
         <is>
-          <t>Candidate row; regulator check and asset sourcing outstanding.</t>
+          <t>Candidate row; regulator check and asset sourcing outstanding. Auto-sourced via brand-press.</t>
         </is>
       </c>
     </row>
@@ -8910,7 +9710,11 @@
           <t>https://www.tiktok.com</t>
         </is>
       </c>
-      <c r="G128" s="8" t="inlineStr"/>
+      <c r="G128" s="8" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/favicon.svg</t>
+        </is>
+      </c>
       <c r="H128" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -8923,15 +9727,19 @@
       </c>
       <c r="J128" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 200x200)</t>
         </is>
       </c>
       <c r="K128" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L128" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L128" s="8" t="inlineStr">
+        <is>
+          <t>assets/ecommerce/indo/tiktok-shop-indonesia.svg</t>
+        </is>
+      </c>
       <c r="M128" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -8939,7 +9747,7 @@
       </c>
       <c r="N128" s="6" t="inlineStr">
         <is>
-          <t>Operates via Tokopedia entity post-2024 merger; confirm whether a distinct TikTok Shop mark or the Tokopedia mark is correct for checkout UI.</t>
+          <t>Operates via Tokopedia entity post-2024 merger; confirm whether a distinct TikTok Shop mark or the Tokopedia mark is correct for checkout UI. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -8970,7 +9778,11 @@
           <t>https://www.akulaku.com</t>
         </is>
       </c>
-      <c r="G129" s="8" t="inlineStr"/>
+      <c r="G129" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/1b/3a/49/1b3a4901-19f6-de1a-e8da-b399521cc315/AppIcon-1x_U007epad-0-1-0-sRGB-85-220-0.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H129" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -8983,15 +9795,19 @@
       </c>
       <c r="J129" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K129" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L129" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L129" s="8" t="inlineStr">
+        <is>
+          <t>assets/ecommerce/indo/akulaku.png</t>
+        </is>
+      </c>
       <c r="M129" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -8999,7 +9815,7 @@
       </c>
       <c r="N129" s="6" t="inlineStr">
         <is>
-          <t>Primarily BNPL/paylater rather than pure marketplace - confirm category fit.</t>
+          <t>Primarily BNPL/paylater rather than pure marketplace - confirm category fit. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -9030,7 +9846,11 @@
           <t>https://www.orami.co.id</t>
         </is>
       </c>
-      <c r="G130" s="8" t="inlineStr"/>
+      <c r="G130" s="8" t="inlineStr">
+        <is>
+          <t>https://www.orami.co.id/static/images/orami-parenting-meta-image.png</t>
+        </is>
+      </c>
       <c r="H130" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -9043,15 +9863,19 @@
       </c>
       <c r="J130" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.90:1 (horizontal, 1200x630)</t>
         </is>
       </c>
       <c r="K130" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L130" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L130" s="8" t="inlineStr">
+        <is>
+          <t>assets/ecommerce/indo/orami.png</t>
+        </is>
+      </c>
       <c r="M130" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -9059,7 +9883,7 @@
       </c>
       <c r="N130" s="6" t="inlineStr">
         <is>
-          <t>Mother/baby vertical (Sirclo group). Confirm current status.</t>
+          <t>Mother/baby vertical (Sirclo group). Confirm current status. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -9090,7 +9914,11 @@
           <t>https://www.sociolla.com</t>
         </is>
       </c>
-      <c r="G131" s="8" t="inlineStr"/>
+      <c r="G131" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/2f/cd/e0/2fcde042-8eef-3a8e-92fb-91f1716ddc82/AppIcon-0-0-1x_U007emarketing-0-6-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H131" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -9103,15 +9931,19 @@
       </c>
       <c r="J131" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K131" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L131" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L131" s="8" t="inlineStr">
+        <is>
+          <t>assets/ecommerce/indo/sociolla.png</t>
+        </is>
+      </c>
       <c r="M131" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -9119,7 +9951,7 @@
       </c>
       <c r="N131" s="6" t="inlineStr">
         <is>
-          <t>Beauty vertical.</t>
+          <t>Beauty vertical. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -9234,7 +10066,11 @@
           <t>https://www.dbs.com.sg</t>
         </is>
       </c>
-      <c r="G134" s="8" t="inlineStr"/>
+      <c r="G134" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/08/72/3a/08723a08-47c6-8514-a6fe-70d4916f0637/AppIcon-0-0-1x_U007emarketing-0-11-0-sRGB-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H134" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -9247,15 +10083,19 @@
       </c>
       <c r="J134" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K134" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L134" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L134" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/sg/dbs.png</t>
+        </is>
+      </c>
       <c r="M134" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -9263,7 +10103,7 @@
       </c>
       <c r="N134" s="6" t="inlineStr">
         <is>
-          <t>Verify: MAS register.</t>
+          <t>Verify: MAS register. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -9298,7 +10138,11 @@
           <t>https://www.ocbc.com</t>
         </is>
       </c>
-      <c r="G135" s="8" t="inlineStr"/>
+      <c r="G135" s="8" t="inlineStr">
+        <is>
+          <t>https://www.ocbc.com/iwov-resources/sg/ocbc/gbc/img/logo_ocbc.png</t>
+        </is>
+      </c>
       <c r="H135" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -9311,15 +10155,19 @@
       </c>
       <c r="J135" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>3.72:1 (horizontal, 1160x312)</t>
         </is>
       </c>
       <c r="K135" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L135" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L135" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/sg/ocbc.png</t>
+        </is>
+      </c>
       <c r="M135" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -9327,7 +10175,7 @@
       </c>
       <c r="N135" s="6" t="inlineStr">
         <is>
-          <t>Verify: MAS register.</t>
+          <t>Verify: MAS register. Auto-sourced via brand-press.</t>
         </is>
       </c>
     </row>
@@ -9362,7 +10210,11 @@
           <t>https://www.uob.com.sg</t>
         </is>
       </c>
-      <c r="G136" s="8" t="inlineStr"/>
+      <c r="G136" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/c9/03/b3/c903b35f-2ee9-9282-87fc-3d4941ae5475/AppIcon-0-0-1x_U007emarketing-0-7-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H136" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -9375,15 +10227,19 @@
       </c>
       <c r="J136" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K136" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L136" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L136" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/sg/uob.png</t>
+        </is>
+      </c>
       <c r="M136" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -9391,7 +10247,7 @@
       </c>
       <c r="N136" s="6" t="inlineStr">
         <is>
-          <t>Verify: MAS register.</t>
+          <t>Verify: MAS register. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -9426,7 +10282,11 @@
           <t>https://www.sc.com/sg</t>
         </is>
       </c>
-      <c r="G137" s="8" t="inlineStr"/>
+      <c r="G137" s="8" t="inlineStr">
+        <is>
+          <t>https://av.sc.com/sg/content/images/content/images/cropped-cropped-favicon-cropped-512x512-1-200x200.png</t>
+        </is>
+      </c>
       <c r="H137" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -9439,15 +10299,19 @@
       </c>
       <c r="J137" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 200x200)</t>
         </is>
       </c>
       <c r="K137" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L137" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L137" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/sg/standard-chartered.png</t>
+        </is>
+      </c>
       <c r="M137" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -9455,7 +10319,7 @@
       </c>
       <c r="N137" s="6" t="inlineStr">
         <is>
-          <t>Verify: MAS register. Consider whether local variants duplicate the international row.</t>
+          <t>Verify: MAS register. Consider whether local variants duplicate the international row. Auto-sourced via brand-press.</t>
         </is>
       </c>
     </row>
@@ -9490,7 +10354,11 @@
           <t>https://www.citibank.com.sg</t>
         </is>
       </c>
-      <c r="G138" s="8" t="inlineStr"/>
+      <c r="G138" s="8" t="inlineStr">
+        <is>
+          <t>https://www.citibank.com.sg/content/experience-fragments/cgcpc/sg/prelogin/www-citibank-com-sg/footer/master/_jcr_content/root/container/container_1938911663/container_780719881/image.coreimg.svg/1756189707913/citi-logo.svg</t>
+        </is>
+      </c>
       <c r="H138" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -9503,15 +10371,19 @@
       </c>
       <c r="J138" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.94:1 (horizontal, 66x34)</t>
         </is>
       </c>
       <c r="K138" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L138" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L138" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/sg/citibank.svg</t>
+        </is>
+      </c>
       <c r="M138" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -9519,7 +10391,7 @@
       </c>
       <c r="N138" s="6" t="inlineStr">
         <is>
-          <t>Verify: MAS register. Consider whether local variants duplicate the international row.</t>
+          <t>Verify: MAS register. Consider whether local variants duplicate the international row. Auto-sourced via brand-press.</t>
         </is>
       </c>
     </row>
@@ -9554,7 +10426,11 @@
           <t>https://www.maybank2u.com.sg</t>
         </is>
       </c>
-      <c r="G139" s="8" t="inlineStr"/>
+      <c r="G139" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/db/ae/17/dbae176c-f96f-7499-0174-ce2ca116c103/AppIcon-0-0-1x_U007emarketing-0-6-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H139" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -9567,15 +10443,19 @@
       </c>
       <c r="J139" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K139" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L139" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L139" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/sg/maybank.png</t>
+        </is>
+      </c>
       <c r="M139" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -9583,7 +10463,7 @@
       </c>
       <c r="N139" s="6" t="inlineStr">
         <is>
-          <t>Verify: MAS register. Same group mark as Maybank MY - confirm whether a distinct SG asset is needed.</t>
+          <t>Verify: MAS register. Same group mark as Maybank MY - confirm whether a distinct SG asset is needed. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -9618,7 +10498,11 @@
           <t>https://www.maybank2u.com.my</t>
         </is>
       </c>
-      <c r="G140" s="8" t="inlineStr"/>
+      <c r="G140" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/c2/19/4f/c2194f6a-05b6-858c-b1a3-c04d65782467/AppIcon-0-0-1x_U007emarketing-0-8-0-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H140" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -9631,15 +10515,19 @@
       </c>
       <c r="J140" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K140" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L140" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L140" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/my/maybank.png</t>
+        </is>
+      </c>
       <c r="M140" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -9647,7 +10535,7 @@
       </c>
       <c r="N140" s="6" t="inlineStr">
         <is>
-          <t>Verify: BNM list.</t>
+          <t>Verify: BNM list. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -9682,7 +10570,11 @@
           <t>https://www.cimb.com.my</t>
         </is>
       </c>
-      <c r="G141" s="8" t="inlineStr"/>
+      <c r="G141" s="8" t="inlineStr">
+        <is>
+          <t>https://www.cimb.com.my/content/dam/cimb/favicon/apple-touch-icon-152x152.png</t>
+        </is>
+      </c>
       <c r="H141" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -9695,15 +10587,19 @@
       </c>
       <c r="J141" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 152x152)</t>
         </is>
       </c>
       <c r="K141" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L141" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L141" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/my/cimb.png</t>
+        </is>
+      </c>
       <c r="M141" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -9711,7 +10607,7 @@
       </c>
       <c r="N141" s="6" t="inlineStr">
         <is>
-          <t>Verify: BNM list.</t>
+          <t>Verify: BNM list. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -9746,7 +10642,11 @@
           <t>https://www.pbebank.com</t>
         </is>
       </c>
-      <c r="G142" s="8" t="inlineStr"/>
+      <c r="G142" s="8" t="inlineStr">
+        <is>
+          <t>https://www.pbebank.com/media/vxfbkfv0/pbb-60th-anniversary.svg</t>
+        </is>
+      </c>
       <c r="H142" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -9759,15 +10659,19 @@
       </c>
       <c r="J142" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>4.00:1 (horizontal, 2000x500)</t>
         </is>
       </c>
       <c r="K142" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L142" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L142" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/my/public-bank.svg</t>
+        </is>
+      </c>
       <c r="M142" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -9775,7 +10679,7 @@
       </c>
       <c r="N142" s="6" t="inlineStr">
         <is>
-          <t>Verify: BNM list.</t>
+          <t>Verify: BNM list. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -9810,7 +10714,11 @@
           <t>https://www.rhbgroup.com</t>
         </is>
       </c>
-      <c r="G143" s="8" t="inlineStr"/>
+      <c r="G143" s="8" t="inlineStr">
+        <is>
+          <t>https://www.rhbgroup.com/-/media/Project/RHB/Logo/logo.png</t>
+        </is>
+      </c>
       <c r="H143" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -9823,15 +10731,19 @@
       </c>
       <c r="J143" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>3.10:1 (horizontal, 248x80)</t>
         </is>
       </c>
       <c r="K143" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L143" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L143" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/my/rhb.webp</t>
+        </is>
+      </c>
       <c r="M143" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -9839,7 +10751,7 @@
       </c>
       <c r="N143" s="6" t="inlineStr">
         <is>
-          <t>Verify: BNM list.</t>
+          <t>Verify: BNM list. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -9874,7 +10786,11 @@
           <t>https://www.hlb.com.my</t>
         </is>
       </c>
-      <c r="G144" s="8" t="inlineStr"/>
+      <c r="G144" s="8" t="inlineStr">
+        <is>
+          <t>https://www.hlb.com.my/content/dam/global/icons/logo-hong-leong-desktop.png</t>
+        </is>
+      </c>
       <c r="H144" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -9887,15 +10803,19 @@
       </c>
       <c r="J144" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>5.50:1 (horizontal, 220x40)</t>
         </is>
       </c>
       <c r="K144" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L144" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L144" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/my/hong-leong-bank.png</t>
+        </is>
+      </c>
       <c r="M144" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -9903,7 +10823,7 @@
       </c>
       <c r="N144" s="6" t="inlineStr">
         <is>
-          <t>Verify: BNM list.</t>
+          <t>Verify: BNM list. Auto-sourced via brand-press.</t>
         </is>
       </c>
     </row>
@@ -9938,7 +10858,11 @@
           <t>https://www.ambank.com.my</t>
         </is>
       </c>
-      <c r="G145" s="8" t="inlineStr"/>
+      <c r="G145" s="8" t="inlineStr">
+        <is>
+          <t>https://www.ambank.com.my/assets/images/logo/main.svg</t>
+        </is>
+      </c>
       <c r="H145" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -9951,15 +10875,19 @@
       </c>
       <c r="J145" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.72:1 (horizontal, 105x61)</t>
         </is>
       </c>
       <c r="K145" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L145" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L145" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/my/ambank.svg</t>
+        </is>
+      </c>
       <c r="M145" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -9967,7 +10895,7 @@
       </c>
       <c r="N145" s="6" t="inlineStr">
         <is>
-          <t>Verify: BNM list.</t>
+          <t>Verify: BNM list. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -10002,7 +10930,11 @@
           <t>https://www.bankislam.com</t>
         </is>
       </c>
-      <c r="G146" s="8" t="inlineStr"/>
+      <c r="G146" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/9d/66/a9/9d66a9c1-716a-304a-e370-56d4252c0a3e/AppIcon-0-0-1x_U007emarketing-0-8-0-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H146" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -10015,15 +10947,19 @@
       </c>
       <c r="J146" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K146" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L146" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L146" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/my/bank-islam.png</t>
+        </is>
+      </c>
       <c r="M146" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -10031,7 +10967,7 @@
       </c>
       <c r="N146" s="6" t="inlineStr">
         <is>
-          <t>Verify: BNM list.</t>
+          <t>Verify: BNM list. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -10066,7 +11002,11 @@
           <t>https://www.bangkokbank.com</t>
         </is>
       </c>
-      <c r="G147" s="8" t="inlineStr"/>
+      <c r="G147" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/3c/5a/6d/3c5a6d5c-dafe-9e51-4b85-99234f990e8b/AppIcon_Rel28-0-0-1x_U007ephone-0-1-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H147" s="8" t="inlineStr">
         <is>
           <t>icon</t>
@@ -10079,15 +11019,19 @@
       </c>
       <c r="J147" s="8" t="inlineStr">
         <is>
-          <t>TBD (square-ish)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K147" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L147" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L147" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/th/bangkok-bank.png</t>
+        </is>
+      </c>
       <c r="M147" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -10095,7 +11039,7 @@
       </c>
       <c r="N147" s="6" t="inlineStr">
         <is>
-          <t>Verify: BOT register. Owns PermataBank Indonesia.</t>
+          <t>Verify: BOT register. Owns PermataBank Indonesia. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -10130,7 +11074,11 @@
           <t>https://www.kasikornbank.com</t>
         </is>
       </c>
-      <c r="G148" s="8" t="inlineStr"/>
+      <c r="G148" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/65/5f/40/655f401a-8db0-8e29-cb11-0701f411906f/AppIcon-0-0-1x_U007emarketing-0-7-0-P3-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H148" s="8" t="inlineStr">
         <is>
           <t>icon</t>
@@ -10143,15 +11091,19 @@
       </c>
       <c r="J148" s="8" t="inlineStr">
         <is>
-          <t>TBD (square-ish)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K148" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L148" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L148" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/th/kasikornbank.png</t>
+        </is>
+      </c>
       <c r="M148" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -10159,7 +11111,7 @@
       </c>
       <c r="N148" s="6" t="inlineStr">
         <is>
-          <t>Verify: BOT register.</t>
+          <t>Verify: BOT register. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -10194,7 +11146,11 @@
           <t>https://www.scb.co.th</t>
         </is>
       </c>
-      <c r="G149" s="8" t="inlineStr"/>
+      <c r="G149" s="8" t="inlineStr">
+        <is>
+          <t>https://www.scb.co.th/etc.clientlibs/settings/wcm/designs/scb/scb-design/resources/safari-pinned-tab.svg</t>
+        </is>
+      </c>
       <c r="H149" s="8" t="inlineStr">
         <is>
           <t>icon</t>
@@ -10207,15 +11163,19 @@
       </c>
       <c r="J149" s="8" t="inlineStr">
         <is>
-          <t>TBD (square-ish)</t>
+          <t>1.00:1 (square, 700x700)</t>
         </is>
       </c>
       <c r="K149" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L149" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L149" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/th/scb.svg</t>
+        </is>
+      </c>
       <c r="M149" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -10223,7 +11183,7 @@
       </c>
       <c r="N149" s="6" t="inlineStr">
         <is>
-          <t>Verify: BOT register.</t>
+          <t>Verify: BOT register. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -10258,7 +11218,11 @@
           <t>https://krungthai.com</t>
         </is>
       </c>
-      <c r="G150" s="8" t="inlineStr"/>
+      <c r="G150" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/bb/ae/be/bbaebea1-2451-9918-8ed8-7a7f37a95ba8/AppIcon-0-0-1x_U007emarketing-0-8-0-sRGB-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H150" s="8" t="inlineStr">
         <is>
           <t>icon</t>
@@ -10271,15 +11235,19 @@
       </c>
       <c r="J150" s="8" t="inlineStr">
         <is>
-          <t>TBD (square-ish)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K150" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L150" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L150" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/th/krungthai.png</t>
+        </is>
+      </c>
       <c r="M150" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -10287,7 +11255,7 @@
       </c>
       <c r="N150" s="6" t="inlineStr">
         <is>
-          <t>Verify: BOT register. State-owned.</t>
+          <t>Verify: BOT register. State-owned. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -10322,7 +11290,11 @@
           <t>https://www.krungsri.com</t>
         </is>
       </c>
-      <c r="G151" s="8" t="inlineStr"/>
+      <c r="G151" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/4f/8e/65/4f8e6504-5e5e-5e47-c876-fe60321af107/AppIcons-0-0-1x_U007emarketing-0-4-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H151" s="8" t="inlineStr">
         <is>
           <t>icon</t>
@@ -10335,15 +11307,19 @@
       </c>
       <c r="J151" s="8" t="inlineStr">
         <is>
-          <t>TBD (square-ish)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K151" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L151" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L151" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/th/krungsri.png</t>
+        </is>
+      </c>
       <c r="M151" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -10351,7 +11327,7 @@
       </c>
       <c r="N151" s="6" t="inlineStr">
         <is>
-          <t>Verify: BOT register. MUFG-controlled.</t>
+          <t>Verify: BOT register. MUFG-controlled. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -10386,7 +11362,11 @@
           <t>https://www.ttbbank.com</t>
         </is>
       </c>
-      <c r="G152" s="8" t="inlineStr"/>
+      <c r="G152" s="8" t="inlineStr">
+        <is>
+          <t>https://www.ttbbank.com/favicon.svg</t>
+        </is>
+      </c>
       <c r="H152" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -10399,15 +11379,19 @@
       </c>
       <c r="J152" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 512x512)</t>
         </is>
       </c>
       <c r="K152" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L152" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L152" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/th/ttb.svg</t>
+        </is>
+      </c>
       <c r="M152" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -10415,7 +11399,7 @@
       </c>
       <c r="N152" s="6" t="inlineStr">
         <is>
-          <t>Formed from TMB + Thanachart merger - do NOT use legacy TMB or Thanachart assets. Verify: BOT register.</t>
+          <t>Formed from TMB + Thanachart merger - do NOT use legacy TMB or Thanachart assets. Verify: BOT register. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -10450,7 +11434,11 @@
           <t>https://www.bdo.com.ph</t>
         </is>
       </c>
-      <c r="G153" s="8" t="inlineStr"/>
+      <c r="G153" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/c0/c8/86/c0c88687-a8e7-e09a-796e-b2bbbdf6ffb6/AppIcon-0-0-1x_U007emarketing-0-8-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H153" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -10463,15 +11451,19 @@
       </c>
       <c r="J153" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K153" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L153" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L153" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/ph/bdo.png</t>
+        </is>
+      </c>
       <c r="M153" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -10479,7 +11471,7 @@
       </c>
       <c r="N153" s="6" t="inlineStr">
         <is>
-          <t>Verify: BSP directory.</t>
+          <t>Verify: BSP directory. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -10514,7 +11506,11 @@
           <t>https://www.bpi.com.ph</t>
         </is>
       </c>
-      <c r="G154" s="8" t="inlineStr"/>
+      <c r="G154" s="8" t="inlineStr">
+        <is>
+          <t>https://www.bpi.com.ph/content/dam/bpi/main-navigation/BPI_RT__96x42_header_rev.svg</t>
+        </is>
+      </c>
       <c r="H154" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -10527,15 +11523,19 @@
       </c>
       <c r="J154" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>2.38:1 (horizontal, 100x42)</t>
         </is>
       </c>
       <c r="K154" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L154" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L154" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/ph/bpi.svg</t>
+        </is>
+      </c>
       <c r="M154" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -10543,7 +11543,7 @@
       </c>
       <c r="N154" s="6" t="inlineStr">
         <is>
-          <t>Verify: BSP directory. Rebranded identity in recent years - use current asset only.</t>
+          <t>Verify: BSP directory. Rebranded identity in recent years - use current asset only. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -10578,7 +11578,11 @@
           <t>https://www.metrobank.com.ph</t>
         </is>
       </c>
-      <c r="G155" s="8" t="inlineStr"/>
+      <c r="G155" s="8" t="inlineStr">
+        <is>
+          <t>https://web-assets.metrobank.com.ph/1724928977-mb-yigh-logo-2019-electric-blue.png</t>
+        </is>
+      </c>
       <c r="H155" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -10591,15 +11595,19 @@
       </c>
       <c r="J155" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>4.16:1 (horizontal, 233x56)</t>
         </is>
       </c>
       <c r="K155" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L155" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L155" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/ph/metrobank.png</t>
+        </is>
+      </c>
       <c r="M155" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -10607,7 +11615,7 @@
       </c>
       <c r="N155" s="6" t="inlineStr">
         <is>
-          <t>Verify: BSP directory.</t>
+          <t>Verify: BSP directory. Auto-sourced via brand-press.</t>
         </is>
       </c>
     </row>
@@ -10642,7 +11650,11 @@
           <t>https://www.landbank.com</t>
         </is>
       </c>
-      <c r="G156" s="8" t="inlineStr"/>
+      <c r="G156" s="8" t="inlineStr">
+        <is>
+          <t>https://www.landbank.com/favicon.ico</t>
+        </is>
+      </c>
       <c r="H156" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -10655,15 +11667,19 @@
       </c>
       <c r="J156" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 128x128)</t>
         </is>
       </c>
       <c r="K156" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L156" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L156" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/ph/landbank.png</t>
+        </is>
+      </c>
       <c r="M156" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -10671,7 +11687,7 @@
       </c>
       <c r="N156" s="6" t="inlineStr">
         <is>
-          <t>State-owned. Verify: BSP directory.</t>
+          <t>State-owned. Verify: BSP directory. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -10706,7 +11722,11 @@
           <t>https://www.securitybank.com</t>
         </is>
       </c>
-      <c r="G157" s="8" t="inlineStr"/>
+      <c r="G157" s="8" t="inlineStr">
+        <is>
+          <t>https://www.securitybank.com/favicon/apple-touch-icon-152x152.png</t>
+        </is>
+      </c>
       <c r="H157" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -10719,15 +11739,19 @@
       </c>
       <c r="J157" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 152x152)</t>
         </is>
       </c>
       <c r="K157" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L157" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L157" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/ph/security-bank.png</t>
+        </is>
+      </c>
       <c r="M157" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -10735,7 +11759,7 @@
       </c>
       <c r="N157" s="6" t="inlineStr">
         <is>
-          <t>Verify: BSP directory.</t>
+          <t>Verify: BSP directory. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -10770,7 +11794,11 @@
           <t>https://www.unionbankph.com</t>
         </is>
       </c>
-      <c r="G158" s="8" t="inlineStr"/>
+      <c r="G158" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/cf/fc/1c/cffc1cad-ec2f-9b7b-1b2a-106b3ccdccbb/AppIcon-0-0-1x_U007emarketing-0-8-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H158" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -10783,15 +11811,19 @@
       </c>
       <c r="J158" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K158" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L158" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L158" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/ph/unionbank.png</t>
+        </is>
+      </c>
       <c r="M158" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -10799,7 +11831,7 @@
       </c>
       <c r="N158" s="6" t="inlineStr">
         <is>
-          <t>Verify: BSP directory.</t>
+          <t>Verify: BSP directory. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -10834,7 +11866,11 @@
           <t>https://www.vietcombank.com.vn</t>
         </is>
       </c>
-      <c r="G159" s="8" t="inlineStr"/>
+      <c r="G159" s="8" t="inlineStr">
+        <is>
+          <t>https://www.vietcombank.com.vn/-/media/Project/VCB-Sites/VCB/Home-page/VCB-Logo/Logo-VCB-no-60.png?ts=20240605031450</t>
+        </is>
+      </c>
       <c r="H159" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -10847,15 +11883,19 @@
       </c>
       <c r="J159" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>2.94:1 (horizontal, 365x124)</t>
         </is>
       </c>
       <c r="K159" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L159" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L159" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/vn/vietcombank.webp</t>
+        </is>
+      </c>
       <c r="M159" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -10863,7 +11903,7 @@
       </c>
       <c r="N159" s="6" t="inlineStr">
         <is>
-          <t>Verify: SBV list.</t>
+          <t>Verify: SBV list. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -10898,7 +11938,11 @@
           <t>https://www.vietinbank.vn</t>
         </is>
       </c>
-      <c r="G160" s="8" t="inlineStr"/>
+      <c r="G160" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/25/2b/cd/252bcdeb-b634-a7f9-00b8-ea704e528f51/AppIcon-0-0-1x_U007emarketing-0-8-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H160" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -10911,15 +11955,19 @@
       </c>
       <c r="J160" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K160" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L160" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L160" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/vn/vietinbank.png</t>
+        </is>
+      </c>
       <c r="M160" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -10927,7 +11975,7 @@
       </c>
       <c r="N160" s="6" t="inlineStr">
         <is>
-          <t>Verify: SBV list.</t>
+          <t>Verify: SBV list. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -10962,7 +12010,11 @@
           <t>https://www.bidv.com.vn</t>
         </is>
       </c>
-      <c r="G161" s="8" t="inlineStr"/>
+      <c r="G161" s="8" t="inlineStr">
+        <is>
+          <t>https://bidv.com.vn/wps/wcm/connect/7d6f3c42-23d4-4868-8340-20114a00d51a/logo+bhtg.jpg?MOD=AJPERES</t>
+        </is>
+      </c>
       <c r="H161" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -10975,15 +12027,19 @@
       </c>
       <c r="J161" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.45:1 (horizontal, 1905x1312)</t>
         </is>
       </c>
       <c r="K161" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L161" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L161" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/vn/bidv.jpg</t>
+        </is>
+      </c>
       <c r="M161" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -10991,7 +12047,7 @@
       </c>
       <c r="N161" s="6" t="inlineStr">
         <is>
-          <t>Verify: SBV list.</t>
+          <t>Verify: SBV list. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -11026,7 +12082,11 @@
           <t>https://www.techcombank.com</t>
         </is>
       </c>
-      <c r="G162" s="8" t="inlineStr"/>
+      <c r="G162" s="8" t="inlineStr">
+        <is>
+          <t>https://techcombank.com/content/dam/techcombank/public-site/seo/techcombank_logo_svg_86201e50d1.svg</t>
+        </is>
+      </c>
       <c r="H162" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -11039,15 +12099,19 @@
       </c>
       <c r="J162" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>7.38:1 (horizontal, 406x55)</t>
         </is>
       </c>
       <c r="K162" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L162" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L162" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/vn/techcombank.svg</t>
+        </is>
+      </c>
       <c r="M162" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -11055,7 +12119,7 @@
       </c>
       <c r="N162" s="6" t="inlineStr">
         <is>
-          <t>Verify: SBV list.</t>
+          <t>Verify: SBV list. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -11090,7 +12154,11 @@
           <t>https://www.vpbank.com.vn</t>
         </is>
       </c>
-      <c r="G163" s="8" t="inlineStr"/>
+      <c r="G163" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/23/35/72/23357258-570b-9294-08f3-f29093ad87de/AppIcon-0-0-1x_U007ephone-0-11-0-sRGB-85-220.jpeg/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H163" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -11103,15 +12171,19 @@
       </c>
       <c r="J163" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K163" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L163" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L163" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/vn/vpbank.png</t>
+        </is>
+      </c>
       <c r="M163" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -11119,7 +12191,7 @@
       </c>
       <c r="N163" s="6" t="inlineStr">
         <is>
-          <t>Verify: SBV list.</t>
+          <t>Verify: SBV list. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -11154,7 +12226,11 @@
           <t>https://www.acb.com.vn</t>
         </is>
       </c>
-      <c r="G164" s="8" t="inlineStr"/>
+      <c r="G164" s="8" t="inlineStr">
+        <is>
+          <t>https://acb.com.vn/_next/image?url=%2Fimages%2Flogo.svg&amp;w=384&amp;q=70</t>
+        </is>
+      </c>
       <c r="H164" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -11167,15 +12243,19 @@
       </c>
       <c r="J164" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>2.41:1 (horizontal, 135x56)</t>
         </is>
       </c>
       <c r="K164" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L164" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L164" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/vn/acb.svg</t>
+        </is>
+      </c>
       <c r="M164" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -11183,7 +12263,7 @@
       </c>
       <c r="N164" s="6" t="inlineStr">
         <is>
-          <t>Verify: SBV list.</t>
+          <t>Verify: SBV list. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -11218,7 +12298,11 @@
           <t>https://www.sacombank.com.vn</t>
         </is>
       </c>
-      <c r="G165" s="8" t="inlineStr"/>
+      <c r="G165" s="8" t="inlineStr">
+        <is>
+          <t>https://www.sacombank.com.vn/android-chrome-512x512.png</t>
+        </is>
+      </c>
       <c r="H165" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -11231,15 +12315,19 @@
       </c>
       <c r="J165" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 512x512)</t>
         </is>
       </c>
       <c r="K165" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L165" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L165" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/vn/sacombank.png</t>
+        </is>
+      </c>
       <c r="M165" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -11247,7 +12335,7 @@
       </c>
       <c r="N165" s="6" t="inlineStr">
         <is>
-          <t>Verify: SBV list.</t>
+          <t>Verify: SBV list. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -11282,7 +12370,11 @@
           <t>https://www.ababank.com</t>
         </is>
       </c>
-      <c r="G166" s="8" t="inlineStr"/>
+      <c r="G166" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/e8/7a/6d/e87a6d83-f52e-7157-75cd-217b7b51d264/AppIcon-0-0-1x_U007ephone-0-1-0-P3-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H166" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -11295,15 +12387,19 @@
       </c>
       <c r="J166" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K166" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L166" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L166" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/kh/aba-bank.png</t>
+        </is>
+      </c>
       <c r="M166" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -11311,7 +12407,7 @@
       </c>
       <c r="N166" s="6" t="inlineStr">
         <is>
-          <t>Verify: NBC list. Lower-priority market per brief.</t>
+          <t>Verify: NBC list. Lower-priority market per brief. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -11346,7 +12442,11 @@
           <t>https://www.bcel.com.la</t>
         </is>
       </c>
-      <c r="G167" s="8" t="inlineStr"/>
+      <c r="G167" s="8" t="inlineStr">
+        <is>
+          <t>https://www.bcel.com.la/bcel/resources/imgs/ibank1_1.png</t>
+        </is>
+      </c>
       <c r="H167" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -11359,15 +12459,19 @@
       </c>
       <c r="J167" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.03:1 (square, 130x126)</t>
         </is>
       </c>
       <c r="K167" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L167" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L167" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/la/bcel.png</t>
+        </is>
+      </c>
       <c r="M167" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -11375,7 +12479,7 @@
       </c>
       <c r="N167" s="6" t="inlineStr">
         <is>
-          <t>Verify: BOL list. Lower-priority market; limited asset availability expected.</t>
+          <t>Verify: BOL list. Lower-priority market; limited asset availability expected. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -11410,7 +12514,11 @@
           <t>https://www.bibd.com.bn</t>
         </is>
       </c>
-      <c r="G168" s="8" t="inlineStr"/>
+      <c r="G168" s="8" t="inlineStr">
+        <is>
+          <t>https://bibd.com.bn/wp-content/uploads/2021/10/BIBD-logo.png</t>
+        </is>
+      </c>
       <c r="H168" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -11423,15 +12531,19 @@
       </c>
       <c r="J168" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>2.67:1 (horizontal, 155x58)</t>
         </is>
       </c>
       <c r="K168" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L168" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L168" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/sea/bn/bibd.png</t>
+        </is>
+      </c>
       <c r="M168" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -11439,7 +12551,7 @@
       </c>
       <c r="N168" s="6" t="inlineStr">
         <is>
-          <t>Verify: BDCB list. Lower-priority market per brief.</t>
+          <t>Verify: BDCB list. Lower-priority market per brief. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -11518,7 +12630,11 @@
           <t>https://www.grab.com/sg/pay</t>
         </is>
       </c>
-      <c r="G170" s="8" t="inlineStr"/>
+      <c r="G170" s="8" t="inlineStr">
+        <is>
+          <t>https://assets.grab.com/wp-content/uploads/sites/4/2021/04/15151634/Grab_Logo_2021.jpg</t>
+        </is>
+      </c>
       <c r="H170" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -11531,15 +12647,19 @@
       </c>
       <c r="J170" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.90:1 (horizontal, 1200x630)</t>
         </is>
       </c>
       <c r="K170" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L170" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L170" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/sea/sg/grabpay.jpg</t>
+        </is>
+      </c>
       <c r="M170" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -11547,7 +12667,7 @@
       </c>
       <c r="N170" s="6" t="inlineStr">
         <is>
-          <t>Regional wallet - confirm whether one shared Grab asset or per-country rows are wanted (see duplicate-risk note in README).</t>
+          <t>Regional wallet - confirm whether one shared Grab asset or per-country rows are wanted (see duplicate-risk note in README). Auto-sourced via brand-press.</t>
         </is>
       </c>
     </row>
@@ -11646,7 +12766,11 @@
           <t>https://dash.com.sg</t>
         </is>
       </c>
-      <c r="G172" s="8" t="inlineStr"/>
+      <c r="G172" s="8" t="inlineStr">
+        <is>
+          <t>https://dash.com.sg/assets/images/general/site-thumbnail.png</t>
+        </is>
+      </c>
       <c r="H172" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -11659,15 +12783,19 @@
       </c>
       <c r="J172" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.90:1 (horizontal, 1200x630)</t>
         </is>
       </c>
       <c r="K172" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L172" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L172" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/sea/sg/dash.png</t>
+        </is>
+      </c>
       <c r="M172" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -11675,7 +12803,7 @@
       </c>
       <c r="N172" s="6" t="inlineStr">
         <is>
-          <t>Brief lists this as "Singtel Dash" - Singtel agreed to sell Dash to Western Union (announced Oct 2024). Use current post-transition branding, not the Singtel-badged asset.</t>
+          <t>Brief lists this as "Singtel Dash" - Singtel agreed to sell Dash to Western Union (announced Oct 2024). Use current post-transition branding, not the Singtel-badged asset. Auto-sourced via brand-press.</t>
         </is>
       </c>
     </row>
@@ -11710,7 +12838,11 @@
           <t>https://myfave.com</t>
         </is>
       </c>
-      <c r="G173" s="8" t="inlineStr"/>
+      <c r="G173" s="8" t="inlineStr">
+        <is>
+          <t>https://myfave.com/favicons/safari-pinned-tab.svg</t>
+        </is>
+      </c>
       <c r="H173" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -11723,15 +12855,19 @@
       </c>
       <c r="J173" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 700x700)</t>
         </is>
       </c>
       <c r="K173" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L173" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L173" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/sea/sg/favepay.svg</t>
+        </is>
+      </c>
       <c r="M173" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -11739,7 +12875,7 @@
       </c>
       <c r="N173" s="6" t="inlineStr">
         <is>
-          <t>Confirm current operating status and ownership (Pine Labs group) before sourcing.</t>
+          <t>Confirm current operating status and ownership (Pine Labs group) before sourcing. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -11774,7 +12910,11 @@
           <t>https://www.you.co</t>
         </is>
       </c>
-      <c r="G174" s="8" t="inlineStr"/>
+      <c r="G174" s="8" t="inlineStr">
+        <is>
+          <t>https://www.you.co/sg/wp-content/uploads/sites/2/2025/11/icon-512x512-1-300x300.png</t>
+        </is>
+      </c>
       <c r="H174" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -11787,15 +12927,19 @@
       </c>
       <c r="J174" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 300x300)</t>
         </is>
       </c>
       <c r="K174" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L174" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L174" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/sea/sg/youtrip.png</t>
+        </is>
+      </c>
       <c r="M174" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -11803,7 +12947,7 @@
       </c>
       <c r="N174" s="6" t="inlineStr">
         <is>
-          <t>Multi-currency card/wallet. Verify: MAS register.</t>
+          <t>Multi-currency card/wallet. Verify: MAS register. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -11838,7 +12982,11 @@
           <t>https://www.touchngo.com.my</t>
         </is>
       </c>
-      <c r="G175" s="8" t="inlineStr"/>
+      <c r="G175" s="8" t="inlineStr">
+        <is>
+          <t>https://www.touchngo.com.my/assets/press-release/putrabrandaward/TNGD_Putra-Brand-of-the-Year-Award.jpg</t>
+        </is>
+      </c>
       <c r="H175" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -11851,15 +12999,19 @@
       </c>
       <c r="J175" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.50:1 (horizontal, 2231x1487)</t>
         </is>
       </c>
       <c r="K175" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L175" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L175" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/sea/my/touch-n-go.jpg</t>
+        </is>
+      </c>
       <c r="M175" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -11867,7 +13019,7 @@
       </c>
       <c r="N175" s="6" t="inlineStr">
         <is>
-          <t>Market leader MY. Verify: BNM list.</t>
+          <t>Market leader MY. Verify: BNM list. Auto-sourced via brand-press.</t>
         </is>
       </c>
     </row>
@@ -11902,7 +13054,11 @@
           <t>https://www.grab.com/my/pay</t>
         </is>
       </c>
-      <c r="G176" s="8" t="inlineStr"/>
+      <c r="G176" s="8" t="inlineStr">
+        <is>
+          <t>https://assets.grab.com/wp-content/uploads/sites/8/2021/04/15153013/Grab_Logo_2021.jpg</t>
+        </is>
+      </c>
       <c r="H176" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -11915,15 +13071,19 @@
       </c>
       <c r="J176" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.90:1 (horizontal, 1200x630)</t>
         </is>
       </c>
       <c r="K176" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L176" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L176" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/sea/my/grabpay.jpg</t>
+        </is>
+      </c>
       <c r="M176" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -11931,7 +13091,7 @@
       </c>
       <c r="N176" s="6" t="inlineStr">
         <is>
-          <t>Same regional brand as sg/grabpay - confirm whether per-country duplication is intended.</t>
+          <t>Same regional brand as sg/grabpay - confirm whether per-country duplication is intended. Auto-sourced via brand-press.</t>
         </is>
       </c>
     </row>
@@ -11966,7 +13126,11 @@
           <t>https://myboost.com.my</t>
         </is>
       </c>
-      <c r="G177" s="8" t="inlineStr"/>
+      <c r="G177" s="8" t="inlineStr">
+        <is>
+          <t>https://myboost.co/themes/custom/boost_web/assets/img/logo.svg</t>
+        </is>
+      </c>
       <c r="H177" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -11979,15 +13143,19 @@
       </c>
       <c r="J177" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>3.13:1 (horizontal, 2033x649)</t>
         </is>
       </c>
       <c r="K177" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L177" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L177" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/sea/my/boost.svg</t>
+        </is>
+      </c>
       <c r="M177" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -11995,7 +13163,7 @@
       </c>
       <c r="N177" s="6" t="inlineStr">
         <is>
-          <t>Axiata group. Verify: BNM list.</t>
+          <t>Axiata group. Verify: BNM list. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -12030,7 +13198,11 @@
           <t>https://shopee.com.my</t>
         </is>
       </c>
-      <c r="G178" s="8" t="inlineStr"/>
+      <c r="G178" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/c9/4d/36/c94d36f7-8a91-d36c-8bed-2c331fe238bb/AppIcon-1x_U007ephone-0-1-0-0-85-220-0.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H178" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -12043,15 +13215,19 @@
       </c>
       <c r="J178" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K178" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L178" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L178" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/sea/my/shopeepay.png</t>
+        </is>
+      </c>
       <c r="M178" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -12059,7 +13235,7 @@
       </c>
       <c r="N178" s="6" t="inlineStr">
         <is>
-          <t>Same regional brand as indo/shopeepay - confirm whether per-country duplication is intended.</t>
+          <t>Same regional brand as indo/shopeepay - confirm whether per-country duplication is intended. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -12094,7 +13270,11 @@
           <t>https://www.bigpayme.com</t>
         </is>
       </c>
-      <c r="G179" s="8" t="inlineStr"/>
+      <c r="G179" s="8" t="inlineStr">
+        <is>
+          <t>https://bigpayme.com/assets/bigpay-logo-512.png</t>
+        </is>
+      </c>
       <c r="H179" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -12107,15 +13287,19 @@
       </c>
       <c r="J179" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 512x512)</t>
         </is>
       </c>
       <c r="K179" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L179" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L179" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/sea/my/bigpay.png</t>
+        </is>
+      </c>
       <c r="M179" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -12123,7 +13307,7 @@
       </c>
       <c r="N179" s="6" t="inlineStr">
         <is>
-          <t>Capital A/AirAsia group. Verify: BNM list.</t>
+          <t>Capital A/AirAsia group. Verify: BNM list. Auto-sourced via brand-press.</t>
         </is>
       </c>
     </row>
@@ -12158,7 +13342,11 @@
           <t>https://www.truemoney.com</t>
         </is>
       </c>
-      <c r="G180" s="8" t="inlineStr"/>
+      <c r="G180" s="8" t="inlineStr">
+        <is>
+          <t>https://www.truemoney.com/wp-content/uploads/2026/08/truemoney-icon-180.png</t>
+        </is>
+      </c>
       <c r="H180" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -12171,15 +13359,19 @@
       </c>
       <c r="J180" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 180x180)</t>
         </is>
       </c>
       <c r="K180" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L180" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L180" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/sea/th/truemoney.png</t>
+        </is>
+      </c>
       <c r="M180" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -12187,7 +13379,7 @@
       </c>
       <c r="N180" s="6" t="inlineStr">
         <is>
-          <t>Ascend Money group; operates across SEA incl. Indonesia. Verify: BOT register.</t>
+          <t>Ascend Money group; operates across SEA incl. Indonesia. Verify: BOT register. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -12222,7 +13414,11 @@
           <t>https://www.rabbitlinepay.com</t>
         </is>
       </c>
-      <c r="G181" s="8" t="inlineStr"/>
+      <c r="G181" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/3b/8b/f4/3b8bf408-788e-5059-05ab-e4857b3dd559/AppIcon-0-0-1x_U007emarketing-0-8-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H181" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -12235,15 +13431,19 @@
       </c>
       <c r="J181" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K181" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L181" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L181" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/sea/th/rabbit-line-pay.png</t>
+        </is>
+      </c>
       <c r="M181" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -12251,7 +13451,7 @@
       </c>
       <c r="N181" s="6" t="inlineStr">
         <is>
-          <t>Confirm current branding/ownership arrangement. Verify: BOT register.</t>
+          <t>Confirm current branding/ownership arrangement. Verify: BOT register. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -12350,7 +13550,11 @@
           <t>https://www.grab.com/th/pay</t>
         </is>
       </c>
-      <c r="G183" s="8" t="inlineStr"/>
+      <c r="G183" s="8" t="inlineStr">
+        <is>
+          <t>https://assets.grab.com/wp-content/uploads/sites/10/2021/04/15154415/Grab_Logo_2021.jpg</t>
+        </is>
+      </c>
       <c r="H183" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -12363,15 +13567,19 @@
       </c>
       <c r="J183" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.90:1 (horizontal, 1200x630)</t>
         </is>
       </c>
       <c r="K183" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L183" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L183" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/sea/th/grabpay.jpg</t>
+        </is>
+      </c>
       <c r="M183" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -12379,7 +13587,7 @@
       </c>
       <c r="N183" s="6" t="inlineStr">
         <is>
-          <t>Regional brand duplication - see README note.</t>
+          <t>Regional brand duplication - see README note. Auto-sourced via brand-press.</t>
         </is>
       </c>
     </row>
@@ -12414,7 +13622,11 @@
           <t>https://www.gcash.com</t>
         </is>
       </c>
-      <c r="G184" s="8" t="inlineStr"/>
+      <c r="G184" s="8" t="inlineStr">
+        <is>
+          <t>https://cdn.prod.website-files.com/6385b55675a0bd614777a5c1/6474928322d48888f6c8cfe5_biz-gcash-logo.svg</t>
+        </is>
+      </c>
       <c r="H184" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -12427,15 +13639,19 @@
       </c>
       <c r="J184" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.18:1 (horizontal, 72x61)</t>
         </is>
       </c>
       <c r="K184" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L184" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L184" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/sea/ph/gcash.svg</t>
+        </is>
+      </c>
       <c r="M184" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -12443,7 +13659,7 @@
       </c>
       <c r="N184" s="6" t="inlineStr">
         <is>
-          <t>Market leader PH. Verify: BSP directory.</t>
+          <t>Market leader PH. Verify: BSP directory. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -12478,7 +13694,11 @@
           <t>https://www.maya.ph</t>
         </is>
       </c>
-      <c r="G185" s="8" t="inlineStr"/>
+      <c r="G185" s="8" t="inlineStr">
+        <is>
+          <t>https://www.maya.ph/hubfs/Maya/money-green.svg</t>
+        </is>
+      </c>
       <c r="H185" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -12491,15 +13711,19 @@
       </c>
       <c r="J185" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>3.50:1 (horizontal, 147x42)</t>
         </is>
       </c>
       <c r="K185" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L185" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L185" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/sea/ph/maya.svg</t>
+        </is>
+      </c>
       <c r="M185" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -12507,7 +13731,7 @@
       </c>
       <c r="N185" s="6" t="inlineStr">
         <is>
-          <t>Rebranded from PayMaya - do NOT use legacy PayMaya asset. Verify: BSP directory.</t>
+          <t>Rebranded from PayMaya - do NOT use legacy PayMaya asset. Verify: BSP directory. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -12542,7 +13766,11 @@
           <t>https://www.grab.com/ph/pay</t>
         </is>
       </c>
-      <c r="G186" s="8" t="inlineStr"/>
+      <c r="G186" s="8" t="inlineStr">
+        <is>
+          <t>https://assets.grab.com/wp-content/uploads/sites/12/2021/04/15154552/Grab_Logo_2021.jpg</t>
+        </is>
+      </c>
       <c r="H186" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -12555,15 +13783,19 @@
       </c>
       <c r="J186" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.90:1 (horizontal, 1200x630)</t>
         </is>
       </c>
       <c r="K186" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L186" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L186" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/sea/ph/grabpay.jpg</t>
+        </is>
+      </c>
       <c r="M186" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -12571,7 +13803,7 @@
       </c>
       <c r="N186" s="6" t="inlineStr">
         <is>
-          <t>Regional brand duplication - see README note.</t>
+          <t>Regional brand duplication - see README note. Auto-sourced via brand-press.</t>
         </is>
       </c>
     </row>
@@ -12606,7 +13838,11 @@
           <t>https://coins.ph</t>
         </is>
       </c>
-      <c r="G187" s="8" t="inlineStr"/>
+      <c r="G187" s="8" t="inlineStr">
+        <is>
+          <t>https://exchange-prod-coins-landing.s3.ap-northeast-1.amazonaws.com/coins-landing/favicon_42b1136f5c.png</t>
+        </is>
+      </c>
       <c r="H187" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -12619,15 +13855,19 @@
       </c>
       <c r="J187" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 512x512)</t>
         </is>
       </c>
       <c r="K187" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L187" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L187" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/sea/ph/coins-ph.png</t>
+        </is>
+      </c>
       <c r="M187" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -12635,7 +13875,7 @@
       </c>
       <c r="N187" s="6" t="inlineStr">
         <is>
-          <t>Crypto-adjacent wallet - confirm it fits the intended payment-method grouping. Verify: BSP directory.</t>
+          <t>Crypto-adjacent wallet - confirm it fits the intended payment-method grouping. Verify: BSP directory. Auto-sourced via brand-press.</t>
         </is>
       </c>
     </row>
@@ -12670,7 +13910,11 @@
           <t>https://momo.vn</t>
         </is>
       </c>
-      <c r="G188" s="8" t="inlineStr"/>
+      <c r="G188" s="8" t="inlineStr">
+        <is>
+          <t>https://homepage.momocdn.net/img/momo-amazone-s3-api-241023152559-638652939595693626.png</t>
+        </is>
+      </c>
       <c r="H188" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -12683,15 +13927,19 @@
       </c>
       <c r="J188" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 180x180)</t>
         </is>
       </c>
       <c r="K188" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L188" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L188" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/sea/vn/momo.png</t>
+        </is>
+      </c>
       <c r="M188" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -12699,7 +13947,7 @@
       </c>
       <c r="N188" s="6" t="inlineStr">
         <is>
-          <t>Market leader VN. Verify: SBV list.</t>
+          <t>Market leader VN. Verify: SBV list. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -12734,7 +13982,11 @@
           <t>https://zalopay.vn</t>
         </is>
       </c>
-      <c r="G189" s="8" t="inlineStr"/>
+      <c r="G189" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/8b/26/d5/8b26d5b4-c2ad-9324-0130-4c281ea02676/AppIcon-0-0-1x_U007emarketing-0-6-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H189" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -12747,15 +13999,19 @@
       </c>
       <c r="J189" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K189" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L189" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L189" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/sea/vn/zalopay.png</t>
+        </is>
+      </c>
       <c r="M189" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -12763,7 +14019,7 @@
       </c>
       <c r="N189" s="6" t="inlineStr">
         <is>
-          <t>Rebranded in recent years - use current asset. Verify: SBV list.</t>
+          <t>Rebranded in recent years - use current asset. Verify: SBV list. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -12798,7 +14054,11 @@
           <t>https://vnpay.vn</t>
         </is>
       </c>
-      <c r="G190" s="8" t="inlineStr"/>
+      <c r="G190" s="8" t="inlineStr">
+        <is>
+          <t>https://1889324617.cloud.edgevnpay.vn/assets/images/logo-icon/logo-primary.svg</t>
+        </is>
+      </c>
       <c r="H190" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -12811,15 +14071,19 @@
       </c>
       <c r="J190" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>3.29:1 (horizontal, 138x42)</t>
         </is>
       </c>
       <c r="K190" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L190" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L190" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/sea/vn/vnpay.svg</t>
+        </is>
+      </c>
       <c r="M190" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -12827,7 +14091,7 @@
       </c>
       <c r="N190" s="6" t="inlineStr">
         <is>
-          <t>Primarily a payment gateway/QR scheme - confirm category fit. Verify: SBV list.</t>
+          <t>Primarily a payment gateway/QR scheme - confirm category fit. Verify: SBV list. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -12970,7 +14234,11 @@
           <t>https://www.wingmoney.com</t>
         </is>
       </c>
-      <c r="G193" s="8" t="inlineStr"/>
+      <c r="G193" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/95/cd/f4/95cdf484-1e7a-b024-87aa-9edc35d3482c/AppIcon-0-0-1x_U007ephone-0-1-0-sRGB-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H193" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -12983,15 +14251,19 @@
       </c>
       <c r="J193" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K193" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L193" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L193" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/sea/kh/wing.png</t>
+        </is>
+      </c>
       <c r="M193" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -12999,7 +14271,7 @@
       </c>
       <c r="N193" s="6" t="inlineStr">
         <is>
-          <t>Verify: NBC list. Lower-priority market per brief.</t>
+          <t>Verify: NBC list. Lower-priority market per brief. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -13078,7 +14350,11 @@
           <t>https://www.bcel.com.la</t>
         </is>
       </c>
-      <c r="G195" s="8" t="inlineStr"/>
+      <c r="G195" s="8" t="inlineStr">
+        <is>
+          <t>https://www.bcel.com.la/bcel/resources/imgs/ibank1_1.png</t>
+        </is>
+      </c>
       <c r="H195" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -13091,15 +14367,19 @@
       </c>
       <c r="J195" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.03:1 (square, 130x126)</t>
         </is>
       </c>
       <c r="K195" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L195" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L195" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/sea/la/bcel-one.png</t>
+        </is>
+      </c>
       <c r="M195" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -13107,7 +14387,7 @@
       </c>
       <c r="N195" s="6" t="inlineStr">
         <is>
-          <t>Mobile app of BCEL. Lower-priority market; limited asset availability expected.</t>
+          <t>Mobile app of BCEL. Lower-priority market; limited asset availability expected. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -13142,7 +14422,11 @@
           <t>https://www.hsbc.com</t>
         </is>
       </c>
-      <c r="G196" s="8" t="inlineStr"/>
+      <c r="G196" s="8" t="inlineStr">
+        <is>
+          <t>https://www.hsbc.com/-/files/hsbc/header/hsbc-logo-200x25.svg?la=en-GB&amp;h=25&amp;hash=FCDFB4DC1991B6B5EE0AB98E7208CB82</t>
+        </is>
+      </c>
       <c r="H196" s="8" t="inlineStr">
         <is>
           <t>icon</t>
@@ -13155,15 +14439,19 @@
       </c>
       <c r="J196" s="8" t="inlineStr">
         <is>
-          <t>TBD (square-ish)</t>
+          <t>3.71:1 (horizontal, 315x85)</t>
         </is>
       </c>
       <c r="K196" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L196" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L196" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/gb/hsbc.svg</t>
+        </is>
+      </c>
       <c r="M196" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -13171,7 +14459,7 @@
       </c>
       <c r="N196" s="6" t="inlineStr">
         <is>
-          <t>Globally recognised; relevant to Indonesian cross-border transfers. Path renamed from a flat banks/international/{name} to the country-scoped convention when the international list expanded to cover Wise/PandaRemit corridors.</t>
+          <t>Globally recognised; relevant to Indonesian cross-border transfers. Path renamed from a flat banks/international/{name} to the country-scoped convention when the international list expanded to cover Wise/PandaRemit corridors. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -13206,7 +14494,11 @@
           <t>https://www.citi.com</t>
         </is>
       </c>
-      <c r="G197" s="8" t="inlineStr"/>
+      <c r="G197" s="8" t="inlineStr">
+        <is>
+          <t>https://www.citi.com/cbol-hp-static-assets/assets/favicon.ico</t>
+        </is>
+      </c>
       <c r="H197" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -13219,15 +14511,19 @@
       </c>
       <c r="J197" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 367x367)</t>
         </is>
       </c>
       <c r="K197" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L197" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L197" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/us/citibank.png</t>
+        </is>
+      </c>
       <c r="M197" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -13235,7 +14531,7 @@
       </c>
       <c r="N197" s="6" t="inlineStr">
         <is>
-          <t>Globally recognised. Path renamed from a flat banks/international/{name} to the country-scoped convention when the international list expanded to cover Wise/PandaRemit corridors.</t>
+          <t>Globally recognised. Path renamed from a flat banks/international/{name} to the country-scoped convention when the international list expanded to cover Wise/PandaRemit corridors. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -13334,7 +14630,11 @@
           <t>https://www.chase.com</t>
         </is>
       </c>
-      <c r="G199" s="8" t="inlineStr"/>
+      <c r="G199" s="8" t="inlineStr">
+        <is>
+          <t>https://www.chase.com/content/dam/unified-assets/logo/chase/chase-logo/additional-file-formats/logo_chase_headerfooter.svg</t>
+        </is>
+      </c>
       <c r="H199" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -13347,15 +14647,19 @@
       </c>
       <c r="J199" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>5.25:1 (horizontal, 126x24)</t>
         </is>
       </c>
       <c r="K199" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L199" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L199" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/us/jpmorgan-chase.svg</t>
+        </is>
+      </c>
       <c r="M199" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -13363,7 +14667,7 @@
       </c>
       <c r="N199" s="6" t="inlineStr">
         <is>
-          <t>Largest US bank by assets. Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Largest US bank by assets. Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -13398,7 +14702,11 @@
           <t>https://www.bankofamerica.com</t>
         </is>
       </c>
-      <c r="G200" s="8" t="inlineStr"/>
+      <c r="G200" s="8" t="inlineStr">
+        <is>
+          <t>https://www.bankofamerica.com/homepage/spa-assets/images/assets-images-global-favicon-safari-pinned-tab-CSX1aebeef6.svg</t>
+        </is>
+      </c>
       <c r="H200" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -13411,15 +14719,19 @@
       </c>
       <c r="J200" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 152x152)</t>
         </is>
       </c>
       <c r="K200" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L200" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L200" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/us/bank-of-america.svg</t>
+        </is>
+      </c>
       <c r="M200" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -13427,7 +14739,7 @@
       </c>
       <c r="N200" s="6" t="inlineStr">
         <is>
-          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -13462,7 +14774,11 @@
           <t>https://www.wellsfargo.com</t>
         </is>
       </c>
-      <c r="G201" s="8" t="inlineStr"/>
+      <c r="G201" s="8" t="inlineStr">
+        <is>
+          <t>https://www17.wellsfargomedia.com/assets/images/rwd/wf_logo_220x23.png</t>
+        </is>
+      </c>
       <c r="H201" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -13475,15 +14791,19 @@
       </c>
       <c r="J201" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>9.57:1 (horizontal, 220x23)</t>
         </is>
       </c>
       <c r="K201" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L201" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L201" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/us/wells-fargo.png</t>
+        </is>
+      </c>
       <c r="M201" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -13491,7 +14811,7 @@
       </c>
       <c r="N201" s="6" t="inlineStr">
         <is>
-          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -13526,7 +14846,11 @@
           <t>https://www.capitalone.com</t>
         </is>
       </c>
-      <c r="G202" s="8" t="inlineStr"/>
+      <c r="G202" s="8" t="inlineStr">
+        <is>
+          <t>https://ecm.capitalone.com/WCM/homepage/photos/more-than-a-bank/paze_logo.svg</t>
+        </is>
+      </c>
       <c r="H202" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -13539,15 +14863,19 @@
       </c>
       <c r="J202" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>3.12:1 (horizontal, 100x32)</t>
         </is>
       </c>
       <c r="K202" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L202" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L202" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/us/capital-one.svg</t>
+        </is>
+      </c>
       <c r="M202" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -13555,7 +14883,7 @@
       </c>
       <c r="N202" s="6" t="inlineStr">
         <is>
-          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -13590,7 +14918,11 @@
           <t>https://www.usbank.com</t>
         </is>
       </c>
-      <c r="G203" s="8" t="inlineStr"/>
+      <c r="G203" s="8" t="inlineStr">
+        <is>
+          <t>https://www.usbank.com/etc.clientlibs/ecm-global/clientlibs/clientlib-resources/resources/images/svg/logo-personal.svg</t>
+        </is>
+      </c>
       <c r="H203" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -13603,15 +14935,19 @@
       </c>
       <c r="J203" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>3.58:1 (horizontal, 258x72)</t>
         </is>
       </c>
       <c r="K203" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L203" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L203" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/us/us-bank.svg</t>
+        </is>
+      </c>
       <c r="M203" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -13619,7 +14955,7 @@
       </c>
       <c r="N203" s="6" t="inlineStr">
         <is>
-          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -13654,7 +14990,11 @@
           <t>https://www.pnc.com</t>
         </is>
       </c>
-      <c r="G204" s="8" t="inlineStr"/>
+      <c r="G204" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/25/26/e7/2526e7be-dd92-52b9-e618-606dcac1e3ea/AppIcon_Glass-0-0-1x_U007epad-0-1-0-sRGB-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H204" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -13667,15 +15007,19 @@
       </c>
       <c r="J204" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K204" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L204" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L204" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/us/pnc-bank.png</t>
+        </is>
+      </c>
       <c r="M204" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -13683,7 +15027,7 @@
       </c>
       <c r="N204" s="6" t="inlineStr">
         <is>
-          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -13718,7 +15062,11 @@
           <t>https://www.chime.com</t>
         </is>
       </c>
-      <c r="G205" s="8" t="inlineStr"/>
+      <c r="G205" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/99/f0/08/99f008b7-df22-1dde-beaa-a1cab754f107/AppIcon-0-0-1x_U007emarketing-0-6-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H205" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -13731,15 +15079,19 @@
       </c>
       <c r="J205" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K205" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L205" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L205" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/us/chime.png</t>
+        </is>
+      </c>
       <c r="M205" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -13747,7 +15099,7 @@
       </c>
       <c r="N205" s="6" t="inlineStr">
         <is>
-          <t>Digital-only neobank; app icon is the recognised mark. Popular receiving account for remittances to US-based students/workers. Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Digital-only neobank; app icon is the recognised mark. Popular receiving account for remittances to US-based students/workers. Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -13782,7 +15134,11 @@
           <t>https://www.barclays.co.uk</t>
         </is>
       </c>
-      <c r="G206" s="8" t="inlineStr"/>
+      <c r="G206" s="8" t="inlineStr">
+        <is>
+          <t>https://www.barclays.co.uk/content/dam/icons/favicons/barclays/Wordmark_RGB_Cyan_Large.svg</t>
+        </is>
+      </c>
       <c r="H206" s="8" t="inlineStr">
         <is>
           <t>icon</t>
@@ -13795,15 +15151,19 @@
       </c>
       <c r="J206" s="8" t="inlineStr">
         <is>
-          <t>TBD (square-ish)</t>
+          <t>6.03:1 (horizontal, 1410x234)</t>
         </is>
       </c>
       <c r="K206" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L206" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L206" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/gb/barclays.svg</t>
+        </is>
+      </c>
       <c r="M206" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -13811,7 +15171,7 @@
       </c>
       <c r="N206" s="6" t="inlineStr">
         <is>
-          <t>Eagle symbol used standalone in UK banking UI. Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Eagle symbol used standalone in UK banking UI. Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -13846,7 +15206,11 @@
           <t>https://www.lloydsbank.com</t>
         </is>
       </c>
-      <c r="G207" s="8" t="inlineStr"/>
+      <c r="G207" s="8" t="inlineStr">
+        <is>
+          <t>https://www.lloydsbank.com/apple-touch-icon.png</t>
+        </is>
+      </c>
       <c r="H207" s="8" t="inlineStr">
         <is>
           <t>icon</t>
@@ -13859,15 +15223,19 @@
       </c>
       <c r="J207" s="8" t="inlineStr">
         <is>
-          <t>TBD (square-ish)</t>
+          <t>1.00:1 (square, 460x460)</t>
         </is>
       </c>
       <c r="K207" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L207" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L207" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/gb/lloyds-bank.png</t>
+        </is>
+      </c>
       <c r="M207" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -13875,7 +15243,7 @@
       </c>
       <c r="N207" s="6" t="inlineStr">
         <is>
-          <t>Black horse symbol used standalone. Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Black horse symbol used standalone. Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -13910,7 +15278,11 @@
           <t>https://www.natwest.com</t>
         </is>
       </c>
-      <c r="G208" s="8" t="inlineStr"/>
+      <c r="G208" s="8" t="inlineStr">
+        <is>
+          <t>https://www.natwest.com/content/dam/championlogos/Natwest_Secondary_Horizontal_RGB_NEG.svg</t>
+        </is>
+      </c>
       <c r="H208" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -13923,15 +15295,19 @@
       </c>
       <c r="J208" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>2.88:1 (horizontal, 288x100)</t>
         </is>
       </c>
       <c r="K208" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L208" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L208" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/gb/natwest.svg</t>
+        </is>
+      </c>
       <c r="M208" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -13939,7 +15315,7 @@
       </c>
       <c r="N208" s="6" t="inlineStr">
         <is>
-          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -13974,7 +15350,11 @@
           <t>https://www.santander.co.uk</t>
         </is>
       </c>
-      <c r="G209" s="8" t="inlineStr"/>
+      <c r="G209" s="8" t="inlineStr">
+        <is>
+          <t>https://www.santander.co.uk/themes/custom/santander_web18_2_0/logo.svg</t>
+        </is>
+      </c>
       <c r="H209" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -13987,15 +15367,19 @@
       </c>
       <c r="J209" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>5.67:1 (horizontal, 816x144)</t>
         </is>
       </c>
       <c r="K209" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L209" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L209" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/gb/santander-uk.svg</t>
+        </is>
+      </c>
       <c r="M209" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -14003,7 +15387,7 @@
       </c>
       <c r="N209" s="6" t="inlineStr">
         <is>
-          <t>Local arm of the Spanish group; distinct brand identity from Santander in other markets. Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Local arm of the Spanish group; distinct brand identity from Santander in other markets. Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -14038,7 +15422,11 @@
           <t>https://monzo.com</t>
         </is>
       </c>
-      <c r="G210" s="8" t="inlineStr"/>
+      <c r="G210" s="8" t="inlineStr">
+        <is>
+          <t>https://static-assets.monzo.com/monzo-com/039b8b32b7ae63535e8bdcbc5f1b220079e3a214/_next/static/media/favicon.4c6ebc6f.svg</t>
+        </is>
+      </c>
       <c r="H210" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -14051,15 +15439,19 @@
       </c>
       <c r="J210" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.11:1 (horizontal, 1024x926)</t>
         </is>
       </c>
       <c r="K210" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L210" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L210" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/gb/monzo.svg</t>
+        </is>
+      </c>
       <c r="M210" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -14067,7 +15459,7 @@
       </c>
       <c r="N210" s="6" t="inlineStr">
         <is>
-          <t>Digital-only neobank; coral-colored app icon is the recognised mark. Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Digital-only neobank; coral-colored app icon is the recognised mark. Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via brand-press.</t>
         </is>
       </c>
     </row>
@@ -14102,7 +15494,11 @@
           <t>https://www.deutsche-bank.de</t>
         </is>
       </c>
-      <c r="G211" s="8" t="inlineStr"/>
+      <c r="G211" s="8" t="inlineStr">
+        <is>
+          <t>https://www.deutsche-bank.de/etc/designs/db-eccs-pws-pwcc/assets/favicon.svg?v=1756713258208</t>
+        </is>
+      </c>
       <c r="H211" s="8" t="inlineStr">
         <is>
           <t>icon</t>
@@ -14115,15 +15511,19 @@
       </c>
       <c r="J211" s="8" t="inlineStr">
         <is>
-          <t>TBD (square-ish)</t>
+          <t>1.00:1 (square, 32x32)</t>
         </is>
       </c>
       <c r="K211" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L211" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L211" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/de/deutsche-bank.svg</t>
+        </is>
+      </c>
       <c r="M211" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -14131,7 +15531,7 @@
       </c>
       <c r="N211" s="6" t="inlineStr">
         <is>
-          <t>Slash-in-square symbol used standalone. Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Slash-in-square symbol used standalone. Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -14166,7 +15566,11 @@
           <t>https://www.commerzbank.de</t>
         </is>
       </c>
-      <c r="G212" s="8" t="inlineStr"/>
+      <c r="G212" s="8" t="inlineStr">
+        <is>
+          <t>https://www.commerzbank.de/ms/media/favicons/apple-touch-icon-144x144_A.png</t>
+        </is>
+      </c>
       <c r="H212" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -14179,15 +15583,19 @@
       </c>
       <c r="J212" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 144x144)</t>
         </is>
       </c>
       <c r="K212" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L212" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L212" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/de/commerzbank.png</t>
+        </is>
+      </c>
       <c r="M212" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -14195,7 +15603,7 @@
       </c>
       <c r="N212" s="6" t="inlineStr">
         <is>
-          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -14230,7 +15638,11 @@
           <t>https://n26.com</t>
         </is>
       </c>
-      <c r="G213" s="8" t="inlineStr"/>
+      <c r="G213" s="8" t="inlineStr">
+        <is>
+          <t>https://n26.com/_build/logo-256x256.png</t>
+        </is>
+      </c>
       <c r="H213" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -14243,15 +15655,19 @@
       </c>
       <c r="J213" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 256x256)</t>
         </is>
       </c>
       <c r="K213" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L213" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L213" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/de/n26.png</t>
+        </is>
+      </c>
       <c r="M213" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -14259,7 +15675,7 @@
       </c>
       <c r="N213" s="6" t="inlineStr">
         <is>
-          <t>Digital-only neobank; app icon is the recognised mark. Common receiving account for Indonesian students in Germany. Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Digital-only neobank; app icon is the recognised mark. Common receiving account for Indonesian students in Germany. Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via brand-press.</t>
         </is>
       </c>
     </row>
@@ -14294,7 +15710,11 @@
           <t>https://www.bnpparibas.com</t>
         </is>
       </c>
-      <c r="G214" s="8" t="inlineStr"/>
+      <c r="G214" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/4c/55/b6/4c55b610-8308-25c0-1671-a3a3c961928b/AppIcon-0-0-1x_U007epad-0-1-0-0-0-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H214" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -14307,15 +15727,19 @@
       </c>
       <c r="J214" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K214" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L214" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L214" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/fr/bnp-paribas.png</t>
+        </is>
+      </c>
       <c r="M214" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -14323,7 +15747,7 @@
       </c>
       <c r="N214" s="6" t="inlineStr">
         <is>
-          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -14358,7 +15782,11 @@
           <t>https://www.societegenerale.com</t>
         </is>
       </c>
-      <c r="G215" s="8" t="inlineStr"/>
+      <c r="G215" s="8" t="inlineStr">
+        <is>
+          <t>https://www.societegenerale.com/sites/default/files/image/logo/soc103c-1-0.svg</t>
+        </is>
+      </c>
       <c r="H215" s="8" t="inlineStr">
         <is>
           <t>icon</t>
@@ -14371,15 +15799,19 @@
       </c>
       <c r="J215" s="8" t="inlineStr">
         <is>
-          <t>TBD (square-ish)</t>
+          <t>5.00:1 (horizontal, 145x29)</t>
         </is>
       </c>
       <c r="K215" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L215" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L215" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/fr/societe-generale.svg</t>
+        </is>
+      </c>
       <c r="M215" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -14387,7 +15819,7 @@
       </c>
       <c r="N215" s="6" t="inlineStr">
         <is>
-          <t>Red/black square symbol used standalone. Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Red/black square symbol used standalone. Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via brand-press.</t>
         </is>
       </c>
     </row>
@@ -14422,7 +15854,11 @@
           <t>https://www.credit-agricole.com</t>
         </is>
       </c>
-      <c r="G216" s="8" t="inlineStr"/>
+      <c r="G216" s="8" t="inlineStr">
+        <is>
+          <t>https://www.credit-agricole.com/assets/build/images/logos/youtube-logo.svg</t>
+        </is>
+      </c>
       <c r="H216" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -14435,15 +15871,19 @@
       </c>
       <c r="J216" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 512x512)</t>
         </is>
       </c>
       <c r="K216" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L216" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L216" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/fr/credit-agricole.svg</t>
+        </is>
+      </c>
       <c r="M216" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -14451,7 +15891,7 @@
       </c>
       <c r="N216" s="6" t="inlineStr">
         <is>
-          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -14486,7 +15926,11 @@
           <t>https://www.ing.nl</t>
         </is>
       </c>
-      <c r="G217" s="8" t="inlineStr"/>
+      <c r="G217" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/4e/22/1c/4e221cfa-d19b-971d-1e67-1b41205678e5/AppIcon-0-0-1x_U007emarketing-0-11-0-sRGB-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H217" s="8" t="inlineStr">
         <is>
           <t>icon</t>
@@ -14499,15 +15943,19 @@
       </c>
       <c r="J217" s="8" t="inlineStr">
         <is>
-          <t>TBD (square-ish)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K217" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L217" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L217" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/nl/ing.png</t>
+        </is>
+      </c>
       <c r="M217" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -14515,7 +15963,7 @@
       </c>
       <c r="N217" s="6" t="inlineStr">
         <is>
-          <t>Orange lion symbol used standalone. Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Orange lion symbol used standalone. Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -14550,7 +15998,11 @@
           <t>https://www.abnamro.nl</t>
         </is>
       </c>
-      <c r="G218" s="8" t="inlineStr"/>
+      <c r="G218" s="8" t="inlineStr">
+        <is>
+          <t>https://www.abnamro.nl/favicon.svg</t>
+        </is>
+      </c>
       <c r="H218" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -14563,15 +16015,19 @@
       </c>
       <c r="J218" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 24x24)</t>
         </is>
       </c>
       <c r="K218" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L218" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L218" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/nl/abn-amro.svg</t>
+        </is>
+      </c>
       <c r="M218" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -14579,7 +16035,7 @@
       </c>
       <c r="N218" s="6" t="inlineStr">
         <is>
-          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -14614,7 +16070,11 @@
           <t>https://www.rabobank.nl</t>
         </is>
       </c>
-      <c r="G219" s="8" t="inlineStr"/>
+      <c r="G219" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/f5/d8/21/f5d82166-92b0-f57e-06cc-28fae7d4c60d/AppIconGlass-0-0-1x_U007epad-0-1-0-sRGB-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H219" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -14627,15 +16087,19 @@
       </c>
       <c r="J219" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K219" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L219" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L219" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/nl/rabobank.png</t>
+        </is>
+      </c>
       <c r="M219" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -14643,7 +16107,7 @@
       </c>
       <c r="N219" s="6" t="inlineStr">
         <is>
-          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -14678,7 +16142,11 @@
           <t>https://www.boc.cn</t>
         </is>
       </c>
-      <c r="G220" s="8" t="inlineStr"/>
+      <c r="G220" s="8" t="inlineStr">
+        <is>
+          <t>https://www.boc.cn/images/LOGO-AGACCS.gif</t>
+        </is>
+      </c>
       <c r="H220" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -14691,15 +16159,19 @@
       </c>
       <c r="J220" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>2.20:1 (horizontal, 132x60)</t>
         </is>
       </c>
       <c r="K220" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L220" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L220" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/cn/bank-of-china.png</t>
+        </is>
+      </c>
       <c r="M220" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -14707,7 +16179,7 @@
       </c>
       <c r="N220" s="6" t="inlineStr">
         <is>
-          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -14742,7 +16214,11 @@
           <t>https://www.icbc.com.cn</t>
         </is>
       </c>
-      <c r="G221" s="8" t="inlineStr"/>
+      <c r="G221" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/4a/66/33/4a6633a2-8ad8-0a7a-c145-e87992c20816/AppIcon-0-0-1x_U007emarketing-0-7-0-sRGB-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H221" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -14755,15 +16231,19 @@
       </c>
       <c r="J221" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K221" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L221" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L221" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/cn/icbc.png</t>
+        </is>
+      </c>
       <c r="M221" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -14771,7 +16251,7 @@
       </c>
       <c r="N221" s="6" t="inlineStr">
         <is>
-          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -14870,7 +16350,11 @@
           <t>https://www.abchina.com</t>
         </is>
       </c>
-      <c r="G223" s="8" t="inlineStr"/>
+      <c r="G223" s="8" t="inlineStr">
+        <is>
+          <t>http://www.abchina.com/cn/images/logo_ue2.png</t>
+        </is>
+      </c>
       <c r="H223" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -14883,15 +16367,19 @@
       </c>
       <c r="J223" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>4.58:1 (horizontal, 220x48)</t>
         </is>
       </c>
       <c r="K223" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L223" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L223" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/cn/agricultural-bank-of-china.png</t>
+        </is>
+      </c>
       <c r="M223" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -14899,7 +16387,7 @@
       </c>
       <c r="N223" s="6" t="inlineStr">
         <is>
-          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -14934,7 +16422,11 @@
           <t>https://www.cmbchina.com</t>
         </is>
       </c>
-      <c r="G224" s="8" t="inlineStr"/>
+      <c r="G224" s="8" t="inlineStr">
+        <is>
+          <t>https://wwwcdn.cmbimg.com/Images/logo.png</t>
+        </is>
+      </c>
       <c r="H224" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -14947,15 +16439,19 @@
       </c>
       <c r="J224" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1:1.11 (vertical, 132x146)</t>
         </is>
       </c>
       <c r="K224" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L224" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L224" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/cn/china-merchants-bank.png</t>
+        </is>
+      </c>
       <c r="M224" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -14963,7 +16459,7 @@
       </c>
       <c r="N224" s="6" t="inlineStr">
         <is>
-          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -14998,7 +16494,11 @@
           <t>https://www.commbank.com.au</t>
         </is>
       </c>
-      <c r="G225" s="8" t="inlineStr"/>
+      <c r="G225" s="8" t="inlineStr">
+        <is>
+          <t>https://www.commbank.com.au/content/dam/commbank/commBank-logo.svg</t>
+        </is>
+      </c>
       <c r="H225" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -15011,15 +16511,19 @@
       </c>
       <c r="J225" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 64x64)</t>
         </is>
       </c>
       <c r="K225" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L225" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L225" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/au/commonwealth-bank.svg</t>
+        </is>
+      </c>
       <c r="M225" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -15027,7 +16531,7 @@
       </c>
       <c r="N225" s="6" t="inlineStr">
         <is>
-          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via brand-press.</t>
         </is>
       </c>
     </row>
@@ -15062,7 +16566,11 @@
           <t>https://www.westpac.com.au</t>
         </is>
       </c>
-      <c r="G226" s="8" t="inlineStr"/>
+      <c r="G226" s="8" t="inlineStr">
+        <is>
+          <t>https://www.westpac.com.au/content/dam/public/wbc/images/home/westpac-logo-social.jpg</t>
+        </is>
+      </c>
       <c r="H226" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -15075,15 +16583,19 @@
       </c>
       <c r="J226" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.90:1 (horizontal, 1200x630)</t>
         </is>
       </c>
       <c r="K226" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L226" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L226" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/au/westpac.jpg</t>
+        </is>
+      </c>
       <c r="M226" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -15091,7 +16603,7 @@
       </c>
       <c r="N226" s="6" t="inlineStr">
         <is>
-          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -15126,7 +16638,11 @@
           <t>https://www.anz.com.au</t>
         </is>
       </c>
-      <c r="G227" s="8" t="inlineStr"/>
+      <c r="G227" s="8" t="inlineStr">
+        <is>
+          <t>https://www.anz.com.au/apps/settings/wcm/designs/commons/images/appicons/apple-touch-icon-152x152.png</t>
+        </is>
+      </c>
       <c r="H227" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -15139,15 +16655,19 @@
       </c>
       <c r="J227" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 152x152)</t>
         </is>
       </c>
       <c r="K227" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L227" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L227" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/au/anz-australia.png</t>
+        </is>
+      </c>
       <c r="M227" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -15155,7 +16675,7 @@
       </c>
       <c r="N227" s="6" t="inlineStr">
         <is>
-          <t>AU/NZ parent group - distinct row from banks/indo/anz-indonesia (consumer business there has since exited; confirm current scope). Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>AU/NZ parent group - distinct row from banks/indo/anz-indonesia (consumer business there has since exited; confirm current scope). Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -15190,7 +16710,11 @@
           <t>https://www.nab.com.au</t>
         </is>
       </c>
-      <c r="G228" s="8" t="inlineStr"/>
+      <c r="G228" s="8" t="inlineStr">
+        <is>
+          <t>https://www.nab.com.au/content/dam/nab/images/types/banners/banker-with-customers-smiling-3000x1000.JPG</t>
+        </is>
+      </c>
       <c r="H228" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -15203,15 +16727,19 @@
       </c>
       <c r="J228" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>3.00:1 (horizontal, 3000x1000)</t>
         </is>
       </c>
       <c r="K228" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L228" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L228" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/au/nab.jpg</t>
+        </is>
+      </c>
       <c r="M228" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -15219,7 +16747,7 @@
       </c>
       <c r="N228" s="6" t="inlineStr">
         <is>
-          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -15254,7 +16782,11 @@
           <t>https://www.rbc.com</t>
         </is>
       </c>
-      <c r="G229" s="8" t="inlineStr"/>
+      <c r="G229" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple211/v4/0b/dd/cd/0bddcd59-76bc-29ec-61c8-0adb3a5f0b79/RBCMobile-0-0-1x_U007epad-0-1-0-sRGB-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H229" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -15267,15 +16799,19 @@
       </c>
       <c r="J229" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K229" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L229" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L229" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/ca/rbc.png</t>
+        </is>
+      </c>
       <c r="M229" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -15283,7 +16819,7 @@
       </c>
       <c r="N229" s="6" t="inlineStr">
         <is>
-          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -15318,7 +16854,11 @@
           <t>https://www.td.com</t>
         </is>
       </c>
-      <c r="G230" s="8" t="inlineStr"/>
+      <c r="G230" s="8" t="inlineStr">
+        <is>
+          <t>https://www.td.com/content/dam/tdcom/shared/social-media-thumbnail.png</t>
+        </is>
+      </c>
       <c r="H230" s="8" t="inlineStr">
         <is>
           <t>icon</t>
@@ -15331,15 +16871,19 @@
       </c>
       <c r="J230" s="8" t="inlineStr">
         <is>
-          <t>TBD (square-ish)</t>
+          <t>1.90:1 (horizontal, 1200x630)</t>
         </is>
       </c>
       <c r="K230" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L230" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L230" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/ca/td-bank.png</t>
+        </is>
+      </c>
       <c r="M230" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -15347,7 +16891,7 @@
       </c>
       <c r="N230" s="6" t="inlineStr">
         <is>
-          <t>Green shield symbol used standalone. Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Green shield symbol used standalone. Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -15382,7 +16926,11 @@
           <t>https://www.scotiabank.com</t>
         </is>
       </c>
-      <c r="G231" s="8" t="inlineStr"/>
+      <c r="G231" s="8" t="inlineStr">
+        <is>
+          <t>https://www.scotiabank.com/content/dam/scotiabank/images/logos/2019/scotiabank-logo-red-desktop-200px.svg</t>
+        </is>
+      </c>
       <c r="H231" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -15395,15 +16943,19 @@
       </c>
       <c r="J231" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>7.14:1 (horizontal, 207x29)</t>
         </is>
       </c>
       <c r="K231" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L231" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L231" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/ca/scotiabank.svg</t>
+        </is>
+      </c>
       <c r="M231" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -15411,7 +16963,7 @@
       </c>
       <c r="N231" s="6" t="inlineStr">
         <is>
-          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -15446,7 +16998,11 @@
           <t>https://www.bk.mufg.jp</t>
         </is>
       </c>
-      <c r="G232" s="8" t="inlineStr"/>
+      <c r="G232" s="8" t="inlineStr">
+        <is>
+          <t>https://www.bk.mufg.jp/shared2019/imgs/logo-20th.svg</t>
+        </is>
+      </c>
       <c r="H232" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -15459,15 +17015,19 @@
       </c>
       <c r="J232" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.41:1 (horizontal, 41x29)</t>
         </is>
       </c>
       <c r="K232" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L232" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L232" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/jp/mufg-bank.svg</t>
+        </is>
+      </c>
       <c r="M232" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -15475,7 +17035,7 @@
       </c>
       <c r="N232" s="6" t="inlineStr">
         <is>
-          <t>JP parent - distinct row from banks/indo/mufg-indonesia. Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>JP parent - distinct row from banks/indo/mufg-indonesia. Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -15510,7 +17070,11 @@
           <t>https://www.smbc.co.jp</t>
         </is>
       </c>
-      <c r="G233" s="8" t="inlineStr"/>
+      <c r="G233" s="8" t="inlineStr">
+        <is>
+          <t>https://www.smbc.co.jp/apple-touch-icon.png</t>
+        </is>
+      </c>
       <c r="H233" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -15523,15 +17087,19 @@
       </c>
       <c r="J233" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 192x192)</t>
         </is>
       </c>
       <c r="K233" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L233" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L233" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/jp/smbc.png</t>
+        </is>
+      </c>
       <c r="M233" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -15539,7 +17107,7 @@
       </c>
       <c r="N233" s="6" t="inlineStr">
         <is>
-          <t>JP parent - distinct from Bank SMBC Indonesia (the renamed ex-BTPN), which has its own local identity. Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>JP parent - distinct from Bank SMBC Indonesia (the renamed ex-BTPN), which has its own local identity. Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -15574,7 +17142,11 @@
           <t>https://www.jp-bank.japanpost.jp</t>
         </is>
       </c>
-      <c r="G234" s="8" t="inlineStr"/>
+      <c r="G234" s="8" t="inlineStr">
+        <is>
+          <t>https://www.jp-bank.japanpost.jp/brand/ambassador/dreams/images/dreams/ogp.jpg</t>
+        </is>
+      </c>
       <c r="H234" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -15587,15 +17159,19 @@
       </c>
       <c r="J234" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.90:1 (horizontal, 1200x630)</t>
         </is>
       </c>
       <c r="K234" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L234" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L234" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/jp/japan-post-bank.jpg</t>
+        </is>
+      </c>
       <c r="M234" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -15603,7 +17179,7 @@
       </c>
       <c r="N234" s="6" t="inlineStr">
         <is>
-          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via brand-press.</t>
         </is>
       </c>
     </row>
@@ -15638,7 +17214,11 @@
           <t>https://www.kbstar.com</t>
         </is>
       </c>
-      <c r="G235" s="8" t="inlineStr"/>
+      <c r="G235" s="8" t="inlineStr">
+        <is>
+          <t>https://www.kbstar.com/openimg/favi_ipad_n201512.png</t>
+        </is>
+      </c>
       <c r="H235" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -15651,15 +17231,19 @@
       </c>
       <c r="J235" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 144x144)</t>
         </is>
       </c>
       <c r="K235" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L235" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L235" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/kr/kb-kookmin-bank.png</t>
+        </is>
+      </c>
       <c r="M235" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -15667,7 +17251,7 @@
       </c>
       <c r="N235" s="6" t="inlineStr">
         <is>
-          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -15766,7 +17350,11 @@
           <t>https://www.wooribank.com</t>
         </is>
       </c>
-      <c r="G237" s="8" t="inlineStr"/>
+      <c r="G237" s="8" t="inlineStr">
+        <is>
+          <t>https://is1-ssl.mzstatic.com/image/thumb/Purple221/v4/79/7f/ea/797fea22-686a-4db9-cbbd-f8ef3b813725/AppIcon-0-0-1x_U007emarketing-0-11-0-0-sRGB-85-220.png/1024x1024bb.png</t>
+        </is>
+      </c>
       <c r="H237" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -15779,15 +17367,19 @@
       </c>
       <c r="J237" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 1024x1024)</t>
         </is>
       </c>
       <c r="K237" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L237" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L237" s="8" t="inlineStr">
+        <is>
+          <t>assets/banks/international/kr/woori-bank.png</t>
+        </is>
+      </c>
       <c r="M237" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -15795,7 +17387,7 @@
       </c>
       <c r="N237" s="6" t="inlineStr">
         <is>
-          <t>KR parent - distinct row from banks/indo/woori-saudara. Reachable via Wise and/or PandaRemit corridors from Indonesia.</t>
+          <t>KR parent - distinct row from banks/indo/woori-saudara. Reachable via Wise and/or PandaRemit corridors from Indonesia. Auto-sourced via app-store.</t>
         </is>
       </c>
     </row>
@@ -15954,7 +17546,11 @@
           <t>https://www.paypal.com</t>
         </is>
       </c>
-      <c r="G240" s="8" t="inlineStr"/>
+      <c r="G240" s="8" t="inlineStr">
+        <is>
+          <t>https://www.paypalobjects.com/marketing/web/icons/monogram/pp196.png</t>
+        </is>
+      </c>
       <c r="H240" s="8" t="inlineStr">
         <is>
           <t>icon</t>
@@ -15967,15 +17563,19 @@
       </c>
       <c r="J240" s="8" t="inlineStr">
         <is>
-          <t>TBD (square-ish)</t>
+          <t>1.00:1 (square, 196x196)</t>
         </is>
       </c>
       <c r="K240" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L240" s="8" t="inlineStr"/>
+          <t>has own baked-in background</t>
+        </is>
+      </c>
+      <c r="L240" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/international/paypal.png</t>
+        </is>
+      </c>
       <c r="M240" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -15983,7 +17583,7 @@
       </c>
       <c r="N240" s="6" t="inlineStr">
         <is>
-          <t>Indonesia support unconfirmed - confirm on PayPal's own site before including.</t>
+          <t>Indonesia support unconfirmed - confirm on PayPal's own site before including. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -16014,7 +17614,11 @@
           <t>https://wise.com</t>
         </is>
       </c>
-      <c r="G241" s="8" t="inlineStr"/>
+      <c r="G241" s="8" t="inlineStr">
+        <is>
+          <t>https://wise.com/public-resources/assets/icons/wise-personal/safari_pinned_tab.svg</t>
+        </is>
+      </c>
       <c r="H241" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -16027,15 +17631,19 @@
       </c>
       <c r="J241" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 32x32)</t>
         </is>
       </c>
       <c r="K241" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L241" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L241" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/international/wise.svg</t>
+        </is>
+      </c>
       <c r="M241" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -16043,7 +17651,7 @@
       </c>
       <c r="N241" s="6" t="inlineStr">
         <is>
-          <t>Indonesia support unconfirmed - confirm IDR receive support on wise.com before including.</t>
+          <t>Indonesia support unconfirmed - confirm IDR receive support on wise.com before including. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -16074,7 +17682,11 @@
           <t>https://www.payoneer.com</t>
         </is>
       </c>
-      <c r="G242" s="8" t="inlineStr"/>
+      <c r="G242" s="8" t="inlineStr">
+        <is>
+          <t>https://www.payoneer.com/wp-content/themes/payo/assets/img/favicons/apple-icon-152x152.png</t>
+        </is>
+      </c>
       <c r="H242" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -16087,15 +17699,19 @@
       </c>
       <c r="J242" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 152x152)</t>
         </is>
       </c>
       <c r="K242" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L242" s="8" t="inlineStr"/>
+          <t>transparent</t>
+        </is>
+      </c>
+      <c r="L242" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/international/payoneer.png</t>
+        </is>
+      </c>
       <c r="M242" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -16103,7 +17719,7 @@
       </c>
       <c r="N242" s="6" t="inlineStr">
         <is>
-          <t>Indonesia support unconfirmed - confirm on payoneer.com before including.</t>
+          <t>Indonesia support unconfirmed - confirm on payoneer.com before including. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -16134,7 +17750,11 @@
           <t>https://www.skrill.com</t>
         </is>
       </c>
-      <c r="G243" s="8" t="inlineStr"/>
+      <c r="G243" s="8" t="inlineStr">
+        <is>
+          <t>https://www.skrill.com/typo3conf/ext/sitepackage/Resources/Public/images/icons/Skrill_Logo_With_Tagline.svg</t>
+        </is>
+      </c>
       <c r="H243" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -16147,15 +17767,19 @@
       </c>
       <c r="J243" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>3.07:1 (horizontal, 141x46)</t>
         </is>
       </c>
       <c r="K243" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L243" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L243" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/international/skrill.svg</t>
+        </is>
+      </c>
       <c r="M243" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -16163,7 +17787,7 @@
       </c>
       <c r="N243" s="6" t="inlineStr">
         <is>
-          <t>Indonesia support unconfirmed - Skrill country coverage changes; confirm before including.</t>
+          <t>Indonesia support unconfirmed - Skrill country coverage changes; confirm before including. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -16194,7 +17818,11 @@
           <t>https://www.westernunion.com</t>
         </is>
       </c>
-      <c r="G244" s="8" t="inlineStr"/>
+      <c r="G244" s="8" t="inlineStr">
+        <is>
+          <t>https://www.westernunion.com/content/dam/wu/logo/logo.wu.big.svg</t>
+        </is>
+      </c>
       <c r="H244" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -16207,15 +17835,19 @@
       </c>
       <c r="J244" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>4.41:1 (horizontal, 260x59)</t>
         </is>
       </c>
       <c r="K244" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L244" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L244" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/international/western-union.svg</t>
+        </is>
+      </c>
       <c r="M244" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -16223,7 +17855,7 @@
       </c>
       <c r="N244" s="6" t="inlineStr">
         <is>
-          <t>Long-established Indonesia corridor; confirm on WU site. Also now owner of Singapore's Dash (see sea/sg/dash).</t>
+          <t>Long-established Indonesia corridor; confirm on WU site. Also now owner of Singapore's Dash (see sea/sg/dash). Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -16254,7 +17886,11 @@
           <t>https://www.moneygram.com</t>
         </is>
       </c>
-      <c r="G245" s="8" t="inlineStr"/>
+      <c r="G245" s="8" t="inlineStr">
+        <is>
+          <t>https://www.moneygram.com/_next/static/media/tiktok_logo_inverse.c05a617f.svg</t>
+        </is>
+      </c>
       <c r="H245" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -16267,15 +17903,19 @@
       </c>
       <c r="J245" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1:1.14 (vertical, 448x512)</t>
         </is>
       </c>
       <c r="K245" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L245" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L245" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/international/moneygram.svg</t>
+        </is>
+      </c>
       <c r="M245" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -16283,7 +17923,7 @@
       </c>
       <c r="N245" s="6" t="inlineStr">
         <is>
-          <t>Indonesia support unconfirmed - confirm before including.</t>
+          <t>Indonesia support unconfirmed - confirm before including. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -16314,7 +17954,11 @@
           <t>https://www.worldremit.com</t>
         </is>
       </c>
-      <c r="G246" s="8" t="inlineStr"/>
+      <c r="G246" s="8" t="inlineStr">
+        <is>
+          <t>https://www.worldremit.com/web-cms-assets/next-assets/icons/favicon.svg</t>
+        </is>
+      </c>
       <c r="H246" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -16327,15 +17971,19 @@
       </c>
       <c r="J246" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>1.00:1 (square, 32x32)</t>
         </is>
       </c>
       <c r="K246" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L246" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L246" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/international/worldremit.svg</t>
+        </is>
+      </c>
       <c r="M246" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -16343,7 +17991,7 @@
       </c>
       <c r="N246" s="6" t="inlineStr">
         <is>
-          <t>Indonesia support unconfirmed - confirm before including. Parent group also operates Zepz/Sendwave brands.</t>
+          <t>Indonesia support unconfirmed - confirm before including. Parent group also operates Zepz/Sendwave brands. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -16374,7 +18022,11 @@
           <t>https://www.remitly.com</t>
         </is>
       </c>
-      <c r="G247" s="8" t="inlineStr"/>
+      <c r="G247" s="8" t="inlineStr">
+        <is>
+          <t>https://media.remitly.io/remitly_logo_horizontal_white_tu.zrhAxFCrR5s4IlKb.svg</t>
+        </is>
+      </c>
       <c r="H247" s="8" t="inlineStr">
         <is>
           <t>wordmark</t>
@@ -16387,15 +18039,19 @@
       </c>
       <c r="J247" s="8" t="inlineStr">
         <is>
-          <t>TBD (horizontal)</t>
+          <t>4.21:1 (horizontal, 236x56)</t>
         </is>
       </c>
       <c r="K247" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L247" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L247" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/international/remitly.svg</t>
+        </is>
+      </c>
       <c r="M247" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -16403,7 +18059,7 @@
       </c>
       <c r="N247" s="6" t="inlineStr">
         <is>
-          <t>Indonesia support unconfirmed - confirm before including.</t>
+          <t>Indonesia support unconfirmed - confirm before including. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
@@ -16566,7 +18222,11 @@
           <t>https://www.revolut.com</t>
         </is>
       </c>
-      <c r="G250" s="8" t="inlineStr"/>
+      <c r="G250" s="8" t="inlineStr">
+        <is>
+          <t>https://assets.revolut.com/assets/favicons/safari-pinned-tab.svg</t>
+        </is>
+      </c>
       <c r="H250" s="8" t="inlineStr">
         <is>
           <t>app-icon</t>
@@ -16579,15 +18239,19 @@
       </c>
       <c r="J250" s="8" t="inlineStr">
         <is>
-          <t>TBD (square)</t>
+          <t>1.00:1 (square, 700x700)</t>
         </is>
       </c>
       <c r="K250" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="L250" s="8" t="inlineStr"/>
+          <t>vector (verify no baked-in background)</t>
+        </is>
+      </c>
+      <c r="L250" s="8" t="inlineStr">
+        <is>
+          <t>assets/ewallets/international/gb/revolut.svg</t>
+        </is>
+      </c>
       <c r="M250" s="10" t="inlineStr">
         <is>
           <t>Needs Review</t>
@@ -16595,7 +18259,7 @@
       </c>
       <c r="N250" s="6" t="inlineStr">
         <is>
-          <t>UK-licensed digital bank/wallet; app icon is the recognised mark. Common Wise-adjacent receiving account in Europe.</t>
+          <t>UK-licensed digital bank/wallet; app icon is the recognised mark. Common Wise-adjacent receiving account in Europe. Auto-sourced via brand-site.</t>
         </is>
       </c>
     </row>
